--- a/Excel Generic Template/excel公版.xlsx
+++ b/Excel Generic Template/excel公版.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\信邦\ai_agent2\Excel Generic Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0651A60-96FC-45E9-93FB-D71B51FC0FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FD8A1B-2C99-4576-A182-38565D85E828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14303" yWindow="-660" windowWidth="21795" windowHeight="13695" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="滾算紀錄單(總紀錄)" sheetId="7" r:id="rId1"/>
@@ -1862,7 +1862,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1885,9 +1885,6 @@
     <xf numFmtId="176" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2199,9 +2196,6 @@
     <xf numFmtId="181" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="183" fontId="9" fillId="11" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="183" fontId="8" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2215,6 +2209,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="19" fillId="12" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="12" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="12" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="12" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="12" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="12" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="20" fillId="13" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2224,12 +2251,6 @@
     <xf numFmtId="176" fontId="20" fillId="13" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="176" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2245,31 +2266,7 @@
     <xf numFmtId="176" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="12" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="12" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="12" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="12" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="12" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="12" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="9" fillId="11" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3260,112 +3257,112 @@
   <dimension ref="B1:AJ112"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="0.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="24" width="18" style="11" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="30" style="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="29" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="19.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="20.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="20.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="20.85546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="15.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="36.85546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="32.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="11"/>
+    <col min="1" max="1" width="0.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="24" width="18" style="10" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="30" style="10" bestFit="1" customWidth="1"/>
+    <col min="26" max="29" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="19.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="20.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="20.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="36.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="32.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:35" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B1" s="133" t="s">
+      <c r="B1" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="135"/>
-      <c r="P1" s="119">
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="120"/>
+      <c r="P1" s="117">
         <f>1-D11</f>
         <v>1</v>
       </c>
-      <c r="Q1" s="119">
+      <c r="Q1" s="117">
         <f t="shared" ref="Q1:AI1" si="0">P1-$D12</f>
         <v>1</v>
       </c>
-      <c r="R1" s="119">
+      <c r="R1" s="117">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="S1" s="119">
+      <c r="S1" s="117">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="T1" s="119">
+      <c r="T1" s="117">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U1" s="119">
+      <c r="U1" s="117">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="V1" s="119">
+      <c r="V1" s="117">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="W1" s="119">
+      <c r="W1" s="117">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="X1" s="119">
+      <c r="X1" s="117">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Y1" s="119">
+      <c r="Y1" s="117">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Z1" s="119">
+      <c r="Z1" s="117">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AA1" s="119">
+      <c r="AA1" s="117">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB1" s="119">
+      <c r="AB1" s="117">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AC1" s="119">
+      <c r="AC1" s="117">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AD1" s="119">
+      <c r="AD1" s="117">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AE1" s="119">
+      <c r="AE1" s="117">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AF1" s="119">
+      <c r="AF1" s="117">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AG1" s="119">
+      <c r="AG1" s="117">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH1" s="119">
+      <c r="AH1" s="117">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AI1" s="119">
+      <c r="AI1" s="117">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>41</v>
       </c>
       <c r="C2" s="3"/>
@@ -3377,7 +3374,7 @@
       </c>
     </row>
     <row r="3" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C3" s="5"/>
@@ -3389,7 +3386,7 @@
       </c>
     </row>
     <row r="4" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>43</v>
       </c>
       <c r="C4" s="5"/>
@@ -3411,128 +3408,128 @@
       <c r="E5" s="5"/>
     </row>
     <row r="6" spans="2:35" ht="20.25" customHeight="1">
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
     </row>
     <row r="7" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B7" s="130" t="s">
+      <c r="B7" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="132"/>
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="123"/>
     </row>
     <row r="8" spans="2:35" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B8" s="136" t="s">
+      <c r="B8" s="124" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="137"/>
-      <c r="D8" s="137"/>
-      <c r="E8" s="138"/>
+      <c r="C8" s="125"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="126"/>
     </row>
     <row r="9" spans="2:35" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="16" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="10" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B10" s="123" t="s">
+      <c r="B10" s="127" t="s">
         <v>52</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="123"/>
+      <c r="E10" s="127"/>
     </row>
     <row r="11" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B11" s="124"/>
+      <c r="B11" s="128"/>
       <c r="C11" s="5" t="s">
         <v>54</v>
       </c>
       <c r="D11" s="5"/>
-      <c r="E11" s="124"/>
+      <c r="E11" s="128"/>
     </row>
     <row r="12" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B12" s="124"/>
+      <c r="B12" s="128"/>
       <c r="C12" s="5" t="s">
         <v>55</v>
       </c>
       <c r="D12" s="5"/>
-      <c r="E12" s="124"/>
+      <c r="E12" s="128"/>
     </row>
     <row r="13" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B13" s="124"/>
+      <c r="B13" s="128"/>
       <c r="C13" s="7" t="s">
         <v>56</v>
       </c>
       <c r="D13" s="7"/>
-      <c r="E13" s="124"/>
+      <c r="E13" s="128"/>
     </row>
     <row r="14" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B14" s="120" t="s">
+      <c r="B14" s="129" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="121"/>
-      <c r="D14" s="121"/>
-      <c r="E14" s="122"/>
+      <c r="C14" s="130"/>
+      <c r="D14" s="130"/>
+      <c r="E14" s="131"/>
     </row>
     <row r="15" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="17" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="16" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B16" s="123" t="s">
+      <c r="B16" s="127" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>60</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="126"/>
+      <c r="E16" s="133"/>
     </row>
     <row r="17" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B17" s="124"/>
+      <c r="B17" s="128"/>
       <c r="C17" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="5"/>
-      <c r="E17" s="127"/>
+      <c r="E17" s="134"/>
     </row>
     <row r="18" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B18" s="125"/>
+      <c r="B18" s="132"/>
       <c r="C18" s="5" t="s">
         <v>62</v>
       </c>
       <c r="D18" s="5"/>
-      <c r="E18" s="128"/>
+      <c r="E18" s="135"/>
     </row>
     <row r="19" spans="2:5" ht="54" customHeight="1">
-      <c r="B19" s="129" t="s">
+      <c r="B19" s="136" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="18" t="s">
         <v>64</v>
       </c>
       <c r="D19" s="5"/>
@@ -3541,15 +3538,15 @@
       </c>
     </row>
     <row r="20" spans="2:5" ht="20.25" customHeight="1">
-      <c r="B20" s="124"/>
-      <c r="C20" s="20" t="s">
+      <c r="B20" s="128"/>
+      <c r="C20" s="19" t="s">
         <v>65</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="4"/>
     </row>
     <row r="21" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B21" s="125"/>
+      <c r="B21" s="132"/>
       <c r="C21" s="5" t="s">
         <v>66</v>
       </c>
@@ -3572,7 +3569,7 @@
       <c r="B23" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="12" t="s">
         <v>70</v>
       </c>
       <c r="D23" s="5"/>
@@ -3595,7 +3592,7 @@
       <c r="C25" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="8"/>
+      <c r="D25" s="5"/>
       <c r="E25" s="6" t="s">
         <v>0</v>
       </c>
@@ -3613,46 +3610,46 @@
       </c>
     </row>
     <row r="27" spans="2:5" ht="20.25" customHeight="1">
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
     </row>
     <row r="28" spans="2:5" ht="20.25" customHeight="1">
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
     </row>
     <row r="29" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B29" s="130" t="s">
+      <c r="B29" s="121" t="s">
         <v>77</v>
       </c>
-      <c r="C29" s="131"/>
-      <c r="D29" s="132"/>
-      <c r="E29" s="14"/>
+      <c r="C29" s="122"/>
+      <c r="D29" s="123"/>
+      <c r="E29" s="13"/>
     </row>
     <row r="30" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E30" s="14"/>
+      <c r="E30" s="13"/>
     </row>
     <row r="31" spans="2:5" ht="18.75" customHeight="1">
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D31" s="3"/>
-      <c r="E31" s="14"/>
+      <c r="E31" s="13"/>
     </row>
     <row r="32" spans="2:5" ht="18.75" customHeight="1">
       <c r="B32" s="3" t="s">
@@ -3662,7 +3659,7 @@
         <v>81</v>
       </c>
       <c r="D32" s="3"/>
-      <c r="E32" s="14"/>
+      <c r="E32" s="13"/>
     </row>
     <row r="33" spans="2:24" ht="18.75" customHeight="1">
       <c r="B33" s="5" t="s">
@@ -3672,7 +3669,7 @@
         <v>83</v>
       </c>
       <c r="D33" s="5"/>
-      <c r="E33" s="14"/>
+      <c r="E33" s="13"/>
     </row>
     <row r="34" spans="2:24" ht="18.75" customHeight="1">
       <c r="B34" s="5" t="s">
@@ -3682,4083 +3679,4083 @@
         <v>81</v>
       </c>
       <c r="D34" s="5"/>
-      <c r="E34" s="14"/>
+      <c r="E34" s="13"/>
     </row>
     <row r="35" spans="2:24" ht="18.75" customHeight="1"/>
     <row r="36" spans="2:24" ht="18.75" customHeight="1"/>
     <row r="37" spans="2:24" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B37" s="52"/>
-      <c r="C37" s="53" t="s">
+      <c r="B37" s="51"/>
+      <c r="C37" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="D37" s="53">
+      <c r="D37" s="52">
         <v>2020</v>
       </c>
-      <c r="E37" s="53">
+      <c r="E37" s="52">
         <v>2021</v>
       </c>
-      <c r="F37" s="53">
+      <c r="F37" s="52">
         <v>2022</v>
       </c>
-      <c r="G37" s="53">
+      <c r="G37" s="52">
         <v>2023</v>
       </c>
-      <c r="H37" s="53">
+      <c r="H37" s="52">
         <v>2024</v>
       </c>
-      <c r="I37" s="53">
+      <c r="I37" s="52">
         <v>2025</v>
       </c>
-      <c r="J37" s="53">
+      <c r="J37" s="52">
         <v>2026</v>
       </c>
-      <c r="K37" s="53">
+      <c r="K37" s="52">
         <v>2027</v>
       </c>
-      <c r="L37" s="53">
+      <c r="L37" s="52">
         <v>2028</v>
       </c>
-      <c r="M37" s="53">
+      <c r="M37" s="52">
         <v>2029</v>
       </c>
-      <c r="N37" s="53">
+      <c r="N37" s="52">
         <v>2030</v>
       </c>
-      <c r="O37" s="53">
+      <c r="O37" s="52">
         <v>2031</v>
       </c>
-      <c r="P37" s="53">
+      <c r="P37" s="52">
         <v>2032</v>
       </c>
-      <c r="Q37" s="53">
+      <c r="Q37" s="52">
         <v>2033</v>
       </c>
-      <c r="R37" s="53">
+      <c r="R37" s="52">
         <v>2034</v>
       </c>
-      <c r="S37" s="53">
+      <c r="S37" s="52">
         <v>2035</v>
       </c>
-      <c r="T37" s="53">
+      <c r="T37" s="52">
         <v>2036</v>
       </c>
-      <c r="U37" s="53">
+      <c r="U37" s="52">
         <v>2037</v>
       </c>
-      <c r="V37" s="53">
+      <c r="V37" s="52">
         <v>2038</v>
       </c>
-      <c r="W37" s="53">
+      <c r="W37" s="52">
         <v>2039</v>
       </c>
-      <c r="X37" s="53"/>
+      <c r="X37" s="52"/>
     </row>
     <row r="38" spans="2:24" ht="18.75" customHeight="1">
-      <c r="B38" s="22">
-        <v>0</v>
-      </c>
-      <c r="C38" s="23"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-      <c r="K38" s="26"/>
-      <c r="L38" s="26"/>
-      <c r="M38" s="26"/>
-      <c r="N38" s="26"/>
-      <c r="O38" s="26"/>
-      <c r="P38" s="26"/>
-      <c r="Q38" s="26"/>
-      <c r="R38" s="26"/>
-      <c r="S38" s="26"/>
-      <c r="T38" s="27"/>
-      <c r="U38" s="26"/>
-      <c r="V38" s="26"/>
-      <c r="W38" s="26"/>
-      <c r="X38" s="28"/>
+      <c r="B38" s="21">
+        <v>0</v>
+      </c>
+      <c r="C38" s="22"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="25"/>
+      <c r="L38" s="25"/>
+      <c r="M38" s="25"/>
+      <c r="N38" s="25"/>
+      <c r="O38" s="25"/>
+      <c r="P38" s="25"/>
+      <c r="Q38" s="25"/>
+      <c r="R38" s="25"/>
+      <c r="S38" s="25"/>
+      <c r="T38" s="26"/>
+      <c r="U38" s="25"/>
+      <c r="V38" s="25"/>
+      <c r="W38" s="25"/>
+      <c r="X38" s="27"/>
     </row>
     <row r="39" spans="2:24" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B39" s="41" t="s">
+      <c r="B39" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C39" s="42">
-        <v>0</v>
-      </c>
-      <c r="D39" s="43">
+      <c r="C39" s="41">
+        <v>0</v>
+      </c>
+      <c r="D39" s="42">
         <v>1</v>
       </c>
-      <c r="E39" s="43">
+      <c r="E39" s="42">
         <v>2</v>
       </c>
-      <c r="F39" s="43">
+      <c r="F39" s="42">
         <v>3</v>
       </c>
-      <c r="G39" s="43">
+      <c r="G39" s="42">
         <v>4</v>
       </c>
-      <c r="H39" s="43">
+      <c r="H39" s="42">
         <v>5</v>
       </c>
-      <c r="I39" s="43">
+      <c r="I39" s="42">
         <v>6</v>
       </c>
-      <c r="J39" s="43">
+      <c r="J39" s="42">
         <v>7</v>
       </c>
-      <c r="K39" s="43">
+      <c r="K39" s="42">
         <v>8</v>
       </c>
-      <c r="L39" s="43">
+      <c r="L39" s="42">
         <v>9</v>
       </c>
-      <c r="M39" s="43">
+      <c r="M39" s="42">
         <v>10</v>
       </c>
-      <c r="N39" s="43">
+      <c r="N39" s="42">
         <v>11</v>
       </c>
-      <c r="O39" s="43">
+      <c r="O39" s="42">
         <v>12</v>
       </c>
-      <c r="P39" s="43">
+      <c r="P39" s="42">
         <v>13</v>
       </c>
-      <c r="Q39" s="43">
+      <c r="Q39" s="42">
         <v>14</v>
       </c>
-      <c r="R39" s="43">
+      <c r="R39" s="42">
         <v>15</v>
       </c>
-      <c r="S39" s="43">
+      <c r="S39" s="42">
         <v>16</v>
       </c>
-      <c r="T39" s="44">
+      <c r="T39" s="43">
         <v>17</v>
       </c>
-      <c r="U39" s="43">
+      <c r="U39" s="42">
         <v>18</v>
       </c>
-      <c r="V39" s="43">
+      <c r="V39" s="42">
         <v>19</v>
       </c>
-      <c r="W39" s="43">
+      <c r="W39" s="42">
         <v>20</v>
       </c>
-      <c r="X39" s="45"/>
+      <c r="X39" s="44"/>
     </row>
     <row r="40" spans="2:24" ht="18.75" customHeight="1">
-      <c r="B40" s="29" t="s">
+      <c r="B40" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C40" s="10">
-        <v>0</v>
-      </c>
-      <c r="D40" s="106">
+      <c r="C40" s="9">
+        <v>0</v>
+      </c>
+      <c r="D40" s="105">
         <f>$D$10*P1</f>
         <v>0</v>
       </c>
-      <c r="E40" s="106">
+      <c r="E40" s="105">
         <f t="shared" ref="E40:W40" si="1">$D$10*Q1</f>
         <v>0</v>
       </c>
-      <c r="F40" s="106">
+      <c r="F40" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G40" s="106">
+      <c r="G40" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H40" s="106">
+      <c r="H40" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I40" s="106">
+      <c r="I40" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J40" s="106">
+      <c r="J40" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K40" s="106">
+      <c r="K40" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L40" s="106">
+      <c r="L40" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M40" s="106">
+      <c r="M40" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N40" s="106">
+      <c r="N40" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O40" s="106">
+      <c r="O40" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P40" s="106">
+      <c r="P40" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q40" s="106">
+      <c r="Q40" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R40" s="106">
+      <c r="R40" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S40" s="106">
+      <c r="S40" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T40" s="106">
+      <c r="T40" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U40" s="106">
+      <c r="U40" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V40" s="106">
+      <c r="V40" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W40" s="106">
+      <c r="W40" s="105">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X40" s="30"/>
-    </row>
-    <row r="41" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B41" s="55" t="s">
+      <c r="X40" s="29"/>
+    </row>
+    <row r="41" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B41" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="C41" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41" s="105">
+      <c r="C41" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="104">
         <f>D40*$D$13</f>
         <v>0</v>
       </c>
-      <c r="E41" s="105">
+      <c r="E41" s="104">
         <f t="shared" ref="E41:W41" si="2">E40*$D$13</f>
         <v>0</v>
       </c>
-      <c r="F41" s="105">
+      <c r="F41" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G41" s="105">
+      <c r="G41" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H41" s="105">
+      <c r="H41" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I41" s="105">
+      <c r="I41" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J41" s="105">
+      <c r="J41" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K41" s="105">
+      <c r="K41" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L41" s="105">
+      <c r="L41" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M41" s="105">
+      <c r="M41" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N41" s="105">
+      <c r="N41" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O41" s="105">
+      <c r="O41" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P41" s="105">
+      <c r="P41" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q41" s="105">
+      <c r="Q41" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R41" s="105">
+      <c r="R41" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S41" s="105">
+      <c r="S41" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T41" s="105">
+      <c r="T41" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U41" s="105">
+      <c r="U41" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V41" s="105">
+      <c r="V41" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W41" s="105">
+      <c r="W41" s="104">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X41" s="57"/>
-    </row>
-    <row r="42" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B42" s="59" t="s">
+      <c r="X41" s="56"/>
+    </row>
+    <row r="42" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B42" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="D42" s="61"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="H42" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="I42" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="J42" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="K42" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="L42" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="M42" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="N42" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="O42" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="P42" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="R42" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="S42" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="T42" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="U42" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="V42" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="W42" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="X42" s="62"/>
-    </row>
-    <row r="43" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B43" s="63" t="s">
+      <c r="C42" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="D42" s="60"/>
+      <c r="E42" s="60"/>
+      <c r="F42" s="60"/>
+      <c r="G42" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="H42" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="I42" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="J42" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="K42" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="L42" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="M42" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="N42" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="O42" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="P42" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="R42" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="S42" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="T42" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="U42" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="V42" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="W42" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="X42" s="61"/>
+    </row>
+    <row r="43" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
+      <c r="B43" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="64"/>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="65"/>
-      <c r="K43" s="65"/>
-      <c r="L43" s="65"/>
-      <c r="M43" s="65"/>
-      <c r="N43" s="65"/>
-      <c r="O43" s="65"/>
-      <c r="P43" s="65"/>
-      <c r="Q43" s="65"/>
-      <c r="R43" s="65"/>
-      <c r="S43" s="65"/>
-      <c r="T43" s="65"/>
-      <c r="U43" s="65"/>
-      <c r="V43" s="65"/>
-      <c r="W43" s="65"/>
-      <c r="X43" s="66"/>
-    </row>
-    <row r="44" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B44" s="67" t="s">
+      <c r="C43" s="63"/>
+      <c r="D43" s="64"/>
+      <c r="E43" s="64"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="64"/>
+      <c r="H43" s="64"/>
+      <c r="I43" s="64"/>
+      <c r="J43" s="64"/>
+      <c r="K43" s="64"/>
+      <c r="L43" s="64"/>
+      <c r="M43" s="64"/>
+      <c r="N43" s="64"/>
+      <c r="O43" s="64"/>
+      <c r="P43" s="64"/>
+      <c r="Q43" s="64"/>
+      <c r="R43" s="64"/>
+      <c r="S43" s="64"/>
+      <c r="T43" s="64"/>
+      <c r="U43" s="64"/>
+      <c r="V43" s="64"/>
+      <c r="W43" s="64"/>
+      <c r="X43" s="65"/>
+    </row>
+    <row r="44" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B44" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="C44" s="99">
+      <c r="C44" s="98">
         <f>-(D16/(1-D17)+D18)*C4</f>
         <v>0</v>
       </c>
-      <c r="D44" s="100"/>
-      <c r="E44" s="100"/>
-      <c r="F44" s="100"/>
-      <c r="G44" s="100"/>
-      <c r="H44" s="100"/>
-      <c r="I44" s="100"/>
-      <c r="J44" s="100"/>
-      <c r="K44" s="100"/>
-      <c r="L44" s="100"/>
-      <c r="M44" s="100"/>
-      <c r="N44" s="100"/>
-      <c r="O44" s="100"/>
-      <c r="P44" s="100"/>
-      <c r="Q44" s="100"/>
-      <c r="R44" s="100"/>
-      <c r="S44" s="100"/>
-      <c r="T44" s="100"/>
-      <c r="U44" s="100"/>
-      <c r="V44" s="100"/>
-      <c r="W44" s="100"/>
-      <c r="X44" s="100"/>
-    </row>
-    <row r="45" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B45" s="67" t="s">
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
+      <c r="F44" s="99"/>
+      <c r="G44" s="99"/>
+      <c r="H44" s="99"/>
+      <c r="I44" s="99"/>
+      <c r="J44" s="99"/>
+      <c r="K44" s="99"/>
+      <c r="L44" s="99"/>
+      <c r="M44" s="99"/>
+      <c r="N44" s="99"/>
+      <c r="O44" s="99"/>
+      <c r="P44" s="99"/>
+      <c r="Q44" s="99"/>
+      <c r="R44" s="99"/>
+      <c r="S44" s="99"/>
+      <c r="T44" s="99"/>
+      <c r="U44" s="99"/>
+      <c r="V44" s="99"/>
+      <c r="W44" s="99"/>
+      <c r="X44" s="99"/>
+    </row>
+    <row r="45" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B45" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="C45" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="D45" s="100"/>
-      <c r="E45" s="100"/>
-      <c r="F45" s="100"/>
-      <c r="G45" s="100"/>
-      <c r="H45" s="100"/>
-      <c r="I45" s="100"/>
-      <c r="J45" s="100"/>
-      <c r="K45" s="100"/>
-      <c r="L45" s="100"/>
-      <c r="M45" s="100"/>
-      <c r="N45" s="100"/>
-      <c r="O45" s="100"/>
-      <c r="P45" s="100"/>
-      <c r="Q45" s="100"/>
-      <c r="R45" s="100"/>
-      <c r="S45" s="100"/>
-      <c r="T45" s="100"/>
-      <c r="U45" s="100"/>
-      <c r="V45" s="100"/>
-      <c r="W45" s="100"/>
-      <c r="X45" s="100"/>
-    </row>
-    <row r="46" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B46" s="67" t="s">
+      <c r="C45" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
+      <c r="F45" s="99"/>
+      <c r="G45" s="99"/>
+      <c r="H45" s="99"/>
+      <c r="I45" s="99"/>
+      <c r="J45" s="99"/>
+      <c r="K45" s="99"/>
+      <c r="L45" s="99"/>
+      <c r="M45" s="99"/>
+      <c r="N45" s="99"/>
+      <c r="O45" s="99"/>
+      <c r="P45" s="99"/>
+      <c r="Q45" s="99"/>
+      <c r="R45" s="99"/>
+      <c r="S45" s="99"/>
+      <c r="T45" s="99"/>
+      <c r="U45" s="99"/>
+      <c r="V45" s="99"/>
+      <c r="W45" s="99"/>
+      <c r="X45" s="99"/>
+    </row>
+    <row r="46" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B46" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="C46" s="60"/>
-      <c r="D46" s="100"/>
-      <c r="E46" s="100"/>
-      <c r="F46" s="100"/>
-      <c r="G46" s="100"/>
-      <c r="H46" s="100"/>
-      <c r="I46" s="100"/>
-      <c r="J46" s="100"/>
-      <c r="K46" s="100"/>
-      <c r="L46" s="100"/>
-      <c r="M46" s="100"/>
-      <c r="N46" s="100"/>
-      <c r="O46" s="100"/>
-      <c r="P46" s="100"/>
-      <c r="Q46" s="100"/>
-      <c r="R46" s="100"/>
-      <c r="S46" s="100"/>
-      <c r="T46" s="100"/>
-      <c r="U46" s="100"/>
-      <c r="V46" s="100"/>
-      <c r="W46" s="100"/>
-      <c r="X46" s="100"/>
-    </row>
-    <row r="47" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B47" s="67" t="s">
+      <c r="C46" s="59"/>
+      <c r="D46" s="99"/>
+      <c r="E46" s="99"/>
+      <c r="F46" s="99"/>
+      <c r="G46" s="99"/>
+      <c r="H46" s="99"/>
+      <c r="I46" s="99"/>
+      <c r="J46" s="99"/>
+      <c r="K46" s="99"/>
+      <c r="L46" s="99"/>
+      <c r="M46" s="99"/>
+      <c r="N46" s="99"/>
+      <c r="O46" s="99"/>
+      <c r="P46" s="99"/>
+      <c r="Q46" s="99"/>
+      <c r="R46" s="99"/>
+      <c r="S46" s="99"/>
+      <c r="T46" s="99"/>
+      <c r="U46" s="99"/>
+      <c r="V46" s="99"/>
+      <c r="W46" s="99"/>
+      <c r="X46" s="99"/>
+    </row>
+    <row r="47" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B47" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="C47" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="D47" s="100"/>
-      <c r="E47" s="100"/>
-      <c r="F47" s="100"/>
-      <c r="G47" s="100"/>
-      <c r="H47" s="100"/>
-      <c r="I47" s="100"/>
-      <c r="J47" s="100"/>
-      <c r="K47" s="100"/>
-      <c r="L47" s="100"/>
-      <c r="M47" s="100"/>
-      <c r="N47" s="100"/>
-      <c r="O47" s="100"/>
-      <c r="P47" s="100"/>
-      <c r="Q47" s="100"/>
-      <c r="R47" s="100"/>
-      <c r="S47" s="100"/>
-      <c r="T47" s="100"/>
-      <c r="U47" s="100"/>
-      <c r="V47" s="100"/>
-      <c r="W47" s="100"/>
-      <c r="X47" s="100"/>
-    </row>
-    <row r="48" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B48" s="67" t="s">
+      <c r="C47" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="D47" s="99"/>
+      <c r="E47" s="99"/>
+      <c r="F47" s="99"/>
+      <c r="G47" s="99"/>
+      <c r="H47" s="99"/>
+      <c r="I47" s="99"/>
+      <c r="J47" s="99"/>
+      <c r="K47" s="99"/>
+      <c r="L47" s="99"/>
+      <c r="M47" s="99"/>
+      <c r="N47" s="99"/>
+      <c r="O47" s="99"/>
+      <c r="P47" s="99"/>
+      <c r="Q47" s="99"/>
+      <c r="R47" s="99"/>
+      <c r="S47" s="99"/>
+      <c r="T47" s="99"/>
+      <c r="U47" s="99"/>
+      <c r="V47" s="99"/>
+      <c r="W47" s="99"/>
+      <c r="X47" s="99"/>
+    </row>
+    <row r="48" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B48" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="D48" s="100"/>
-      <c r="E48" s="100"/>
-      <c r="F48" s="100"/>
-      <c r="G48" s="100"/>
-      <c r="H48" s="100"/>
-      <c r="I48" s="100"/>
-      <c r="J48" s="100"/>
-      <c r="K48" s="100"/>
-      <c r="L48" s="100"/>
-      <c r="M48" s="100"/>
-      <c r="N48" s="100"/>
-      <c r="O48" s="100"/>
-      <c r="P48" s="100"/>
-      <c r="Q48" s="100"/>
-      <c r="R48" s="100"/>
-      <c r="S48" s="100"/>
-      <c r="T48" s="100"/>
-      <c r="U48" s="100"/>
-      <c r="V48" s="100"/>
-      <c r="W48" s="100"/>
-      <c r="X48" s="100"/>
-    </row>
-    <row r="49" spans="2:36" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B49" s="67" t="s">
+      <c r="C48" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="D48" s="99"/>
+      <c r="E48" s="99"/>
+      <c r="F48" s="99"/>
+      <c r="G48" s="99"/>
+      <c r="H48" s="99"/>
+      <c r="I48" s="99"/>
+      <c r="J48" s="99"/>
+      <c r="K48" s="99"/>
+      <c r="L48" s="99"/>
+      <c r="M48" s="99"/>
+      <c r="N48" s="99"/>
+      <c r="O48" s="99"/>
+      <c r="P48" s="99"/>
+      <c r="Q48" s="99"/>
+      <c r="R48" s="99"/>
+      <c r="S48" s="99"/>
+      <c r="T48" s="99"/>
+      <c r="U48" s="99"/>
+      <c r="V48" s="99"/>
+      <c r="W48" s="99"/>
+      <c r="X48" s="99"/>
+    </row>
+    <row r="49" spans="2:36" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B49" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="C49" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="D49" s="100"/>
-      <c r="E49" s="100"/>
-      <c r="F49" s="100"/>
-      <c r="G49" s="100"/>
-      <c r="H49" s="100"/>
-      <c r="I49" s="100"/>
-      <c r="J49" s="100"/>
-      <c r="K49" s="100"/>
-      <c r="L49" s="100"/>
-      <c r="M49" s="100"/>
-      <c r="N49" s="100"/>
-      <c r="O49" s="100"/>
-      <c r="P49" s="100"/>
-      <c r="Q49" s="100"/>
-      <c r="R49" s="100"/>
-      <c r="S49" s="100"/>
-      <c r="T49" s="100"/>
-      <c r="U49" s="100"/>
-      <c r="V49" s="100"/>
-      <c r="W49" s="100"/>
-      <c r="X49" s="100"/>
-    </row>
-    <row r="50" spans="2:36" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B50" s="67" t="s">
+      <c r="C49" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="D49" s="99"/>
+      <c r="E49" s="99"/>
+      <c r="F49" s="99"/>
+      <c r="G49" s="99"/>
+      <c r="H49" s="99"/>
+      <c r="I49" s="99"/>
+      <c r="J49" s="99"/>
+      <c r="K49" s="99"/>
+      <c r="L49" s="99"/>
+      <c r="M49" s="99"/>
+      <c r="N49" s="99"/>
+      <c r="O49" s="99"/>
+      <c r="P49" s="99"/>
+      <c r="Q49" s="99"/>
+      <c r="R49" s="99"/>
+      <c r="S49" s="99"/>
+      <c r="T49" s="99"/>
+      <c r="U49" s="99"/>
+      <c r="V49" s="99"/>
+      <c r="W49" s="99"/>
+      <c r="X49" s="99"/>
+    </row>
+    <row r="50" spans="2:36" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B50" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="60"/>
-      <c r="D50" s="100"/>
-      <c r="E50" s="100"/>
-      <c r="F50" s="100"/>
-      <c r="G50" s="100"/>
-      <c r="H50" s="100"/>
-      <c r="I50" s="100"/>
-      <c r="J50" s="100"/>
-      <c r="K50" s="100"/>
-      <c r="L50" s="100"/>
-      <c r="M50" s="100"/>
-      <c r="N50" s="100"/>
-      <c r="O50" s="100"/>
-      <c r="P50" s="100"/>
-      <c r="Q50" s="100"/>
-      <c r="R50" s="100"/>
-      <c r="S50" s="100"/>
-      <c r="T50" s="100"/>
-      <c r="U50" s="100"/>
-      <c r="V50" s="100"/>
-      <c r="W50" s="100"/>
-      <c r="X50" s="100"/>
-    </row>
-    <row r="51" spans="2:36" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B51" s="67" t="s">
+      <c r="C50" s="59"/>
+      <c r="D50" s="99"/>
+      <c r="E50" s="99"/>
+      <c r="F50" s="99"/>
+      <c r="G50" s="99"/>
+      <c r="H50" s="99"/>
+      <c r="I50" s="99"/>
+      <c r="J50" s="99"/>
+      <c r="K50" s="99"/>
+      <c r="L50" s="99"/>
+      <c r="M50" s="99"/>
+      <c r="N50" s="99"/>
+      <c r="O50" s="99"/>
+      <c r="P50" s="99"/>
+      <c r="Q50" s="99"/>
+      <c r="R50" s="99"/>
+      <c r="S50" s="99"/>
+      <c r="T50" s="99"/>
+      <c r="U50" s="99"/>
+      <c r="V50" s="99"/>
+      <c r="W50" s="99"/>
+      <c r="X50" s="99"/>
+    </row>
+    <row r="51" spans="2:36" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B51" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="C51" s="68"/>
-      <c r="D51" s="100"/>
-      <c r="E51" s="100"/>
-      <c r="F51" s="100"/>
-      <c r="G51" s="100"/>
-      <c r="H51" s="100"/>
-      <c r="I51" s="100"/>
-      <c r="J51" s="100"/>
-      <c r="K51" s="100"/>
-      <c r="L51" s="100"/>
-      <c r="M51" s="100"/>
-      <c r="N51" s="100"/>
-      <c r="O51" s="100"/>
-      <c r="P51" s="100"/>
-      <c r="Q51" s="100"/>
-      <c r="R51" s="100"/>
-      <c r="S51" s="100"/>
-      <c r="T51" s="100"/>
-      <c r="U51" s="100"/>
-      <c r="V51" s="100"/>
-      <c r="W51" s="100"/>
-      <c r="X51" s="100"/>
-    </row>
-    <row r="52" spans="2:36" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B52" s="67" t="s">
+      <c r="C51" s="67"/>
+      <c r="D51" s="99"/>
+      <c r="E51" s="99"/>
+      <c r="F51" s="99"/>
+      <c r="G51" s="99"/>
+      <c r="H51" s="99"/>
+      <c r="I51" s="99"/>
+      <c r="J51" s="99"/>
+      <c r="K51" s="99"/>
+      <c r="L51" s="99"/>
+      <c r="M51" s="99"/>
+      <c r="N51" s="99"/>
+      <c r="O51" s="99"/>
+      <c r="P51" s="99"/>
+      <c r="Q51" s="99"/>
+      <c r="R51" s="99"/>
+      <c r="S51" s="99"/>
+      <c r="T51" s="99"/>
+      <c r="U51" s="99"/>
+      <c r="V51" s="99"/>
+      <c r="W51" s="99"/>
+      <c r="X51" s="99"/>
+    </row>
+    <row r="52" spans="2:36" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B52" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C52" s="68"/>
-      <c r="D52" s="100"/>
-      <c r="E52" s="100"/>
-      <c r="F52" s="100"/>
-      <c r="G52" s="100"/>
-      <c r="H52" s="100"/>
-      <c r="I52" s="100"/>
-      <c r="J52" s="100"/>
-      <c r="K52" s="100"/>
-      <c r="L52" s="100"/>
-      <c r="M52" s="100"/>
-      <c r="N52" s="100"/>
-      <c r="O52" s="100"/>
-      <c r="P52" s="100"/>
-      <c r="Q52" s="100"/>
-      <c r="R52" s="100"/>
-      <c r="S52" s="100"/>
-      <c r="T52" s="100"/>
-      <c r="U52" s="100"/>
-      <c r="V52" s="100"/>
-      <c r="W52" s="100"/>
-      <c r="X52" s="100"/>
-    </row>
-    <row r="53" spans="2:36" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B53" s="71" t="s">
+      <c r="C52" s="67"/>
+      <c r="D52" s="99"/>
+      <c r="E52" s="99"/>
+      <c r="F52" s="99"/>
+      <c r="G52" s="99"/>
+      <c r="H52" s="99"/>
+      <c r="I52" s="99"/>
+      <c r="J52" s="99"/>
+      <c r="K52" s="99"/>
+      <c r="L52" s="99"/>
+      <c r="M52" s="99"/>
+      <c r="N52" s="99"/>
+      <c r="O52" s="99"/>
+      <c r="P52" s="99"/>
+      <c r="Q52" s="99"/>
+      <c r="R52" s="99"/>
+      <c r="S52" s="99"/>
+      <c r="T52" s="99"/>
+      <c r="U52" s="99"/>
+      <c r="V52" s="99"/>
+      <c r="W52" s="99"/>
+      <c r="X52" s="99"/>
+    </row>
+    <row r="53" spans="2:36" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B53" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="68"/>
-      <c r="D53" s="100"/>
-      <c r="E53" s="100"/>
-      <c r="F53" s="100"/>
-      <c r="G53" s="100"/>
-      <c r="H53" s="100"/>
-      <c r="I53" s="100"/>
-      <c r="J53" s="100"/>
-      <c r="K53" s="100"/>
-      <c r="L53" s="100"/>
-      <c r="M53" s="100"/>
-      <c r="N53" s="100"/>
-      <c r="O53" s="100"/>
-      <c r="P53" s="100"/>
-      <c r="Q53" s="100"/>
-      <c r="R53" s="100"/>
-      <c r="S53" s="100"/>
-      <c r="T53" s="100"/>
-      <c r="U53" s="100"/>
-      <c r="V53" s="100"/>
-      <c r="W53" s="100"/>
-      <c r="X53" s="100"/>
-    </row>
-    <row r="54" spans="2:36" s="58" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B54" s="71" t="s">
+      <c r="C53" s="67"/>
+      <c r="D53" s="99"/>
+      <c r="E53" s="99"/>
+      <c r="F53" s="99"/>
+      <c r="G53" s="99"/>
+      <c r="H53" s="99"/>
+      <c r="I53" s="99"/>
+      <c r="J53" s="99"/>
+      <c r="K53" s="99"/>
+      <c r="L53" s="99"/>
+      <c r="M53" s="99"/>
+      <c r="N53" s="99"/>
+      <c r="O53" s="99"/>
+      <c r="P53" s="99"/>
+      <c r="Q53" s="99"/>
+      <c r="R53" s="99"/>
+      <c r="S53" s="99"/>
+      <c r="T53" s="99"/>
+      <c r="U53" s="99"/>
+      <c r="V53" s="99"/>
+      <c r="W53" s="99"/>
+      <c r="X53" s="99"/>
+    </row>
+    <row r="54" spans="2:36" s="57" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
+      <c r="B54" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="68"/>
-      <c r="D54" s="100" t="e">
+      <c r="C54" s="67"/>
+      <c r="D54" s="99" t="e">
         <f>-(D64+D67+D68+D71+D72+D73+D74)*0.2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E54" s="100" t="e">
+      <c r="E54" s="99" t="e">
         <f t="shared" ref="E54:W54" si="3">-(E64+E67+E68+E71+E72+E73+E74)*0.2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F54" s="100" t="e">
+      <c r="F54" s="99" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G54" s="100" t="e">
+      <c r="G54" s="99" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H54" s="100" t="e">
+      <c r="H54" s="99" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I54" s="100" t="e">
+      <c r="I54" s="99" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J54" s="100" t="e">
+      <c r="J54" s="99" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K54" s="100" t="e">
+      <c r="K54" s="99" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L54" s="100" t="e">
+      <c r="L54" s="99" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M54" s="100" t="e">
+      <c r="M54" s="99" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N54" s="100" t="e">
+      <c r="N54" s="99" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O54" s="100" t="e">
+      <c r="O54" s="99" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P54" s="100" t="e">
+      <c r="P54" s="99" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q54" s="100" t="e">
+      <c r="Q54" s="99" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R54" s="100" t="e">
+      <c r="R54" s="99" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S54" s="100" t="e">
+      <c r="S54" s="99" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T54" s="100" t="e">
+      <c r="T54" s="99" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U54" s="100" t="e">
+      <c r="U54" s="99" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V54" s="100" t="e">
+      <c r="V54" s="99" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W54" s="100" t="e">
+      <c r="W54" s="99" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X54" s="61"/>
-    </row>
-    <row r="55" spans="2:36" s="58" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B55" s="72" t="s">
+      <c r="X54" s="60"/>
+    </row>
+    <row r="55" spans="2:36" s="57" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
+      <c r="B55" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="C55" s="104">
+      <c r="C55" s="103">
         <f>C44</f>
         <v>0</v>
       </c>
-      <c r="D55" s="101" t="e">
+      <c r="D55" s="100" t="e">
         <f>SUM(D41:D54)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E55" s="101" t="e">
+      <c r="E55" s="100" t="e">
         <f>SUM(E41:E54)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F55" s="101" t="e">
+      <c r="F55" s="100" t="e">
         <f t="shared" ref="F55:W55" si="4">SUM(F41:F54)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G55" s="101" t="e">
+      <c r="G55" s="100" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H55" s="101" t="e">
+      <c r="H55" s="100" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I55" s="101" t="e">
+      <c r="I55" s="100" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J55" s="101" t="e">
+      <c r="J55" s="100" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K55" s="101" t="e">
+      <c r="K55" s="100" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L55" s="101" t="e">
+      <c r="L55" s="100" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M55" s="101" t="e">
+      <c r="M55" s="100" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N55" s="101" t="e">
+      <c r="N55" s="100" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O55" s="101" t="e">
+      <c r="O55" s="100" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P55" s="101" t="e">
+      <c r="P55" s="100" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q55" s="101" t="e">
+      <c r="Q55" s="100" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R55" s="101" t="e">
+      <c r="R55" s="100" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S55" s="101" t="e">
+      <c r="S55" s="100" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T55" s="101" t="e">
+      <c r="T55" s="100" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U55" s="101" t="e">
+      <c r="U55" s="100" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V55" s="101" t="e">
+      <c r="V55" s="100" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W55" s="101" t="e">
+      <c r="W55" s="100" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X55" s="74"/>
-      <c r="Y55" s="75"/>
-      <c r="Z55" s="76"/>
-      <c r="AA55" s="75"/>
-      <c r="AB55" s="75"/>
-      <c r="AC55" s="75"/>
-      <c r="AD55" s="75"/>
-      <c r="AE55" s="75"/>
-      <c r="AF55" s="75"/>
-      <c r="AG55" s="75"/>
-      <c r="AH55" s="75"/>
-      <c r="AI55" s="75"/>
-      <c r="AJ55" s="75"/>
-    </row>
-    <row r="56" spans="2:36" s="58" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B56" s="77" t="s">
+      <c r="X55" s="73"/>
+      <c r="Y55" s="74"/>
+      <c r="Z55" s="75"/>
+      <c r="AA55" s="74"/>
+      <c r="AB55" s="74"/>
+      <c r="AC55" s="74"/>
+      <c r="AD55" s="74"/>
+      <c r="AE55" s="74"/>
+      <c r="AF55" s="74"/>
+      <c r="AG55" s="74"/>
+      <c r="AH55" s="74"/>
+      <c r="AI55" s="74"/>
+      <c r="AJ55" s="74"/>
+    </row>
+    <row r="56" spans="2:36" s="57" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
+      <c r="B56" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="D56" s="102" t="e">
+      <c r="D56" s="101" t="e">
         <f>C55+D55</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E56" s="102" t="e">
+      <c r="E56" s="101" t="e">
         <f>D56+E55</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F56" s="102" t="e">
+      <c r="F56" s="101" t="e">
         <f t="shared" ref="F56:X56" si="5">E56+F55</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G56" s="102" t="e">
+      <c r="G56" s="101" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H56" s="102" t="e">
+      <c r="H56" s="101" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I56" s="102" t="e">
+      <c r="I56" s="101" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J56" s="102" t="e">
+      <c r="J56" s="101" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K56" s="102" t="e">
+      <c r="K56" s="101" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L56" s="102" t="e">
+      <c r="L56" s="101" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M56" s="102" t="e">
+      <c r="M56" s="101" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N56" s="102" t="e">
+      <c r="N56" s="101" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O56" s="102" t="e">
+      <c r="O56" s="101" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P56" s="102" t="e">
+      <c r="P56" s="101" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q56" s="102" t="e">
+      <c r="Q56" s="101" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R56" s="102" t="e">
+      <c r="R56" s="101" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S56" s="102" t="e">
+      <c r="S56" s="101" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T56" s="102" t="e">
+      <c r="T56" s="101" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U56" s="102" t="e">
+      <c r="U56" s="101" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V56" s="102" t="e">
+      <c r="V56" s="101" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W56" s="102" t="e">
+      <c r="W56" s="101" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X56" s="102" t="e">
+      <c r="X56" s="101" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y56" s="75"/>
-      <c r="Z56" s="75"/>
-      <c r="AA56" s="75"/>
-      <c r="AB56" s="75"/>
-      <c r="AC56" s="75"/>
-      <c r="AD56" s="75"/>
-      <c r="AE56" s="75"/>
-      <c r="AF56" s="75"/>
-      <c r="AG56" s="75"/>
-      <c r="AH56" s="75"/>
-      <c r="AI56" s="75"/>
-      <c r="AJ56" s="75"/>
-    </row>
-    <row r="57" spans="2:36" s="58" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B57" s="80" t="s">
+      <c r="Y56" s="74"/>
+      <c r="Z56" s="74"/>
+      <c r="AA56" s="74"/>
+      <c r="AB56" s="74"/>
+      <c r="AC56" s="74"/>
+      <c r="AD56" s="74"/>
+      <c r="AE56" s="74"/>
+      <c r="AF56" s="74"/>
+      <c r="AG56" s="74"/>
+      <c r="AH56" s="74"/>
+      <c r="AI56" s="74"/>
+      <c r="AJ56" s="74"/>
+    </row>
+    <row r="57" spans="2:36" s="57" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
+      <c r="B57" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C57" s="81"/>
-      <c r="D57" s="103" t="e">
+      <c r="C57" s="80"/>
+      <c r="D57" s="102" t="e">
         <f t="shared" ref="D57:X57" si="6">IF((D56)&gt;0,"回收","未回收")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E57" s="82" t="e">
+      <c r="E57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F57" s="82" t="e">
+      <c r="F57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G57" s="82" t="e">
+      <c r="G57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H57" s="82" t="e">
+      <c r="H57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I57" s="82" t="e">
+      <c r="I57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J57" s="82" t="e">
+      <c r="J57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K57" s="82" t="e">
+      <c r="K57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L57" s="82" t="e">
+      <c r="L57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M57" s="82" t="e">
+      <c r="M57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N57" s="82" t="e">
+      <c r="N57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O57" s="82" t="e">
+      <c r="O57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P57" s="82" t="e">
+      <c r="P57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q57" s="82" t="e">
+      <c r="Q57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R57" s="82" t="e">
+      <c r="R57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S57" s="82" t="e">
+      <c r="S57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T57" s="82" t="e">
+      <c r="T57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U57" s="82" t="e">
+      <c r="U57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V57" s="82" t="e">
+      <c r="V57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W57" s="82" t="e">
+      <c r="W57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X57" s="82" t="e">
+      <c r="X57" s="81" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y57" s="75"/>
-      <c r="Z57" s="75"/>
-      <c r="AA57" s="75"/>
-      <c r="AB57" s="75"/>
-      <c r="AC57" s="75"/>
-      <c r="AD57" s="75"/>
-      <c r="AE57" s="75"/>
-      <c r="AF57" s="75"/>
-      <c r="AG57" s="75"/>
-      <c r="AH57" s="75"/>
-      <c r="AI57" s="75"/>
-      <c r="AJ57" s="75"/>
+      <c r="Y57" s="74"/>
+      <c r="Z57" s="74"/>
+      <c r="AA57" s="74"/>
+      <c r="AB57" s="74"/>
+      <c r="AC57" s="74"/>
+      <c r="AD57" s="74"/>
+      <c r="AE57" s="74"/>
+      <c r="AF57" s="74"/>
+      <c r="AG57" s="74"/>
+      <c r="AH57" s="74"/>
+      <c r="AI57" s="74"/>
+      <c r="AJ57" s="74"/>
     </row>
     <row r="58" spans="2:36" ht="18.75" customHeight="1">
-      <c r="B58" s="36" t="s">
+      <c r="B58" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C58" s="98" t="e">
+      <c r="C58" s="97" t="e">
         <f>IRR(C55:W55)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21"/>
-      <c r="H58" s="21"/>
-      <c r="I58" s="21"/>
-      <c r="J58" s="21"/>
-      <c r="K58" s="21"/>
-      <c r="L58" s="21"/>
-      <c r="M58" s="21"/>
-      <c r="N58" s="21"/>
-      <c r="O58" s="21"/>
-      <c r="P58" s="21"/>
-      <c r="Q58" s="21"/>
-      <c r="R58" s="21"/>
-      <c r="S58" s="21"/>
-      <c r="T58" s="21"/>
-      <c r="U58" s="21"/>
-      <c r="V58" s="21"/>
-      <c r="W58" s="21"/>
-      <c r="X58" s="21"/>
-      <c r="Y58" s="31"/>
-      <c r="Z58" s="31"/>
-      <c r="AA58" s="31"/>
-      <c r="AB58" s="31"/>
-      <c r="AC58" s="31"/>
-      <c r="AD58" s="31"/>
-      <c r="AE58" s="31"/>
-      <c r="AF58" s="31"/>
-      <c r="AG58" s="31"/>
-      <c r="AH58" s="31"/>
-      <c r="AI58" s="31"/>
-      <c r="AJ58" s="31"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="20"/>
+      <c r="J58" s="20"/>
+      <c r="K58" s="20"/>
+      <c r="L58" s="20"/>
+      <c r="M58" s="20"/>
+      <c r="N58" s="20"/>
+      <c r="O58" s="20"/>
+      <c r="P58" s="20"/>
+      <c r="Q58" s="20"/>
+      <c r="R58" s="20"/>
+      <c r="S58" s="20"/>
+      <c r="T58" s="20"/>
+      <c r="U58" s="20"/>
+      <c r="V58" s="20"/>
+      <c r="W58" s="20"/>
+      <c r="X58" s="20"/>
+      <c r="Y58" s="30"/>
+      <c r="Z58" s="30"/>
+      <c r="AA58" s="30"/>
+      <c r="AB58" s="30"/>
+      <c r="AC58" s="30"/>
+      <c r="AD58" s="30"/>
+      <c r="AE58" s="30"/>
+      <c r="AF58" s="30"/>
+      <c r="AG58" s="30"/>
+      <c r="AH58" s="30"/>
+      <c r="AI58" s="30"/>
+      <c r="AJ58" s="30"/>
     </row>
     <row r="59" spans="2:36" ht="18.75" customHeight="1">
-      <c r="B59" s="21"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="21"/>
-      <c r="G59" s="21"/>
-      <c r="H59" s="21"/>
-      <c r="I59" s="21"/>
-      <c r="J59" s="21"/>
-      <c r="K59" s="21"/>
-      <c r="L59" s="21"/>
-      <c r="M59" s="9"/>
-      <c r="N59" s="21"/>
-      <c r="O59" s="21"/>
-      <c r="P59" s="21"/>
-      <c r="Q59" s="21"/>
-      <c r="R59" s="21"/>
-      <c r="S59" s="21"/>
-      <c r="T59" s="21"/>
-      <c r="U59" s="21"/>
-      <c r="V59" s="21"/>
-      <c r="W59" s="21"/>
-      <c r="X59" s="21"/>
-      <c r="Y59" s="31"/>
-      <c r="Z59" s="31"/>
-      <c r="AA59" s="31"/>
-      <c r="AB59" s="31"/>
-      <c r="AC59" s="31"/>
-      <c r="AD59" s="31"/>
-      <c r="AE59" s="31"/>
-      <c r="AF59" s="31"/>
-      <c r="AG59" s="31"/>
-      <c r="AH59" s="31"/>
-      <c r="AI59" s="31"/>
-      <c r="AJ59" s="31"/>
+      <c r="B59" s="20"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="20"/>
+      <c r="I59" s="20"/>
+      <c r="J59" s="20"/>
+      <c r="K59" s="20"/>
+      <c r="L59" s="20"/>
+      <c r="M59" s="8"/>
+      <c r="N59" s="20"/>
+      <c r="O59" s="20"/>
+      <c r="P59" s="20"/>
+      <c r="Q59" s="20"/>
+      <c r="R59" s="20"/>
+      <c r="S59" s="20"/>
+      <c r="T59" s="20"/>
+      <c r="U59" s="20"/>
+      <c r="V59" s="20"/>
+      <c r="W59" s="20"/>
+      <c r="X59" s="20"/>
+      <c r="Y59" s="30"/>
+      <c r="Z59" s="30"/>
+      <c r="AA59" s="30"/>
+      <c r="AB59" s="30"/>
+      <c r="AC59" s="30"/>
+      <c r="AD59" s="30"/>
+      <c r="AE59" s="30"/>
+      <c r="AF59" s="30"/>
+      <c r="AG59" s="30"/>
+      <c r="AH59" s="30"/>
+      <c r="AI59" s="30"/>
+      <c r="AJ59" s="30"/>
     </row>
     <row r="60" spans="2:36" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B60" s="52"/>
-      <c r="C60" s="53" t="s">
+      <c r="B60" s="51"/>
+      <c r="C60" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="D60" s="53">
+      <c r="D60" s="52">
         <f t="shared" ref="D60:W60" si="7">D37</f>
         <v>2020</v>
       </c>
-      <c r="E60" s="53">
+      <c r="E60" s="52">
         <f t="shared" si="7"/>
         <v>2021</v>
       </c>
-      <c r="F60" s="53">
+      <c r="F60" s="52">
         <f t="shared" si="7"/>
         <v>2022</v>
       </c>
-      <c r="G60" s="53">
+      <c r="G60" s="52">
         <f t="shared" si="7"/>
         <v>2023</v>
       </c>
-      <c r="H60" s="53">
+      <c r="H60" s="52">
         <f t="shared" si="7"/>
         <v>2024</v>
       </c>
-      <c r="I60" s="53">
+      <c r="I60" s="52">
         <f t="shared" si="7"/>
         <v>2025</v>
       </c>
-      <c r="J60" s="53">
+      <c r="J60" s="52">
         <f t="shared" si="7"/>
         <v>2026</v>
       </c>
-      <c r="K60" s="53">
+      <c r="K60" s="52">
         <f t="shared" si="7"/>
         <v>2027</v>
       </c>
-      <c r="L60" s="53">
+      <c r="L60" s="52">
         <f t="shared" si="7"/>
         <v>2028</v>
       </c>
-      <c r="M60" s="53">
+      <c r="M60" s="52">
         <f t="shared" si="7"/>
         <v>2029</v>
       </c>
-      <c r="N60" s="53">
+      <c r="N60" s="52">
         <f t="shared" si="7"/>
         <v>2030</v>
       </c>
-      <c r="O60" s="53">
+      <c r="O60" s="52">
         <f t="shared" si="7"/>
         <v>2031</v>
       </c>
-      <c r="P60" s="53">
+      <c r="P60" s="52">
         <f t="shared" si="7"/>
         <v>2032</v>
       </c>
-      <c r="Q60" s="53">
+      <c r="Q60" s="52">
         <f t="shared" si="7"/>
         <v>2033</v>
       </c>
-      <c r="R60" s="53">
+      <c r="R60" s="52">
         <f t="shared" si="7"/>
         <v>2034</v>
       </c>
-      <c r="S60" s="53">
+      <c r="S60" s="52">
         <f t="shared" si="7"/>
         <v>2035</v>
       </c>
-      <c r="T60" s="53">
+      <c r="T60" s="52">
         <f t="shared" si="7"/>
         <v>2036</v>
       </c>
-      <c r="U60" s="53">
+      <c r="U60" s="52">
         <f t="shared" si="7"/>
         <v>2037</v>
       </c>
-      <c r="V60" s="53">
+      <c r="V60" s="52">
         <f t="shared" si="7"/>
         <v>2038</v>
       </c>
-      <c r="W60" s="53">
+      <c r="W60" s="52">
         <f t="shared" si="7"/>
         <v>2039</v>
       </c>
-      <c r="X60" s="53"/>
-      <c r="Y60" s="54"/>
-      <c r="Z60" s="54"/>
-      <c r="AA60" s="54"/>
-      <c r="AB60" s="54"/>
-      <c r="AC60" s="54"/>
-      <c r="AD60" s="54"/>
-      <c r="AE60" s="54"/>
-      <c r="AF60" s="54"/>
-      <c r="AG60" s="54"/>
-      <c r="AH60" s="54"/>
-      <c r="AI60" s="54"/>
-      <c r="AJ60" s="54"/>
+      <c r="X60" s="52"/>
+      <c r="Y60" s="53"/>
+      <c r="Z60" s="53"/>
+      <c r="AA60" s="53"/>
+      <c r="AB60" s="53"/>
+      <c r="AC60" s="53"/>
+      <c r="AD60" s="53"/>
+      <c r="AE60" s="53"/>
+      <c r="AF60" s="53"/>
+      <c r="AG60" s="53"/>
+      <c r="AH60" s="53"/>
+      <c r="AI60" s="53"/>
+      <c r="AJ60" s="53"/>
     </row>
     <row r="61" spans="2:36" ht="18.75" customHeight="1">
-      <c r="B61" s="22">
-        <v>0</v>
-      </c>
-      <c r="C61" s="23"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="25"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="26"/>
-      <c r="J61" s="26"/>
-      <c r="K61" s="26"/>
-      <c r="L61" s="26"/>
-      <c r="M61" s="26"/>
-      <c r="N61" s="26"/>
-      <c r="O61" s="26"/>
-      <c r="P61" s="26"/>
-      <c r="Q61" s="26"/>
-      <c r="R61" s="26"/>
-      <c r="S61" s="26"/>
-      <c r="T61" s="37" t="s">
+      <c r="B61" s="21">
+        <v>0</v>
+      </c>
+      <c r="C61" s="22"/>
+      <c r="D61" s="23"/>
+      <c r="E61" s="23"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="25"/>
+      <c r="J61" s="25"/>
+      <c r="K61" s="25"/>
+      <c r="L61" s="25"/>
+      <c r="M61" s="25"/>
+      <c r="N61" s="25"/>
+      <c r="O61" s="25"/>
+      <c r="P61" s="25"/>
+      <c r="Q61" s="25"/>
+      <c r="R61" s="25"/>
+      <c r="S61" s="25"/>
+      <c r="T61" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="U61" s="26"/>
-      <c r="V61" s="26"/>
-      <c r="W61" s="26"/>
-      <c r="X61" s="28"/>
+      <c r="U61" s="25"/>
+      <c r="V61" s="25"/>
+      <c r="W61" s="25"/>
+      <c r="X61" s="27"/>
     </row>
     <row r="62" spans="2:36" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B62" s="41" t="s">
+      <c r="B62" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C62" s="42">
-        <v>0</v>
-      </c>
-      <c r="D62" s="43">
+      <c r="C62" s="41">
+        <v>0</v>
+      </c>
+      <c r="D62" s="42">
         <v>1</v>
       </c>
-      <c r="E62" s="43">
+      <c r="E62" s="42">
         <v>2</v>
       </c>
-      <c r="F62" s="43">
+      <c r="F62" s="42">
         <v>3</v>
       </c>
-      <c r="G62" s="43">
+      <c r="G62" s="42">
         <v>4</v>
       </c>
-      <c r="H62" s="43">
+      <c r="H62" s="42">
         <v>5</v>
       </c>
-      <c r="I62" s="43">
+      <c r="I62" s="42">
         <v>6</v>
       </c>
-      <c r="J62" s="43">
+      <c r="J62" s="42">
         <v>7</v>
       </c>
-      <c r="K62" s="43">
+      <c r="K62" s="42">
         <v>8</v>
       </c>
-      <c r="L62" s="43">
+      <c r="L62" s="42">
         <v>9</v>
       </c>
-      <c r="M62" s="43">
+      <c r="M62" s="42">
         <v>10</v>
       </c>
-      <c r="N62" s="43">
+      <c r="N62" s="42">
         <v>11</v>
       </c>
-      <c r="O62" s="43">
+      <c r="O62" s="42">
         <v>12</v>
       </c>
-      <c r="P62" s="43">
+      <c r="P62" s="42">
         <v>13</v>
       </c>
-      <c r="Q62" s="43">
+      <c r="Q62" s="42">
         <v>14</v>
       </c>
-      <c r="R62" s="43">
+      <c r="R62" s="42">
         <v>15</v>
       </c>
-      <c r="S62" s="43">
+      <c r="S62" s="42">
         <v>16</v>
       </c>
-      <c r="T62" s="46">
+      <c r="T62" s="45">
         <v>17</v>
       </c>
-      <c r="U62" s="43">
+      <c r="U62" s="42">
         <v>18</v>
       </c>
-      <c r="V62" s="43">
+      <c r="V62" s="42">
         <v>19</v>
       </c>
-      <c r="W62" s="43">
+      <c r="W62" s="42">
         <v>20</v>
       </c>
-      <c r="X62" s="45"/>
+      <c r="X62" s="44"/>
     </row>
     <row r="63" spans="2:36" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B63" s="29" t="s">
+      <c r="B63" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C63" s="10">
-        <v>0</v>
-      </c>
-      <c r="D63" s="106">
+      <c r="C63" s="9">
+        <v>0</v>
+      </c>
+      <c r="D63" s="105">
         <f t="shared" ref="D63:W63" si="8">D40</f>
         <v>0</v>
       </c>
-      <c r="E63" s="106">
+      <c r="E63" s="105">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F63" s="106">
+      <c r="F63" s="105">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G63" s="106">
+      <c r="G63" s="105">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="H63" s="106">
+      <c r="H63" s="105">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I63" s="106">
+      <c r="I63" s="105">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="J63" s="106">
+      <c r="J63" s="105">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="K63" s="106">
+      <c r="K63" s="105">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L63" s="106">
+      <c r="L63" s="105">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="M63" s="106">
+      <c r="M63" s="105">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N63" s="106">
+      <c r="N63" s="105">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O63" s="106">
+      <c r="O63" s="105">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="P63" s="106">
+      <c r="P63" s="105">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q63" s="106">
+      <c r="Q63" s="105">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R63" s="106">
+      <c r="R63" s="105">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S63" s="106">
+      <c r="S63" s="105">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T63" s="106">
+      <c r="T63" s="105">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="U63" s="106">
+      <c r="U63" s="105">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V63" s="106">
+      <c r="V63" s="105">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W63" s="106">
+      <c r="W63" s="105">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X63" s="30"/>
-    </row>
-    <row r="64" spans="2:36" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B64" s="55" t="s">
+      <c r="X63" s="29"/>
+    </row>
+    <row r="64" spans="2:36" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B64" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="D64" s="105">
+      <c r="C64" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="D64" s="104">
         <f t="shared" ref="D64:W64" si="9">D41</f>
         <v>0</v>
       </c>
-      <c r="E64" s="105">
+      <c r="E64" s="104">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F64" s="105">
+      <c r="F64" s="104">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="G64" s="105">
+      <c r="G64" s="104">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H64" s="105">
+      <c r="H64" s="104">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="I64" s="105">
+      <c r="I64" s="104">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J64" s="105">
+      <c r="J64" s="104">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="K64" s="105">
+      <c r="K64" s="104">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="L64" s="105">
+      <c r="L64" s="104">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M64" s="105">
+      <c r="M64" s="104">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="N64" s="105">
+      <c r="N64" s="104">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="O64" s="105">
+      <c r="O64" s="104">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="P64" s="105">
+      <c r="P64" s="104">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q64" s="105">
+      <c r="Q64" s="104">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="R64" s="105">
+      <c r="R64" s="104">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="S64" s="105">
+      <c r="S64" s="104">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T64" s="105">
+      <c r="T64" s="104">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U64" s="105">
+      <c r="U64" s="104">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="V64" s="105">
+      <c r="V64" s="104">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="W64" s="105">
+      <c r="W64" s="104">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="X64" s="57"/>
-    </row>
-    <row r="65" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B65" s="59" t="s">
+      <c r="X64" s="56"/>
+    </row>
+    <row r="65" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B65" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="C65" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="D65" s="61"/>
-      <c r="E65" s="61"/>
-      <c r="F65" s="61"/>
-      <c r="G65" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="H65" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="I65" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="J65" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="K65" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="L65" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="M65" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="N65" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="O65" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="P65" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="R65" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="S65" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="T65" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="U65" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="V65" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="W65" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="X65" s="62"/>
-    </row>
-    <row r="66" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B66" s="63" t="s">
+      <c r="C65" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="D65" s="60"/>
+      <c r="E65" s="60"/>
+      <c r="F65" s="60"/>
+      <c r="G65" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="H65" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="I65" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="J65" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="K65" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="L65" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="M65" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="N65" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="O65" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="P65" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="R65" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="S65" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="T65" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="U65" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="V65" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="W65" s="60" t="s">
+        <v>0</v>
+      </c>
+      <c r="X65" s="61"/>
+    </row>
+    <row r="66" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
+      <c r="B66" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="C66" s="64"/>
-      <c r="D66" s="65"/>
-      <c r="E66" s="65"/>
-      <c r="F66" s="65"/>
-      <c r="G66" s="65"/>
-      <c r="H66" s="65"/>
-      <c r="I66" s="65"/>
-      <c r="J66" s="65"/>
-      <c r="K66" s="65"/>
-      <c r="L66" s="65"/>
-      <c r="M66" s="65"/>
-      <c r="N66" s="65"/>
-      <c r="O66" s="65"/>
-      <c r="P66" s="65"/>
-      <c r="Q66" s="65"/>
-      <c r="R66" s="65"/>
-      <c r="S66" s="65"/>
-      <c r="T66" s="65"/>
-      <c r="U66" s="65"/>
-      <c r="V66" s="65"/>
-      <c r="W66" s="65"/>
-      <c r="X66" s="66"/>
-    </row>
-    <row r="67" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B67" s="67" t="s">
+      <c r="C66" s="63"/>
+      <c r="D66" s="64"/>
+      <c r="E66" s="64"/>
+      <c r="F66" s="64"/>
+      <c r="G66" s="64"/>
+      <c r="H66" s="64"/>
+      <c r="I66" s="64"/>
+      <c r="J66" s="64"/>
+      <c r="K66" s="64"/>
+      <c r="L66" s="64"/>
+      <c r="M66" s="64"/>
+      <c r="N66" s="64"/>
+      <c r="O66" s="64"/>
+      <c r="P66" s="64"/>
+      <c r="Q66" s="64"/>
+      <c r="R66" s="64"/>
+      <c r="S66" s="64"/>
+      <c r="T66" s="64"/>
+      <c r="U66" s="64"/>
+      <c r="V66" s="64"/>
+      <c r="W66" s="64"/>
+      <c r="X66" s="65"/>
+    </row>
+    <row r="67" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B67" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="C67" s="60"/>
-      <c r="D67" s="107" t="e">
+      <c r="C67" s="59"/>
+      <c r="D67" s="106" t="e">
         <f>$C$44/$E$16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E67" s="107" t="e">
+      <c r="E67" s="106" t="e">
         <f t="shared" ref="E67:W67" si="10">$C$44/$E$16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F67" s="107" t="e">
+      <c r="F67" s="106" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G67" s="107" t="e">
+      <c r="G67" s="106" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H67" s="107" t="e">
+      <c r="H67" s="106" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I67" s="107" t="e">
+      <c r="I67" s="106" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J67" s="107" t="e">
+      <c r="J67" s="106" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K67" s="107" t="e">
+      <c r="K67" s="106" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L67" s="107" t="e">
+      <c r="L67" s="106" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M67" s="107" t="e">
+      <c r="M67" s="106" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N67" s="107" t="e">
+      <c r="N67" s="106" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O67" s="107" t="e">
+      <c r="O67" s="106" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P67" s="107" t="e">
+      <c r="P67" s="106" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q67" s="107" t="e">
+      <c r="Q67" s="106" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R67" s="107" t="e">
+      <c r="R67" s="106" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S67" s="107" t="e">
+      <c r="S67" s="106" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T67" s="107" t="e">
+      <c r="T67" s="106" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U67" s="107" t="e">
+      <c r="U67" s="106" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V67" s="107" t="e">
+      <c r="V67" s="106" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W67" s="107" t="e">
+      <c r="W67" s="106" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X67" s="62"/>
-    </row>
-    <row r="68" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B68" s="67" t="s">
+      <c r="X67" s="61"/>
+    </row>
+    <row r="68" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B68" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="C68" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="D68" s="100">
+      <c r="C68" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="D68" s="99">
         <f>D44</f>
         <v>0</v>
       </c>
-      <c r="E68" s="100">
+      <c r="E68" s="99">
         <f t="shared" ref="E68:W68" si="11">E44</f>
         <v>0</v>
       </c>
-      <c r="F68" s="100">
+      <c r="F68" s="99">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G68" s="100">
+      <c r="G68" s="99">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="H68" s="100">
+      <c r="H68" s="99">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I68" s="100">
+      <c r="I68" s="99">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J68" s="100">
+      <c r="J68" s="99">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="K68" s="100">
+      <c r="K68" s="99">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="L68" s="100">
+      <c r="L68" s="99">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="M68" s="100">
+      <c r="M68" s="99">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="N68" s="100">
+      <c r="N68" s="99">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="O68" s="100">
+      <c r="O68" s="99">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P68" s="100">
+      <c r="P68" s="99">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q68" s="100">
+      <c r="Q68" s="99">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="R68" s="100">
+      <c r="R68" s="99">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S68" s="100">
+      <c r="S68" s="99">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="T68" s="100">
+      <c r="T68" s="99">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="U68" s="100">
+      <c r="U68" s="99">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="V68" s="100">
+      <c r="V68" s="99">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="W68" s="100">
+      <c r="W68" s="99">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="X68" s="62"/>
-    </row>
-    <row r="69" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B69" s="67" t="s">
+      <c r="X68" s="61"/>
+    </row>
+    <row r="69" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B69" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="C69" s="60"/>
-      <c r="D69" s="61"/>
-      <c r="E69" s="61"/>
-      <c r="F69" s="61"/>
-      <c r="G69" s="61"/>
-      <c r="H69" s="61"/>
-      <c r="I69" s="61"/>
-      <c r="J69" s="61"/>
-      <c r="K69" s="61"/>
-      <c r="L69" s="61"/>
-      <c r="M69" s="61"/>
-      <c r="N69" s="61"/>
-      <c r="O69" s="61"/>
-      <c r="P69" s="61"/>
-      <c r="Q69" s="61"/>
-      <c r="R69" s="61"/>
-      <c r="S69" s="61"/>
-      <c r="T69" s="61"/>
-      <c r="U69" s="61"/>
-      <c r="V69" s="61"/>
-      <c r="W69" s="61"/>
-      <c r="X69" s="62"/>
-    </row>
-    <row r="70" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B70" s="67" t="s">
+      <c r="C69" s="59"/>
+      <c r="D69" s="60"/>
+      <c r="E69" s="60"/>
+      <c r="F69" s="60"/>
+      <c r="G69" s="60"/>
+      <c r="H69" s="60"/>
+      <c r="I69" s="60"/>
+      <c r="J69" s="60"/>
+      <c r="K69" s="60"/>
+      <c r="L69" s="60"/>
+      <c r="M69" s="60"/>
+      <c r="N69" s="60"/>
+      <c r="O69" s="60"/>
+      <c r="P69" s="60"/>
+      <c r="Q69" s="60"/>
+      <c r="R69" s="60"/>
+      <c r="S69" s="60"/>
+      <c r="T69" s="60"/>
+      <c r="U69" s="60"/>
+      <c r="V69" s="60"/>
+      <c r="W69" s="60"/>
+      <c r="X69" s="61"/>
+    </row>
+    <row r="70" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B70" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="C70" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="D70" s="100">
+      <c r="C70" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="D70" s="99">
         <f>-D109*$D25</f>
         <v>0</v>
       </c>
-      <c r="E70" s="100">
+      <c r="E70" s="99">
         <f t="shared" ref="E70:W70" si="12">-E109*$D25</f>
         <v>0</v>
       </c>
-      <c r="F70" s="100">
+      <c r="F70" s="99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="G70" s="100">
+      <c r="G70" s="99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H70" s="100">
+      <c r="H70" s="99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I70" s="100">
+      <c r="I70" s="99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="J70" s="100">
+      <c r="J70" s="99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K70" s="100">
+      <c r="K70" s="99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L70" s="100">
+      <c r="L70" s="99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="M70" s="100">
+      <c r="M70" s="99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="N70" s="100">
+      <c r="N70" s="99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="O70" s="100">
+      <c r="O70" s="99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="P70" s="100">
+      <c r="P70" s="99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Q70" s="100">
+      <c r="Q70" s="99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="R70" s="100">
+      <c r="R70" s="99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="S70" s="100">
+      <c r="S70" s="99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="T70" s="100">
+      <c r="T70" s="99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="U70" s="100">
+      <c r="U70" s="99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="V70" s="100">
+      <c r="V70" s="99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="W70" s="100">
+      <c r="W70" s="99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="X70" s="62"/>
-    </row>
-    <row r="71" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B71" s="67" t="s">
+      <c r="X70" s="61"/>
+    </row>
+    <row r="71" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B71" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="C71" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="D71" s="100">
+      <c r="C71" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="D71" s="99">
         <f t="shared" ref="D71:W71" si="13">D48</f>
         <v>0</v>
       </c>
-      <c r="E71" s="100">
+      <c r="E71" s="99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F71" s="100">
+      <c r="F71" s="99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="G71" s="100">
+      <c r="G71" s="99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="H71" s="100">
+      <c r="H71" s="99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I71" s="100">
+      <c r="I71" s="99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="J71" s="100">
+      <c r="J71" s="99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="K71" s="100">
+      <c r="K71" s="99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L71" s="100">
+      <c r="L71" s="99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M71" s="100">
+      <c r="M71" s="99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="N71" s="100">
+      <c r="N71" s="99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="O71" s="100">
+      <c r="O71" s="99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="P71" s="100">
+      <c r="P71" s="99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Q71" s="100">
+      <c r="Q71" s="99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="R71" s="100">
+      <c r="R71" s="99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S71" s="100">
+      <c r="S71" s="99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="T71" s="100">
+      <c r="T71" s="99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U71" s="100">
+      <c r="U71" s="99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V71" s="100">
+      <c r="V71" s="99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="W71" s="100">
+      <c r="W71" s="99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="X71" s="62"/>
-    </row>
-    <row r="72" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B72" s="67" t="s">
+      <c r="X71" s="61"/>
+    </row>
+    <row r="72" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B72" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="C72" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="D72" s="100">
+      <c r="C72" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="D72" s="99">
         <f t="shared" ref="D72:W72" si="14">D49</f>
         <v>0</v>
       </c>
-      <c r="E72" s="100">
+      <c r="E72" s="99">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="F72" s="100">
+      <c r="F72" s="99">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G72" s="100">
+      <c r="G72" s="99">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H72" s="100">
+      <c r="H72" s="99">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I72" s="100">
+      <c r="I72" s="99">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J72" s="100">
+      <c r="J72" s="99">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K72" s="100">
+      <c r="K72" s="99">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="L72" s="100">
+      <c r="L72" s="99">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M72" s="100">
+      <c r="M72" s="99">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="N72" s="100">
+      <c r="N72" s="99">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="O72" s="100">
+      <c r="O72" s="99">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="P72" s="100">
+      <c r="P72" s="99">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="Q72" s="100">
+      <c r="Q72" s="99">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="R72" s="100">
+      <c r="R72" s="99">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="S72" s="100">
+      <c r="S72" s="99">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="T72" s="100">
+      <c r="T72" s="99">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="U72" s="100">
+      <c r="U72" s="99">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="V72" s="100">
+      <c r="V72" s="99">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="W72" s="100">
+      <c r="W72" s="99">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="X72" s="62"/>
-    </row>
-    <row r="73" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B73" s="67" t="s">
+      <c r="X72" s="61"/>
+    </row>
+    <row r="73" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B73" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="C73" s="60"/>
-      <c r="D73" s="100">
+      <c r="C73" s="59"/>
+      <c r="D73" s="99">
         <f t="shared" ref="D73:W73" si="15">D50</f>
         <v>0</v>
       </c>
-      <c r="E73" s="100">
+      <c r="E73" s="99">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="F73" s="100">
+      <c r="F73" s="99">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="G73" s="100">
+      <c r="G73" s="99">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H73" s="100">
+      <c r="H73" s="99">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I73" s="100">
+      <c r="I73" s="99">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="J73" s="100">
+      <c r="J73" s="99">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="K73" s="100">
+      <c r="K73" s="99">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L73" s="100">
+      <c r="L73" s="99">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="M73" s="100">
+      <c r="M73" s="99">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N73" s="100">
+      <c r="N73" s="99">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="O73" s="100">
+      <c r="O73" s="99">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="P73" s="100">
+      <c r="P73" s="99">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Q73" s="100">
+      <c r="Q73" s="99">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="R73" s="100">
+      <c r="R73" s="99">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="S73" s="100">
+      <c r="S73" s="99">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="T73" s="100">
+      <c r="T73" s="99">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="U73" s="100">
+      <c r="U73" s="99">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="V73" s="100">
+      <c r="V73" s="99">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="W73" s="100">
+      <c r="W73" s="99">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="X73" s="62"/>
-    </row>
-    <row r="74" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B74" s="67" t="s">
+      <c r="X73" s="61"/>
+    </row>
+    <row r="74" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B74" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="C74" s="68"/>
-      <c r="D74" s="69"/>
-      <c r="E74" s="70"/>
-      <c r="F74" s="61"/>
-      <c r="G74" s="61"/>
-      <c r="H74" s="61"/>
-      <c r="I74" s="61"/>
-      <c r="J74" s="61"/>
-      <c r="K74" s="61"/>
-      <c r="L74" s="61"/>
-      <c r="M74" s="61"/>
-      <c r="N74" s="61"/>
-      <c r="O74" s="61"/>
-      <c r="P74" s="61"/>
-      <c r="Q74" s="61"/>
-      <c r="R74" s="61"/>
-      <c r="S74" s="61"/>
-      <c r="T74" s="61"/>
-      <c r="U74" s="61"/>
-      <c r="V74" s="61"/>
-      <c r="W74" s="61"/>
-      <c r="X74" s="62"/>
-    </row>
-    <row r="75" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B75" s="67" t="s">
+      <c r="C74" s="67"/>
+      <c r="D74" s="68"/>
+      <c r="E74" s="69"/>
+      <c r="F74" s="60"/>
+      <c r="G74" s="60"/>
+      <c r="H74" s="60"/>
+      <c r="I74" s="60"/>
+      <c r="J74" s="60"/>
+      <c r="K74" s="60"/>
+      <c r="L74" s="60"/>
+      <c r="M74" s="60"/>
+      <c r="N74" s="60"/>
+      <c r="O74" s="60"/>
+      <c r="P74" s="60"/>
+      <c r="Q74" s="60"/>
+      <c r="R74" s="60"/>
+      <c r="S74" s="60"/>
+      <c r="T74" s="60"/>
+      <c r="U74" s="60"/>
+      <c r="V74" s="60"/>
+      <c r="W74" s="60"/>
+      <c r="X74" s="61"/>
+    </row>
+    <row r="75" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
+      <c r="B75" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C75" s="68"/>
-      <c r="D75" s="61"/>
-      <c r="E75" s="61"/>
-      <c r="F75" s="61"/>
-      <c r="G75" s="61"/>
-      <c r="H75" s="61"/>
-      <c r="I75" s="61"/>
-      <c r="J75" s="61"/>
-      <c r="K75" s="61"/>
-      <c r="L75" s="61"/>
-      <c r="M75" s="61"/>
-      <c r="N75" s="61"/>
-      <c r="O75" s="61"/>
-      <c r="P75" s="61"/>
-      <c r="Q75" s="61"/>
-      <c r="R75" s="61"/>
-      <c r="S75" s="61"/>
-      <c r="T75" s="61"/>
-      <c r="U75" s="61"/>
-      <c r="V75" s="61"/>
-      <c r="W75" s="61"/>
-      <c r="X75" s="62"/>
-    </row>
-    <row r="76" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B76" s="72" t="s">
+      <c r="C75" s="67"/>
+      <c r="D75" s="60"/>
+      <c r="E75" s="60"/>
+      <c r="F75" s="60"/>
+      <c r="G75" s="60"/>
+      <c r="H75" s="60"/>
+      <c r="I75" s="60"/>
+      <c r="J75" s="60"/>
+      <c r="K75" s="60"/>
+      <c r="L75" s="60"/>
+      <c r="M75" s="60"/>
+      <c r="N75" s="60"/>
+      <c r="O75" s="60"/>
+      <c r="P75" s="60"/>
+      <c r="Q75" s="60"/>
+      <c r="R75" s="60"/>
+      <c r="S75" s="60"/>
+      <c r="T75" s="60"/>
+      <c r="U75" s="60"/>
+      <c r="V75" s="60"/>
+      <c r="W75" s="60"/>
+      <c r="X75" s="61"/>
+    </row>
+    <row r="76" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B76" s="71" t="s">
         <v>94</v>
       </c>
-      <c r="C76" s="83"/>
-      <c r="D76" s="101" t="e">
+      <c r="C76" s="82"/>
+      <c r="D76" s="100" t="e">
         <f>SUM(D64:D75)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E76" s="101" t="e">
+      <c r="E76" s="100" t="e">
         <f t="shared" ref="E76:W76" si="16">SUM(E64:E75)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F76" s="101" t="e">
+      <c r="F76" s="100" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G76" s="101" t="e">
+      <c r="G76" s="100" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H76" s="101" t="e">
+      <c r="H76" s="100" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I76" s="101" t="e">
+      <c r="I76" s="100" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J76" s="101" t="e">
+      <c r="J76" s="100" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K76" s="101" t="e">
+      <c r="K76" s="100" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L76" s="101" t="e">
+      <c r="L76" s="100" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M76" s="101" t="e">
+      <c r="M76" s="100" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N76" s="101" t="e">
+      <c r="N76" s="100" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O76" s="101" t="e">
+      <c r="O76" s="100" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P76" s="101" t="e">
+      <c r="P76" s="100" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q76" s="101" t="e">
+      <c r="Q76" s="100" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R76" s="101" t="e">
+      <c r="R76" s="100" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S76" s="101" t="e">
+      <c r="S76" s="100" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T76" s="101" t="e">
+      <c r="T76" s="100" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U76" s="101" t="e">
+      <c r="U76" s="100" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V76" s="101" t="e">
+      <c r="V76" s="100" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W76" s="101" t="e">
+      <c r="W76" s="100" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X76" s="101">
+      <c r="X76" s="100">
         <f t="shared" ref="X76" si="17">SUM(X64:X75)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B77" s="71" t="s">
+    <row r="77" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B77" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="C77" s="68"/>
-      <c r="D77" s="100" t="e">
+      <c r="C77" s="67"/>
+      <c r="D77" s="99" t="e">
         <f>-D76*0.2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E77" s="100" t="e">
+      <c r="E77" s="99" t="e">
         <f t="shared" ref="E77:W77" si="18">-E76*0.2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F77" s="100" t="e">
+      <c r="F77" s="99" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G77" s="100" t="e">
+      <c r="G77" s="99" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H77" s="100" t="e">
+      <c r="H77" s="99" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I77" s="100" t="e">
+      <c r="I77" s="99" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J77" s="100" t="e">
+      <c r="J77" s="99" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K77" s="100" t="e">
+      <c r="K77" s="99" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L77" s="100" t="e">
+      <c r="L77" s="99" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M77" s="100" t="e">
+      <c r="M77" s="99" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N77" s="100" t="e">
+      <c r="N77" s="99" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O77" s="100" t="e">
+      <c r="O77" s="99" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P77" s="100" t="e">
+      <c r="P77" s="99" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q77" s="100" t="e">
+      <c r="Q77" s="99" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R77" s="100" t="e">
+      <c r="R77" s="99" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S77" s="100" t="e">
+      <c r="S77" s="99" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T77" s="100" t="e">
+      <c r="T77" s="99" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U77" s="100" t="e">
+      <c r="U77" s="99" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V77" s="100" t="e">
+      <c r="V77" s="99" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W77" s="100" t="e">
+      <c r="W77" s="99" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X77" s="100">
+      <c r="X77" s="99">
         <f t="shared" ref="X77" si="19">-X76*0.2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:24" s="58" customFormat="1">
-      <c r="B78" s="84" t="s">
+    <row r="78" spans="2:24" s="57" customFormat="1">
+      <c r="B78" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="D78" s="108" t="e">
+      <c r="D78" s="107" t="e">
         <f>SUM(D76:D77)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E78" s="108" t="e">
+      <c r="E78" s="107" t="e">
         <f t="shared" ref="E78:W78" si="20">SUM(E76:E77)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F78" s="108" t="e">
+      <c r="F78" s="107" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G78" s="108" t="e">
+      <c r="G78" s="107" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H78" s="108" t="e">
+      <c r="H78" s="107" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I78" s="108" t="e">
+      <c r="I78" s="107" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J78" s="108" t="e">
+      <c r="J78" s="107" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K78" s="108" t="e">
+      <c r="K78" s="107" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L78" s="108" t="e">
+      <c r="L78" s="107" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M78" s="108" t="e">
+      <c r="M78" s="107" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N78" s="108" t="e">
+      <c r="N78" s="107" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O78" s="108" t="e">
+      <c r="O78" s="107" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P78" s="108" t="e">
+      <c r="P78" s="107" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q78" s="108" t="e">
+      <c r="Q78" s="107" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R78" s="108" t="e">
+      <c r="R78" s="107" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S78" s="108" t="e">
+      <c r="S78" s="107" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T78" s="108" t="e">
+      <c r="T78" s="107" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U78" s="108" t="e">
+      <c r="U78" s="107" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V78" s="108" t="e">
+      <c r="V78" s="107" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W78" s="108" t="e">
+      <c r="W78" s="107" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X78" s="108">
+      <c r="X78" s="107">
         <f t="shared" ref="X78" si="21">SUM(X76:X77)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:24" s="58" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B79" s="77" t="s">
+    <row r="79" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
+      <c r="B79" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="C79" s="73"/>
-      <c r="D79" s="78"/>
-      <c r="E79" s="78"/>
-      <c r="F79" s="78"/>
-      <c r="G79" s="78"/>
-      <c r="H79" s="78"/>
-      <c r="I79" s="78"/>
-      <c r="J79" s="78"/>
-      <c r="K79" s="78"/>
-      <c r="L79" s="78"/>
-      <c r="M79" s="78"/>
-      <c r="N79" s="78"/>
-      <c r="O79" s="78"/>
-      <c r="P79" s="78"/>
-      <c r="Q79" s="78"/>
-      <c r="R79" s="78"/>
-      <c r="S79" s="78"/>
-      <c r="T79" s="78"/>
-      <c r="U79" s="78"/>
-      <c r="V79" s="78"/>
-      <c r="W79" s="78"/>
-      <c r="X79" s="85"/>
+      <c r="C79" s="72"/>
+      <c r="D79" s="77"/>
+      <c r="E79" s="77"/>
+      <c r="F79" s="77"/>
+      <c r="G79" s="77"/>
+      <c r="H79" s="77"/>
+      <c r="I79" s="77"/>
+      <c r="J79" s="77"/>
+      <c r="K79" s="77"/>
+      <c r="L79" s="77"/>
+      <c r="M79" s="77"/>
+      <c r="N79" s="77"/>
+      <c r="O79" s="77"/>
+      <c r="P79" s="77"/>
+      <c r="Q79" s="77"/>
+      <c r="R79" s="77"/>
+      <c r="S79" s="77"/>
+      <c r="T79" s="77"/>
+      <c r="U79" s="77"/>
+      <c r="V79" s="77"/>
+      <c r="W79" s="77"/>
+      <c r="X79" s="84"/>
     </row>
     <row r="80" spans="2:24" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B80" s="33" t="s">
+      <c r="B80" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C80" s="34"/>
-      <c r="D80" s="35"/>
-      <c r="E80" s="35"/>
-      <c r="F80" s="35"/>
-      <c r="G80" s="35"/>
-      <c r="H80" s="35"/>
-      <c r="I80" s="35"/>
-      <c r="J80" s="35"/>
-      <c r="K80" s="35"/>
-      <c r="L80" s="35"/>
-      <c r="M80" s="35"/>
-      <c r="N80" s="35"/>
-      <c r="O80" s="35"/>
-      <c r="P80" s="35"/>
-      <c r="Q80" s="35"/>
-      <c r="R80" s="35"/>
-      <c r="S80" s="35"/>
-      <c r="T80" s="35"/>
-      <c r="U80" s="35"/>
-      <c r="V80" s="35"/>
-      <c r="W80" s="35"/>
-      <c r="X80" s="38"/>
+      <c r="C80" s="33"/>
+      <c r="D80" s="34"/>
+      <c r="E80" s="34"/>
+      <c r="F80" s="34"/>
+      <c r="G80" s="34"/>
+      <c r="H80" s="34"/>
+      <c r="I80" s="34"/>
+      <c r="J80" s="34"/>
+      <c r="K80" s="34"/>
+      <c r="L80" s="34"/>
+      <c r="M80" s="34"/>
+      <c r="N80" s="34"/>
+      <c r="O80" s="34"/>
+      <c r="P80" s="34"/>
+      <c r="Q80" s="34"/>
+      <c r="R80" s="34"/>
+      <c r="S80" s="34"/>
+      <c r="T80" s="34"/>
+      <c r="U80" s="34"/>
+      <c r="V80" s="34"/>
+      <c r="W80" s="34"/>
+      <c r="X80" s="37"/>
     </row>
     <row r="81" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B81" s="21"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="21"/>
-      <c r="G81" s="21"/>
-      <c r="H81" s="21"/>
-      <c r="I81" s="21"/>
-      <c r="J81" s="21"/>
-      <c r="K81" s="21"/>
-      <c r="L81" s="21"/>
-      <c r="M81" s="9"/>
-      <c r="N81" s="21"/>
-      <c r="O81" s="21"/>
-      <c r="P81" s="21"/>
-      <c r="Q81" s="21"/>
-      <c r="R81" s="21"/>
-      <c r="S81" s="21"/>
-      <c r="T81" s="21"/>
-      <c r="U81" s="21"/>
-      <c r="V81" s="21"/>
-      <c r="W81" s="21"/>
-      <c r="X81" s="21"/>
+      <c r="B81" s="20"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="20"/>
+      <c r="G81" s="20"/>
+      <c r="H81" s="20"/>
+      <c r="I81" s="20"/>
+      <c r="J81" s="20"/>
+      <c r="K81" s="20"/>
+      <c r="L81" s="20"/>
+      <c r="M81" s="8"/>
+      <c r="N81" s="20"/>
+      <c r="O81" s="20"/>
+      <c r="P81" s="20"/>
+      <c r="Q81" s="20"/>
+      <c r="R81" s="20"/>
+      <c r="S81" s="20"/>
+      <c r="T81" s="20"/>
+      <c r="U81" s="20"/>
+      <c r="V81" s="20"/>
+      <c r="W81" s="20"/>
+      <c r="X81" s="20"/>
     </row>
     <row r="82" spans="2:25" customFormat="1" ht="18.75" customHeight="1">
-      <c r="C82" s="49" t="s">
+      <c r="C82" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="D82" s="50">
+      <c r="D82" s="49">
         <f t="shared" ref="D82:W82" si="22">D37</f>
         <v>2020</v>
       </c>
-      <c r="E82" s="50">
+      <c r="E82" s="49">
         <f t="shared" si="22"/>
         <v>2021</v>
       </c>
-      <c r="F82" s="50">
+      <c r="F82" s="49">
         <f t="shared" si="22"/>
         <v>2022</v>
       </c>
-      <c r="G82" s="50">
+      <c r="G82" s="49">
         <f t="shared" si="22"/>
         <v>2023</v>
       </c>
-      <c r="H82" s="50">
+      <c r="H82" s="49">
         <f t="shared" si="22"/>
         <v>2024</v>
       </c>
-      <c r="I82" s="50">
+      <c r="I82" s="49">
         <f t="shared" si="22"/>
         <v>2025</v>
       </c>
-      <c r="J82" s="50">
+      <c r="J82" s="49">
         <f t="shared" si="22"/>
         <v>2026</v>
       </c>
-      <c r="K82" s="50">
+      <c r="K82" s="49">
         <f t="shared" si="22"/>
         <v>2027</v>
       </c>
-      <c r="L82" s="50">
+      <c r="L82" s="49">
         <f t="shared" si="22"/>
         <v>2028</v>
       </c>
-      <c r="M82" s="50">
+      <c r="M82" s="49">
         <f t="shared" si="22"/>
         <v>2029</v>
       </c>
-      <c r="N82" s="50">
+      <c r="N82" s="49">
         <f t="shared" si="22"/>
         <v>2030</v>
       </c>
-      <c r="O82" s="50">
+      <c r="O82" s="49">
         <f t="shared" si="22"/>
         <v>2031</v>
       </c>
-      <c r="P82" s="50">
+      <c r="P82" s="49">
         <f t="shared" si="22"/>
         <v>2032</v>
       </c>
-      <c r="Q82" s="50">
+      <c r="Q82" s="49">
         <f t="shared" si="22"/>
         <v>2033</v>
       </c>
-      <c r="R82" s="50">
+      <c r="R82" s="49">
         <f t="shared" si="22"/>
         <v>2034</v>
       </c>
-      <c r="S82" s="50">
+      <c r="S82" s="49">
         <f t="shared" si="22"/>
         <v>2035</v>
       </c>
-      <c r="T82" s="50">
+      <c r="T82" s="49">
         <f t="shared" si="22"/>
         <v>2036</v>
       </c>
-      <c r="U82" s="50">
+      <c r="U82" s="49">
         <f t="shared" si="22"/>
         <v>2037</v>
       </c>
-      <c r="V82" s="50">
+      <c r="V82" s="49">
         <f t="shared" si="22"/>
         <v>2038</v>
       </c>
-      <c r="W82" s="50">
+      <c r="W82" s="49">
         <f t="shared" si="22"/>
         <v>2039</v>
       </c>
-      <c r="X82" s="51"/>
+      <c r="X82" s="50"/>
     </row>
     <row r="83" spans="2:25" ht="18.75" customHeight="1">
-      <c r="X83" s="39"/>
+      <c r="X83" s="38"/>
     </row>
     <row r="84" spans="2:25" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B84" s="47" t="s">
+      <c r="B84" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="C84" s="47">
-        <v>0</v>
-      </c>
-      <c r="D84" s="47">
+      <c r="C84" s="46">
+        <v>0</v>
+      </c>
+      <c r="D84" s="46">
         <v>1</v>
       </c>
-      <c r="E84" s="47">
+      <c r="E84" s="46">
         <v>2</v>
       </c>
-      <c r="F84" s="47">
+      <c r="F84" s="46">
         <v>3</v>
       </c>
-      <c r="G84" s="47">
+      <c r="G84" s="46">
         <v>4</v>
       </c>
-      <c r="H84" s="47">
+      <c r="H84" s="46">
         <v>5</v>
       </c>
-      <c r="I84" s="47">
+      <c r="I84" s="46">
         <v>6</v>
       </c>
-      <c r="J84" s="47">
+      <c r="J84" s="46">
         <v>7</v>
       </c>
-      <c r="K84" s="47">
+      <c r="K84" s="46">
         <v>8</v>
       </c>
-      <c r="L84" s="47">
+      <c r="L84" s="46">
         <v>9</v>
       </c>
-      <c r="M84" s="47">
+      <c r="M84" s="46">
         <v>10</v>
       </c>
-      <c r="N84" s="47">
+      <c r="N84" s="46">
         <v>11</v>
       </c>
-      <c r="O84" s="47">
+      <c r="O84" s="46">
         <v>12</v>
       </c>
-      <c r="P84" s="47">
+      <c r="P84" s="46">
         <v>13</v>
       </c>
-      <c r="Q84" s="47">
+      <c r="Q84" s="46">
         <v>14</v>
       </c>
-      <c r="R84" s="47">
+      <c r="R84" s="46">
         <v>15</v>
       </c>
-      <c r="S84" s="47">
+      <c r="S84" s="46">
         <v>16</v>
       </c>
-      <c r="T84" s="47">
+      <c r="T84" s="46">
         <v>17</v>
       </c>
-      <c r="U84" s="47">
+      <c r="U84" s="46">
         <v>18</v>
       </c>
-      <c r="V84" s="47">
+      <c r="V84" s="46">
         <v>19</v>
       </c>
-      <c r="W84" s="47">
+      <c r="W84" s="46">
         <v>20</v>
       </c>
-      <c r="X84" s="48"/>
-    </row>
-    <row r="85" spans="2:25" s="58" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B85" s="86" t="s">
+      <c r="X84" s="47"/>
+    </row>
+    <row r="85" spans="2:25" s="57" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B85" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="C85" s="86"/>
-      <c r="D85" s="109" t="e">
+      <c r="C85" s="85"/>
+      <c r="D85" s="108" t="e">
         <f>D78</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E85" s="109" t="e">
+      <c r="E85" s="108" t="e">
         <f t="shared" ref="E85:W85" si="23">E78</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F85" s="109" t="e">
+      <c r="F85" s="108" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G85" s="109" t="e">
+      <c r="G85" s="108" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H85" s="109" t="e">
+      <c r="H85" s="108" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I85" s="109" t="e">
+      <c r="I85" s="108" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J85" s="109" t="e">
+      <c r="J85" s="108" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K85" s="109" t="e">
+      <c r="K85" s="108" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L85" s="109" t="e">
+      <c r="L85" s="108" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M85" s="109" t="e">
+      <c r="M85" s="108" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N85" s="109" t="e">
+      <c r="N85" s="108" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O85" s="109" t="e">
+      <c r="O85" s="108" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P85" s="109" t="e">
+      <c r="P85" s="108" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q85" s="109" t="e">
+      <c r="Q85" s="108" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R85" s="109" t="e">
+      <c r="R85" s="108" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S85" s="109" t="e">
+      <c r="S85" s="108" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T85" s="109" t="e">
+      <c r="T85" s="108" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U85" s="109" t="e">
+      <c r="U85" s="108" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V85" s="109" t="e">
+      <c r="V85" s="108" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W85" s="109" t="e">
+      <c r="W85" s="108" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X85" s="86"/>
-      <c r="Y85" s="86"/>
-    </row>
-    <row r="86" spans="2:25" s="58" customFormat="1">
-      <c r="B86" s="86" t="s">
+      <c r="X85" s="85"/>
+      <c r="Y85" s="85"/>
+    </row>
+    <row r="86" spans="2:25" s="57" customFormat="1">
+      <c r="B86" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="C86" s="86"/>
-      <c r="D86" s="110" t="e">
+      <c r="C86" s="85"/>
+      <c r="D86" s="109" t="e">
         <f>-D67</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E86" s="110" t="e">
+      <c r="E86" s="109" t="e">
         <f t="shared" ref="E86:W86" si="24">-E67</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F86" s="110" t="e">
+      <c r="F86" s="109" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G86" s="110" t="e">
+      <c r="G86" s="109" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H86" s="110" t="e">
+      <c r="H86" s="109" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I86" s="110" t="e">
+      <c r="I86" s="109" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J86" s="110" t="e">
+      <c r="J86" s="109" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K86" s="110" t="e">
+      <c r="K86" s="109" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L86" s="110" t="e">
+      <c r="L86" s="109" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M86" s="110" t="e">
+      <c r="M86" s="109" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N86" s="110" t="e">
+      <c r="N86" s="109" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O86" s="110" t="e">
+      <c r="O86" s="109" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P86" s="110" t="e">
+      <c r="P86" s="109" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q86" s="110" t="e">
+      <c r="Q86" s="109" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R86" s="110" t="e">
+      <c r="R86" s="109" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S86" s="110" t="e">
+      <c r="S86" s="109" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T86" s="110" t="e">
+      <c r="T86" s="109" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U86" s="110" t="e">
+      <c r="U86" s="109" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V86" s="110" t="e">
+      <c r="V86" s="109" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W86" s="110" t="e">
+      <c r="W86" s="109" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X86" s="111"/>
-      <c r="Y86" s="111"/>
-    </row>
-    <row r="87" spans="2:25" s="58" customFormat="1">
-      <c r="B87" s="86" t="s">
+      <c r="X86" s="110"/>
+      <c r="Y86" s="110"/>
+    </row>
+    <row r="87" spans="2:25" s="57" customFormat="1">
+      <c r="B87" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="C87" s="86"/>
-      <c r="D87" s="112" t="e">
+      <c r="C87" s="85"/>
+      <c r="D87" s="111" t="e">
         <f>SUM(D85:D86)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E87" s="112" t="e">
+      <c r="E87" s="111" t="e">
         <f t="shared" ref="E87:W87" si="25">SUM(E85:E86)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F87" s="112" t="e">
+      <c r="F87" s="111" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G87" s="112" t="e">
+      <c r="G87" s="111" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H87" s="112" t="e">
+      <c r="H87" s="111" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I87" s="112" t="e">
+      <c r="I87" s="111" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J87" s="112" t="e">
+      <c r="J87" s="111" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K87" s="112" t="e">
+      <c r="K87" s="111" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L87" s="112" t="e">
+      <c r="L87" s="111" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M87" s="112" t="e">
+      <c r="M87" s="111" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N87" s="112" t="e">
+      <c r="N87" s="111" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O87" s="112" t="e">
+      <c r="O87" s="111" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P87" s="112" t="e">
+      <c r="P87" s="111" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q87" s="112" t="e">
+      <c r="Q87" s="111" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R87" s="112" t="e">
+      <c r="R87" s="111" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S87" s="112" t="e">
+      <c r="S87" s="111" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T87" s="112" t="e">
+      <c r="T87" s="111" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U87" s="112" t="e">
+      <c r="U87" s="111" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V87" s="112" t="e">
+      <c r="V87" s="111" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W87" s="112" t="e">
+      <c r="W87" s="111" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X87" s="87"/>
-    </row>
-    <row r="88" spans="2:25" s="58" customFormat="1">
-      <c r="B88" s="86"/>
-      <c r="C88" s="86"/>
-      <c r="D88" s="86"/>
-      <c r="E88" s="86"/>
-      <c r="F88" s="88"/>
-      <c r="G88" s="88"/>
-      <c r="H88" s="88"/>
-      <c r="I88" s="88"/>
-      <c r="J88" s="88"/>
-      <c r="K88" s="88"/>
-      <c r="L88" s="88"/>
-      <c r="M88" s="88"/>
-      <c r="N88" s="88"/>
-      <c r="O88" s="88"/>
-      <c r="P88" s="88"/>
-      <c r="Q88" s="88"/>
-      <c r="R88" s="88"/>
-      <c r="S88" s="88"/>
-      <c r="T88" s="88"/>
-      <c r="U88" s="88"/>
-      <c r="V88" s="88"/>
-      <c r="W88" s="88"/>
-      <c r="X88" s="89"/>
-    </row>
-    <row r="89" spans="2:25" s="58" customFormat="1">
-      <c r="B89" s="90" t="s">
+      <c r="X87" s="86"/>
+    </row>
+    <row r="88" spans="2:25" s="57" customFormat="1">
+      <c r="B88" s="85"/>
+      <c r="C88" s="85"/>
+      <c r="D88" s="85"/>
+      <c r="E88" s="85"/>
+      <c r="F88" s="87"/>
+      <c r="G88" s="87"/>
+      <c r="H88" s="87"/>
+      <c r="I88" s="87"/>
+      <c r="J88" s="87"/>
+      <c r="K88" s="87"/>
+      <c r="L88" s="87"/>
+      <c r="M88" s="87"/>
+      <c r="N88" s="87"/>
+      <c r="O88" s="87"/>
+      <c r="P88" s="87"/>
+      <c r="Q88" s="87"/>
+      <c r="R88" s="87"/>
+      <c r="S88" s="87"/>
+      <c r="T88" s="87"/>
+      <c r="U88" s="87"/>
+      <c r="V88" s="87"/>
+      <c r="W88" s="87"/>
+      <c r="X88" s="88"/>
+    </row>
+    <row r="89" spans="2:25" s="57" customFormat="1">
+      <c r="B89" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="C89" s="91"/>
-      <c r="D89" s="113">
+      <c r="C89" s="90"/>
+      <c r="D89" s="112">
         <f>C44</f>
         <v>0</v>
       </c>
-      <c r="E89" s="91"/>
-      <c r="F89" s="91"/>
-      <c r="G89" s="91"/>
-      <c r="H89" s="91"/>
-      <c r="I89" s="91"/>
-      <c r="J89" s="91"/>
-      <c r="K89" s="91"/>
-      <c r="L89" s="91"/>
-      <c r="M89" s="91"/>
-      <c r="N89" s="91"/>
-      <c r="O89" s="91"/>
-      <c r="P89" s="91"/>
-      <c r="Q89" s="91"/>
-      <c r="R89" s="91"/>
-      <c r="S89" s="91"/>
-      <c r="T89" s="91"/>
-      <c r="U89" s="91"/>
-      <c r="V89" s="91"/>
-      <c r="W89" s="91"/>
-      <c r="X89" s="79"/>
-    </row>
-    <row r="90" spans="2:25" s="58" customFormat="1">
-      <c r="B90" s="86"/>
-      <c r="C90" s="86"/>
-      <c r="D90" s="86"/>
-      <c r="E90" s="86"/>
-      <c r="F90" s="88"/>
-      <c r="G90" s="88"/>
-      <c r="H90" s="88"/>
-      <c r="I90" s="88"/>
-      <c r="J90" s="88"/>
-      <c r="K90" s="88"/>
-      <c r="L90" s="88"/>
-      <c r="M90" s="88"/>
-      <c r="N90" s="88"/>
-      <c r="O90" s="88"/>
-      <c r="P90" s="88"/>
-      <c r="Q90" s="88"/>
-      <c r="R90" s="88"/>
-      <c r="S90" s="88"/>
-      <c r="T90" s="88"/>
-      <c r="U90" s="88"/>
-      <c r="V90" s="88"/>
-      <c r="W90" s="88"/>
-      <c r="X90" s="89"/>
-    </row>
-    <row r="91" spans="2:25" s="58" customFormat="1">
-      <c r="B91" s="86"/>
-      <c r="C91" s="86"/>
-      <c r="D91" s="86"/>
-      <c r="E91" s="86"/>
-      <c r="F91" s="88"/>
-      <c r="G91" s="88"/>
-      <c r="H91" s="88"/>
-      <c r="I91" s="88"/>
-      <c r="J91" s="88"/>
-      <c r="K91" s="88"/>
-      <c r="L91" s="88"/>
-      <c r="M91" s="88"/>
-      <c r="N91" s="88"/>
-      <c r="O91" s="88"/>
-      <c r="P91" s="88"/>
-      <c r="Q91" s="88"/>
-      <c r="R91" s="88"/>
-      <c r="S91" s="88"/>
-      <c r="T91" s="88"/>
-      <c r="U91" s="88"/>
-      <c r="V91" s="88"/>
-      <c r="W91" s="88"/>
-      <c r="X91" s="89"/>
-    </row>
-    <row r="92" spans="2:25" s="58" customFormat="1">
-      <c r="B92" s="90" t="s">
+      <c r="E89" s="90"/>
+      <c r="F89" s="90"/>
+      <c r="G89" s="90"/>
+      <c r="H89" s="90"/>
+      <c r="I89" s="90"/>
+      <c r="J89" s="90"/>
+      <c r="K89" s="90"/>
+      <c r="L89" s="90"/>
+      <c r="M89" s="90"/>
+      <c r="N89" s="90"/>
+      <c r="O89" s="90"/>
+      <c r="P89" s="90"/>
+      <c r="Q89" s="90"/>
+      <c r="R89" s="90"/>
+      <c r="S89" s="90"/>
+      <c r="T89" s="90"/>
+      <c r="U89" s="90"/>
+      <c r="V89" s="90"/>
+      <c r="W89" s="90"/>
+      <c r="X89" s="78"/>
+    </row>
+    <row r="90" spans="2:25" s="57" customFormat="1">
+      <c r="B90" s="85"/>
+      <c r="C90" s="85"/>
+      <c r="D90" s="85"/>
+      <c r="E90" s="85"/>
+      <c r="F90" s="87"/>
+      <c r="G90" s="87"/>
+      <c r="H90" s="87"/>
+      <c r="I90" s="87"/>
+      <c r="J90" s="87"/>
+      <c r="K90" s="87"/>
+      <c r="L90" s="87"/>
+      <c r="M90" s="87"/>
+      <c r="N90" s="87"/>
+      <c r="O90" s="87"/>
+      <c r="P90" s="87"/>
+      <c r="Q90" s="87"/>
+      <c r="R90" s="87"/>
+      <c r="S90" s="87"/>
+      <c r="T90" s="87"/>
+      <c r="U90" s="87"/>
+      <c r="V90" s="87"/>
+      <c r="W90" s="87"/>
+      <c r="X90" s="88"/>
+    </row>
+    <row r="91" spans="2:25" s="57" customFormat="1">
+      <c r="B91" s="85"/>
+      <c r="C91" s="85"/>
+      <c r="D91" s="85"/>
+      <c r="E91" s="85"/>
+      <c r="F91" s="87"/>
+      <c r="G91" s="87"/>
+      <c r="H91" s="87"/>
+      <c r="I91" s="87"/>
+      <c r="J91" s="87"/>
+      <c r="K91" s="87"/>
+      <c r="L91" s="87"/>
+      <c r="M91" s="87"/>
+      <c r="N91" s="87"/>
+      <c r="O91" s="87"/>
+      <c r="P91" s="87"/>
+      <c r="Q91" s="87"/>
+      <c r="R91" s="87"/>
+      <c r="S91" s="87"/>
+      <c r="T91" s="87"/>
+      <c r="U91" s="87"/>
+      <c r="V91" s="87"/>
+      <c r="W91" s="87"/>
+      <c r="X91" s="88"/>
+    </row>
+    <row r="92" spans="2:25" s="57" customFormat="1">
+      <c r="B92" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="C92" s="91"/>
-      <c r="D92" s="113">
+      <c r="C92" s="90"/>
+      <c r="D92" s="112">
         <f>-D89*D31</f>
         <v>0</v>
       </c>
-      <c r="E92" s="91"/>
-      <c r="F92" s="91"/>
-      <c r="G92" s="91"/>
-      <c r="H92" s="91"/>
-      <c r="I92" s="91"/>
-      <c r="J92" s="91"/>
-      <c r="K92" s="91"/>
-      <c r="L92" s="91"/>
-      <c r="M92" s="91"/>
-      <c r="N92" s="91"/>
-      <c r="O92" s="91"/>
-      <c r="P92" s="91"/>
-      <c r="Q92" s="91"/>
-      <c r="R92" s="91"/>
-      <c r="S92" s="91"/>
-      <c r="T92" s="91"/>
-      <c r="U92" s="91"/>
-      <c r="V92" s="91"/>
-      <c r="W92" s="91"/>
-      <c r="X92" s="89"/>
-    </row>
-    <row r="93" spans="2:25" s="58" customFormat="1">
-      <c r="B93" s="86" t="s">
+      <c r="E92" s="90"/>
+      <c r="F92" s="90"/>
+      <c r="G92" s="90"/>
+      <c r="H92" s="90"/>
+      <c r="I92" s="90"/>
+      <c r="J92" s="90"/>
+      <c r="K92" s="90"/>
+      <c r="L92" s="90"/>
+      <c r="M92" s="90"/>
+      <c r="N92" s="90"/>
+      <c r="O92" s="90"/>
+      <c r="P92" s="90"/>
+      <c r="Q92" s="90"/>
+      <c r="R92" s="90"/>
+      <c r="S92" s="90"/>
+      <c r="T92" s="90"/>
+      <c r="U92" s="90"/>
+      <c r="V92" s="90"/>
+      <c r="W92" s="90"/>
+      <c r="X92" s="88"/>
+    </row>
+    <row r="93" spans="2:25" s="57" customFormat="1">
+      <c r="B93" s="85" t="s">
         <v>28</v>
       </c>
-      <c r="C93" s="86"/>
-      <c r="D93" s="118"/>
-      <c r="E93" s="118"/>
-      <c r="F93" s="118"/>
-      <c r="G93" s="118"/>
-      <c r="H93" s="118"/>
-      <c r="I93" s="118"/>
-      <c r="J93" s="118"/>
-      <c r="K93" s="118"/>
-      <c r="L93" s="118"/>
-      <c r="M93" s="118"/>
-      <c r="N93" s="118"/>
-      <c r="O93" s="118"/>
-      <c r="P93" s="118"/>
-      <c r="Q93" s="118"/>
-      <c r="R93" s="118"/>
-      <c r="S93" s="118"/>
-      <c r="T93" s="118"/>
-      <c r="U93" s="118"/>
-      <c r="V93" s="118"/>
-      <c r="W93" s="118"/>
-      <c r="X93" s="79"/>
-    </row>
-    <row r="94" spans="2:25" s="58" customFormat="1">
-      <c r="B94" s="86" t="s">
+      <c r="C93" s="85"/>
+      <c r="D93" s="116"/>
+      <c r="E93" s="116"/>
+      <c r="F93" s="116"/>
+      <c r="G93" s="116"/>
+      <c r="H93" s="116"/>
+      <c r="I93" s="116"/>
+      <c r="J93" s="116"/>
+      <c r="K93" s="116"/>
+      <c r="L93" s="116"/>
+      <c r="M93" s="116"/>
+      <c r="N93" s="116"/>
+      <c r="O93" s="116"/>
+      <c r="P93" s="116"/>
+      <c r="Q93" s="116"/>
+      <c r="R93" s="116"/>
+      <c r="S93" s="116"/>
+      <c r="T93" s="116"/>
+      <c r="U93" s="116"/>
+      <c r="V93" s="116"/>
+      <c r="W93" s="116"/>
+      <c r="X93" s="78"/>
+    </row>
+    <row r="94" spans="2:25" s="57" customFormat="1">
+      <c r="B94" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="C94" s="88"/>
-      <c r="D94" s="109">
+      <c r="C94" s="87"/>
+      <c r="D94" s="108">
         <f>-D89*(1-D31)</f>
         <v>0</v>
       </c>
-      <c r="E94" s="88"/>
-      <c r="F94" s="88"/>
-      <c r="G94" s="88"/>
-      <c r="H94" s="88"/>
-      <c r="I94" s="88"/>
-      <c r="J94" s="88"/>
-      <c r="K94" s="88"/>
-      <c r="L94" s="88"/>
-      <c r="M94" s="88"/>
-      <c r="N94" s="88"/>
-      <c r="O94" s="88"/>
-      <c r="P94" s="88"/>
-      <c r="Q94" s="88"/>
-      <c r="R94" s="88"/>
-      <c r="S94" s="88"/>
-      <c r="T94" s="88"/>
-      <c r="U94" s="88"/>
-      <c r="V94" s="88"/>
-      <c r="W94" s="88"/>
-      <c r="X94" s="87"/>
-    </row>
-    <row r="95" spans="2:25" s="58" customFormat="1">
-      <c r="B95" s="86" t="s">
+      <c r="E94" s="87"/>
+      <c r="F94" s="87"/>
+      <c r="G94" s="87"/>
+      <c r="H94" s="87"/>
+      <c r="I94" s="87"/>
+      <c r="J94" s="87"/>
+      <c r="K94" s="87"/>
+      <c r="L94" s="87"/>
+      <c r="M94" s="87"/>
+      <c r="N94" s="87"/>
+      <c r="O94" s="87"/>
+      <c r="P94" s="87"/>
+      <c r="Q94" s="87"/>
+      <c r="R94" s="87"/>
+      <c r="S94" s="87"/>
+      <c r="T94" s="87"/>
+      <c r="U94" s="87"/>
+      <c r="V94" s="87"/>
+      <c r="W94" s="87"/>
+      <c r="X94" s="86"/>
+    </row>
+    <row r="95" spans="2:25" s="57" customFormat="1">
+      <c r="B95" s="85" t="s">
         <v>30</v>
       </c>
-      <c r="C95" s="88"/>
-      <c r="D95" s="88"/>
-      <c r="E95" s="114" t="e">
+      <c r="C95" s="87"/>
+      <c r="D95" s="87"/>
+      <c r="E95" s="137" t="e">
         <f>-D85*$D$33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F95" s="114" t="e">
-        <f t="shared" ref="F95:X95" si="26">-E85*$D$33</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G95" s="114" t="e">
+      <c r="F95" s="137" t="e">
+        <f t="shared" ref="F95:W95" si="26">-E85*$D$33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G95" s="137" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H95" s="114" t="e">
+      <c r="H95" s="137" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I95" s="114" t="e">
+      <c r="I95" s="137" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J95" s="114" t="e">
+      <c r="J95" s="137" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K95" s="114" t="e">
+      <c r="K95" s="137" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L95" s="114" t="e">
+      <c r="L95" s="137" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M95" s="114" t="e">
+      <c r="M95" s="137" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N95" s="114" t="e">
+      <c r="N95" s="137" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O95" s="114" t="e">
+      <c r="O95" s="137" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P95" s="114" t="e">
+      <c r="P95" s="137" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q95" s="114" t="e">
+      <c r="Q95" s="137" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R95" s="114" t="e">
+      <c r="R95" s="137" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S95" s="114" t="e">
+      <c r="S95" s="137" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T95" s="114" t="e">
+      <c r="T95" s="137" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U95" s="114" t="e">
+      <c r="U95" s="137" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V95" s="114" t="e">
+      <c r="V95" s="137" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W95" s="114" t="e">
+      <c r="W95" s="137" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X95" s="114" t="e">
-        <f t="shared" si="26"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="96" spans="2:25" s="58" customFormat="1">
-      <c r="B96" s="92" t="s">
+      <c r="X95" s="137" t="e">
+        <f t="shared" ref="F95:X95" si="27">-W85*$D$33</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="96" spans="2:25" s="57" customFormat="1">
+      <c r="B96" s="91" t="s">
         <v>31</v>
       </c>
-      <c r="C96" s="93"/>
-      <c r="D96" s="93"/>
-      <c r="E96" s="116"/>
-      <c r="F96" s="116"/>
-      <c r="G96" s="116"/>
-      <c r="H96" s="116"/>
-      <c r="I96" s="116"/>
-      <c r="J96" s="116"/>
-      <c r="K96" s="116"/>
-      <c r="L96" s="116"/>
-      <c r="M96" s="116"/>
-      <c r="N96" s="116"/>
-      <c r="O96" s="116"/>
-      <c r="P96" s="116"/>
-      <c r="Q96" s="116"/>
-      <c r="R96" s="116"/>
-      <c r="S96" s="116"/>
-      <c r="T96" s="116"/>
-      <c r="U96" s="116"/>
-      <c r="V96" s="116"/>
-      <c r="W96" s="116"/>
-      <c r="X96" s="115" t="e">
+      <c r="C96" s="92"/>
+      <c r="D96" s="92"/>
+      <c r="E96" s="114"/>
+      <c r="F96" s="114"/>
+      <c r="G96" s="114"/>
+      <c r="H96" s="114"/>
+      <c r="I96" s="114"/>
+      <c r="J96" s="114"/>
+      <c r="K96" s="114"/>
+      <c r="L96" s="114"/>
+      <c r="M96" s="114"/>
+      <c r="N96" s="114"/>
+      <c r="O96" s="114"/>
+      <c r="P96" s="114"/>
+      <c r="Q96" s="114"/>
+      <c r="R96" s="114"/>
+      <c r="S96" s="114"/>
+      <c r="T96" s="114"/>
+      <c r="U96" s="114"/>
+      <c r="V96" s="114"/>
+      <c r="W96" s="114"/>
+      <c r="X96" s="113" t="e">
         <f>-W101-X95</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="97" spans="2:24" s="58" customFormat="1">
-      <c r="B97" s="88"/>
-      <c r="C97" s="88"/>
-      <c r="D97" s="88"/>
-      <c r="E97" s="88"/>
-      <c r="F97" s="88"/>
-      <c r="G97" s="88"/>
-      <c r="H97" s="88"/>
-      <c r="I97" s="88"/>
-      <c r="J97" s="88"/>
-      <c r="K97" s="88"/>
-      <c r="L97" s="88"/>
-      <c r="M97" s="88"/>
-      <c r="N97" s="88"/>
-      <c r="O97" s="88"/>
-      <c r="P97" s="88"/>
-      <c r="Q97" s="88"/>
-      <c r="R97" s="88"/>
-      <c r="S97" s="88"/>
-      <c r="T97" s="88"/>
-      <c r="U97" s="88"/>
-      <c r="V97" s="88"/>
-      <c r="W97" s="88"/>
-      <c r="X97" s="87"/>
-    </row>
-    <row r="98" spans="2:24" s="58" customFormat="1">
-      <c r="B98" s="88"/>
-      <c r="C98" s="88"/>
-      <c r="D98" s="88"/>
-      <c r="E98" s="88"/>
-      <c r="F98" s="88"/>
-      <c r="G98" s="88"/>
-      <c r="H98" s="88"/>
-      <c r="I98" s="88"/>
-      <c r="J98" s="88"/>
-      <c r="K98" s="88"/>
-      <c r="L98" s="88"/>
-      <c r="M98" s="88"/>
-      <c r="N98" s="88"/>
-      <c r="O98" s="88"/>
-      <c r="P98" s="88"/>
-      <c r="Q98" s="88"/>
-      <c r="R98" s="88"/>
-      <c r="S98" s="88"/>
-      <c r="T98" s="88"/>
-      <c r="U98" s="88"/>
-      <c r="V98" s="88"/>
-      <c r="W98" s="88"/>
-      <c r="X98" s="87"/>
-    </row>
-    <row r="99" spans="2:24" s="58" customFormat="1">
-      <c r="B99" s="86" t="s">
+    <row r="97" spans="2:24" s="57" customFormat="1">
+      <c r="B97" s="87"/>
+      <c r="C97" s="87"/>
+      <c r="D97" s="87"/>
+      <c r="E97" s="87"/>
+      <c r="F97" s="87"/>
+      <c r="G97" s="87"/>
+      <c r="H97" s="87"/>
+      <c r="I97" s="87"/>
+      <c r="J97" s="87"/>
+      <c r="K97" s="87"/>
+      <c r="L97" s="87"/>
+      <c r="M97" s="87"/>
+      <c r="N97" s="87"/>
+      <c r="O97" s="87"/>
+      <c r="P97" s="87"/>
+      <c r="Q97" s="87"/>
+      <c r="R97" s="87"/>
+      <c r="S97" s="87"/>
+      <c r="T97" s="87"/>
+      <c r="U97" s="87"/>
+      <c r="V97" s="87"/>
+      <c r="W97" s="87"/>
+      <c r="X97" s="86"/>
+    </row>
+    <row r="98" spans="2:24" s="57" customFormat="1">
+      <c r="B98" s="87"/>
+      <c r="C98" s="87"/>
+      <c r="D98" s="87"/>
+      <c r="E98" s="87"/>
+      <c r="F98" s="87"/>
+      <c r="G98" s="87"/>
+      <c r="H98" s="87"/>
+      <c r="I98" s="87"/>
+      <c r="J98" s="87"/>
+      <c r="K98" s="87"/>
+      <c r="L98" s="87"/>
+      <c r="M98" s="87"/>
+      <c r="N98" s="87"/>
+      <c r="O98" s="87"/>
+      <c r="P98" s="87"/>
+      <c r="Q98" s="87"/>
+      <c r="R98" s="87"/>
+      <c r="S98" s="87"/>
+      <c r="T98" s="87"/>
+      <c r="U98" s="87"/>
+      <c r="V98" s="87"/>
+      <c r="W98" s="87"/>
+      <c r="X98" s="86"/>
+    </row>
+    <row r="99" spans="2:24" s="57" customFormat="1">
+      <c r="B99" s="85" t="s">
         <v>32</v>
       </c>
-      <c r="C99" s="109">
-        <v>0</v>
-      </c>
-      <c r="D99" s="109" t="e">
+      <c r="C99" s="108">
+        <v>0</v>
+      </c>
+      <c r="D99" s="108" t="e">
         <f>SUM(D87:D96)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E99" s="109" t="e">
-        <f t="shared" ref="E99:W99" si="27">SUM(E87:E96)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F99" s="109" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G99" s="109" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H99" s="109" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I99" s="109" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J99" s="109" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K99" s="109" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L99" s="109" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M99" s="109" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N99" s="109" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O99" s="109" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P99" s="109" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q99" s="109" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R99" s="109" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S99" s="109" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T99" s="109" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U99" s="109" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V99" s="109" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W99" s="109" t="e">
-        <f t="shared" si="27"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X99" s="87"/>
-    </row>
-    <row r="100" spans="2:24" s="58" customFormat="1">
-      <c r="B100" s="86" t="s">
+      <c r="E99" s="108" t="e">
+        <f t="shared" ref="E99:W99" si="28">SUM(E87:E96)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F99" s="108" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G99" s="108" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H99" s="108" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I99" s="108" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J99" s="108" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K99" s="108" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L99" s="108" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M99" s="108" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N99" s="108" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O99" s="108" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P99" s="108" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q99" s="108" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R99" s="108" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S99" s="108" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T99" s="108" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U99" s="108" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V99" s="108" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W99" s="108" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X99" s="86"/>
+    </row>
+    <row r="100" spans="2:24" s="57" customFormat="1">
+      <c r="B100" s="85" t="s">
         <v>33</v>
       </c>
-      <c r="C100" s="109">
-        <v>0</v>
-      </c>
-      <c r="D100" s="109">
+      <c r="C100" s="108">
+        <v>0</v>
+      </c>
+      <c r="D100" s="108">
         <f>C101</f>
         <v>0</v>
       </c>
-      <c r="E100" s="109" t="e">
+      <c r="E100" s="108" t="e">
         <f>D101</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F100" s="109" t="e">
+      <c r="F100" s="108" t="e">
         <f>E101</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G100" s="109" t="e">
-        <f t="shared" ref="G100:W100" si="28">F101</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H100" s="109" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I100" s="109" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J100" s="109" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K100" s="109" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L100" s="109" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M100" s="109" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N100" s="109" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O100" s="109" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P100" s="109" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q100" s="109" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R100" s="109" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S100" s="109" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T100" s="109" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U100" s="109" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V100" s="109" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W100" s="109" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X100" s="89"/>
-    </row>
-    <row r="101" spans="2:24" s="58" customFormat="1">
-      <c r="B101" s="86" t="s">
+      <c r="G100" s="108" t="e">
+        <f t="shared" ref="G100:W100" si="29">F101</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H100" s="108" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I100" s="108" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J100" s="108" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K100" s="108" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L100" s="108" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M100" s="108" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N100" s="108" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O100" s="108" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P100" s="108" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q100" s="108" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R100" s="108" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S100" s="108" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T100" s="108" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U100" s="108" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V100" s="108" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W100" s="108" t="e">
+        <f t="shared" si="29"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X100" s="88"/>
+    </row>
+    <row r="101" spans="2:24" s="57" customFormat="1">
+      <c r="B101" s="85" t="s">
         <v>34</v>
       </c>
-      <c r="C101" s="109">
-        <v>0</v>
-      </c>
-      <c r="D101" s="109" t="e">
+      <c r="C101" s="108">
+        <v>0</v>
+      </c>
+      <c r="D101" s="108" t="e">
         <f>D99+D100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E101" s="109" t="e">
+      <c r="E101" s="108" t="e">
         <f>E99+E100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F101" s="109" t="e">
-        <f t="shared" ref="F101:W101" si="29">F99+F100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G101" s="109" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H101" s="109" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I101" s="109" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J101" s="109" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K101" s="109" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L101" s="109" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M101" s="109" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N101" s="109" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O101" s="109" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P101" s="109" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q101" s="109" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R101" s="109" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S101" s="109" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T101" s="109" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U101" s="109" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V101" s="109" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W101" s="109" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X101" s="89"/>
-    </row>
-    <row r="102" spans="2:24" s="58" customFormat="1">
-      <c r="B102" s="86"/>
-      <c r="C102" s="86"/>
-      <c r="D102" s="86"/>
-      <c r="E102" s="86"/>
-      <c r="F102" s="86"/>
-      <c r="G102" s="86"/>
-      <c r="H102" s="86"/>
-      <c r="I102" s="86"/>
-      <c r="J102" s="86"/>
-      <c r="K102" s="86"/>
-      <c r="L102" s="86"/>
-      <c r="M102" s="86"/>
-      <c r="N102" s="86"/>
-      <c r="O102" s="86"/>
-      <c r="P102" s="86"/>
-      <c r="Q102" s="86"/>
-      <c r="R102" s="86"/>
-      <c r="S102" s="86"/>
-      <c r="T102" s="86"/>
-      <c r="U102" s="86"/>
-      <c r="V102" s="86"/>
-      <c r="W102" s="86"/>
-      <c r="X102" s="86"/>
-    </row>
-    <row r="103" spans="2:24" s="58" customFormat="1">
-      <c r="B103" s="86"/>
-      <c r="C103" s="86"/>
-      <c r="D103" s="86"/>
-      <c r="E103" s="86"/>
-      <c r="F103" s="88"/>
-      <c r="G103" s="86"/>
-      <c r="H103" s="86"/>
-      <c r="I103" s="86"/>
-      <c r="J103" s="86"/>
-      <c r="K103" s="86"/>
-      <c r="L103" s="86"/>
-      <c r="M103" s="86"/>
-      <c r="N103" s="86"/>
-      <c r="O103" s="86"/>
-      <c r="P103" s="86"/>
-      <c r="Q103" s="86"/>
-      <c r="R103" s="86"/>
-      <c r="S103" s="86"/>
-      <c r="T103" s="86"/>
-      <c r="U103" s="86"/>
-      <c r="V103" s="86"/>
-      <c r="W103" s="86"/>
-      <c r="X103" s="86"/>
-    </row>
-    <row r="104" spans="2:24" s="58" customFormat="1">
-      <c r="B104" s="94" t="s">
+      <c r="F101" s="108" t="e">
+        <f t="shared" ref="F101:W101" si="30">F99+F100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G101" s="108" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H101" s="108" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I101" s="108" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J101" s="108" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K101" s="108" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L101" s="108" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M101" s="108" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N101" s="108" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O101" s="108" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P101" s="108" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q101" s="108" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R101" s="108" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S101" s="108" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T101" s="108" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U101" s="108" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V101" s="108" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W101" s="108" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X101" s="88"/>
+    </row>
+    <row r="102" spans="2:24" s="57" customFormat="1">
+      <c r="B102" s="85"/>
+      <c r="C102" s="85"/>
+      <c r="D102" s="85"/>
+      <c r="E102" s="85"/>
+      <c r="F102" s="85"/>
+      <c r="G102" s="85"/>
+      <c r="H102" s="85"/>
+      <c r="I102" s="85"/>
+      <c r="J102" s="85"/>
+      <c r="K102" s="85"/>
+      <c r="L102" s="85"/>
+      <c r="M102" s="85"/>
+      <c r="N102" s="85"/>
+      <c r="O102" s="85"/>
+      <c r="P102" s="85"/>
+      <c r="Q102" s="85"/>
+      <c r="R102" s="85"/>
+      <c r="S102" s="85"/>
+      <c r="T102" s="85"/>
+      <c r="U102" s="85"/>
+      <c r="V102" s="85"/>
+      <c r="W102" s="85"/>
+      <c r="X102" s="85"/>
+    </row>
+    <row r="103" spans="2:24" s="57" customFormat="1">
+      <c r="B103" s="85"/>
+      <c r="C103" s="85"/>
+      <c r="D103" s="85"/>
+      <c r="E103" s="85"/>
+      <c r="F103" s="87"/>
+      <c r="G103" s="85"/>
+      <c r="H103" s="85"/>
+      <c r="I103" s="85"/>
+      <c r="J103" s="85"/>
+      <c r="K103" s="85"/>
+      <c r="L103" s="85"/>
+      <c r="M103" s="85"/>
+      <c r="N103" s="85"/>
+      <c r="O103" s="85"/>
+      <c r="P103" s="85"/>
+      <c r="Q103" s="85"/>
+      <c r="R103" s="85"/>
+      <c r="S103" s="85"/>
+      <c r="T103" s="85"/>
+      <c r="U103" s="85"/>
+      <c r="V103" s="85"/>
+      <c r="W103" s="85"/>
+      <c r="X103" s="85"/>
+    </row>
+    <row r="104" spans="2:24" s="57" customFormat="1">
+      <c r="B104" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="C104" s="95"/>
-      <c r="D104" s="117">
+      <c r="C104" s="94"/>
+      <c r="D104" s="115">
         <f>-D94</f>
         <v>0</v>
       </c>
-      <c r="E104" s="112" t="e">
+      <c r="E104" s="111" t="e">
         <f>-E95-E96</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F104" s="112" t="e">
-        <f t="shared" ref="F104:X104" si="30">-F95-F96</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G104" s="112" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H104" s="112" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I104" s="112" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J104" s="112" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K104" s="112" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L104" s="112" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M104" s="112" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N104" s="112" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O104" s="112" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P104" s="112" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q104" s="112" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R104" s="112" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S104" s="112" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T104" s="112" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U104" s="112" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V104" s="112" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W104" s="112" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X104" s="112" t="e">
-        <f t="shared" si="30"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="105" spans="2:24" s="58" customFormat="1">
-      <c r="B105" s="86" t="s">
+      <c r="F104" s="111" t="e">
+        <f t="shared" ref="F104:X104" si="31">-F95-F96</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G104" s="111" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H104" s="111" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I104" s="111" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J104" s="111" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K104" s="111" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L104" s="111" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M104" s="111" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N104" s="111" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O104" s="111" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P104" s="111" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q104" s="111" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R104" s="111" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S104" s="111" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T104" s="111" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U104" s="111" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V104" s="111" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W104" s="111" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X104" s="111" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="105" spans="2:24" s="57" customFormat="1">
+      <c r="B105" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="C105" s="97" t="e">
+      <c r="C105" s="96" t="e">
         <f>IRR(D104:X104)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D105" s="88"/>
-      <c r="E105" s="88"/>
-      <c r="F105" s="86"/>
-      <c r="G105" s="86"/>
-      <c r="H105" s="86"/>
-      <c r="I105" s="86"/>
-      <c r="J105" s="86"/>
-      <c r="K105" s="86"/>
-      <c r="L105" s="86"/>
-      <c r="M105" s="86"/>
-      <c r="N105" s="86"/>
-      <c r="O105" s="86"/>
-      <c r="P105" s="86"/>
-      <c r="Q105" s="86"/>
-      <c r="R105" s="86"/>
-      <c r="S105" s="86"/>
-      <c r="T105" s="86"/>
-      <c r="U105" s="86"/>
-      <c r="V105" s="86"/>
-      <c r="W105" s="86"/>
-      <c r="X105" s="86"/>
-    </row>
-    <row r="106" spans="2:24" s="58" customFormat="1">
-      <c r="B106" s="94" t="s">
+      <c r="D105" s="87"/>
+      <c r="E105" s="87"/>
+      <c r="F105" s="85"/>
+      <c r="G105" s="85"/>
+      <c r="H105" s="85"/>
+      <c r="I105" s="85"/>
+      <c r="J105" s="85"/>
+      <c r="K105" s="85"/>
+      <c r="L105" s="85"/>
+      <c r="M105" s="85"/>
+      <c r="N105" s="85"/>
+      <c r="O105" s="85"/>
+      <c r="P105" s="85"/>
+      <c r="Q105" s="85"/>
+      <c r="R105" s="85"/>
+      <c r="S105" s="85"/>
+      <c r="T105" s="85"/>
+      <c r="U105" s="85"/>
+      <c r="V105" s="85"/>
+      <c r="W105" s="85"/>
+      <c r="X105" s="85"/>
+    </row>
+    <row r="106" spans="2:24" s="57" customFormat="1">
+      <c r="B106" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="C106" s="95"/>
-      <c r="D106" s="117" t="e">
+      <c r="C106" s="94"/>
+      <c r="D106" s="115" t="e">
         <f>D85-D94</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E106" s="112" t="e">
+      <c r="E106" s="111" t="e">
         <f>E85</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F106" s="112" t="e">
+      <c r="F106" s="111" t="e">
         <f>F85-F96</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G106" s="112" t="e">
-        <f t="shared" ref="G106:W106" si="31">G85-G96</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H106" s="112" t="e">
-        <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I106" s="112" t="e">
-        <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J106" s="112" t="e">
-        <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K106" s="112" t="e">
-        <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L106" s="112" t="e">
-        <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M106" s="112" t="e">
-        <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N106" s="112" t="e">
-        <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O106" s="112" t="e">
-        <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P106" s="112" t="e">
-        <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q106" s="112" t="e">
-        <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R106" s="112" t="e">
-        <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S106" s="112" t="e">
-        <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T106" s="112" t="e">
-        <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U106" s="112" t="e">
-        <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V106" s="112" t="e">
-        <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W106" s="112" t="e">
-        <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X106" s="79"/>
-    </row>
-    <row r="107" spans="2:24" s="58" customFormat="1">
-      <c r="B107" s="94" t="s">
+      <c r="G106" s="111" t="e">
+        <f t="shared" ref="G106:W106" si="32">G85-G96</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H106" s="111" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I106" s="111" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J106" s="111" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K106" s="111" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L106" s="111" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M106" s="111" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N106" s="111" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O106" s="111" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P106" s="111" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q106" s="111" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R106" s="111" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S106" s="111" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T106" s="111" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U106" s="111" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V106" s="111" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W106" s="111" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X106" s="78"/>
+    </row>
+    <row r="107" spans="2:24" s="57" customFormat="1">
+      <c r="B107" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="C107" s="96" t="e">
+      <c r="C107" s="95" t="e">
         <f>IRR(D106:W106)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D107" s="88"/>
-      <c r="E107" s="88"/>
-      <c r="F107" s="86"/>
-      <c r="G107" s="86"/>
-      <c r="H107" s="86"/>
-      <c r="I107" s="86"/>
-      <c r="J107" s="86"/>
-      <c r="K107" s="86"/>
-      <c r="L107" s="86"/>
-      <c r="M107" s="86"/>
-      <c r="N107" s="86"/>
-      <c r="O107" s="86"/>
-      <c r="P107" s="86"/>
-      <c r="Q107" s="86"/>
-      <c r="R107" s="86"/>
-      <c r="S107" s="86"/>
-      <c r="T107" s="86"/>
-      <c r="U107" s="86"/>
-      <c r="V107" s="86"/>
-      <c r="W107" s="86"/>
-      <c r="X107" s="86"/>
-    </row>
-    <row r="108" spans="2:24" s="58" customFormat="1">
-      <c r="B108" s="86"/>
-      <c r="C108" s="86"/>
-      <c r="D108" s="86"/>
-      <c r="E108" s="86"/>
-      <c r="F108" s="86"/>
-      <c r="G108" s="86"/>
-      <c r="H108" s="86"/>
-      <c r="I108" s="86"/>
-      <c r="J108" s="86"/>
-      <c r="K108" s="86"/>
-      <c r="L108" s="86"/>
-      <c r="M108" s="86"/>
-      <c r="N108" s="86"/>
-      <c r="O108" s="86"/>
-      <c r="P108" s="86"/>
-      <c r="Q108" s="86"/>
-      <c r="R108" s="86"/>
-      <c r="S108" s="86"/>
-      <c r="T108" s="86"/>
-      <c r="U108" s="86"/>
-      <c r="V108" s="86"/>
-      <c r="W108" s="86"/>
-      <c r="X108" s="86"/>
-    </row>
-    <row r="109" spans="2:24" s="58" customFormat="1">
-      <c r="B109" s="86" t="s">
+      <c r="D107" s="87"/>
+      <c r="E107" s="87"/>
+      <c r="F107" s="85"/>
+      <c r="G107" s="85"/>
+      <c r="H107" s="85"/>
+      <c r="I107" s="85"/>
+      <c r="J107" s="85"/>
+      <c r="K107" s="85"/>
+      <c r="L107" s="85"/>
+      <c r="M107" s="85"/>
+      <c r="N107" s="85"/>
+      <c r="O107" s="85"/>
+      <c r="P107" s="85"/>
+      <c r="Q107" s="85"/>
+      <c r="R107" s="85"/>
+      <c r="S107" s="85"/>
+      <c r="T107" s="85"/>
+      <c r="U107" s="85"/>
+      <c r="V107" s="85"/>
+      <c r="W107" s="85"/>
+      <c r="X107" s="85"/>
+    </row>
+    <row r="108" spans="2:24" s="57" customFormat="1">
+      <c r="B108" s="85"/>
+      <c r="C108" s="85"/>
+      <c r="D108" s="85"/>
+      <c r="E108" s="85"/>
+      <c r="F108" s="85"/>
+      <c r="G108" s="85"/>
+      <c r="H108" s="85"/>
+      <c r="I108" s="85"/>
+      <c r="J108" s="85"/>
+      <c r="K108" s="85"/>
+      <c r="L108" s="85"/>
+      <c r="M108" s="85"/>
+      <c r="N108" s="85"/>
+      <c r="O108" s="85"/>
+      <c r="P108" s="85"/>
+      <c r="Q108" s="85"/>
+      <c r="R108" s="85"/>
+      <c r="S108" s="85"/>
+      <c r="T108" s="85"/>
+      <c r="U108" s="85"/>
+      <c r="V108" s="85"/>
+      <c r="W108" s="85"/>
+      <c r="X108" s="85"/>
+    </row>
+    <row r="109" spans="2:24" s="57" customFormat="1">
+      <c r="B109" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="C109" s="109">
-        <v>0</v>
-      </c>
-      <c r="D109" s="109">
+      <c r="C109" s="108">
+        <v>0</v>
+      </c>
+      <c r="D109" s="108">
         <f>D92</f>
         <v>0</v>
       </c>
-      <c r="E109" s="109">
+      <c r="E109" s="108">
         <f>D109+E93</f>
         <v>0</v>
       </c>
-      <c r="F109" s="109">
-        <f t="shared" ref="F109:W109" si="32">E109+F93</f>
-        <v>0</v>
-      </c>
-      <c r="G109" s="109">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="H109" s="109">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="I109" s="109">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J109" s="109">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="K109" s="109">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="L109" s="109">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="M109" s="109">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="N109" s="109">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="O109" s="109">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="P109" s="109">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="Q109" s="109">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="R109" s="109">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="S109" s="109">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="T109" s="109">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="U109" s="109">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="V109" s="109">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="W109" s="109">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="X109" s="88"/>
+      <c r="F109" s="108">
+        <f t="shared" ref="F109:W109" si="33">E109+F93</f>
+        <v>0</v>
+      </c>
+      <c r="G109" s="108">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="H109" s="108">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="I109" s="108">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="J109" s="108">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="K109" s="108">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="L109" s="108">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="M109" s="108">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="N109" s="108">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="O109" s="108">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="P109" s="108">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="Q109" s="108">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="R109" s="108">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="S109" s="108">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="T109" s="108">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="U109" s="108">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="V109" s="108">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="W109" s="108">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="X109" s="87"/>
     </row>
     <row r="111" spans="2:24">
-      <c r="B111" s="40"/>
+      <c r="B111" s="39"/>
     </row>
     <row r="112" spans="2:24" ht="16.5">
-      <c r="G112" s="32"/>
+      <c r="G112" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="E10:E13"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B29:D29"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel Generic Template/excel公版.xlsx
+++ b/Excel Generic Template/excel公版.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\信邦\ai_agent2\Excel Generic Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FD8A1B-2C99-4576-A182-38565D85E828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B50EFA-B92A-4C88-AC1C-0BCC71111C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="滾算紀錄單(總紀錄)" sheetId="7" r:id="rId1"/>
@@ -2209,6 +2209,48 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="9" fillId="11" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="13" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="13" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="13" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="12" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="12" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="12" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="176" fontId="19" fillId="12" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2218,15 +2260,6 @@
     <xf numFmtId="176" fontId="19" fillId="12" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="12" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="12" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="12" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="176" fontId="20" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2234,39 +2267,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="20" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="13" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="13" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="13" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="11" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3274,12 +3274,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:35" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B1" s="118" t="s">
+      <c r="B1" s="132" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="120"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="134"/>
       <c r="P1" s="117">
         <f>1-D11</f>
         <v>1</v>
@@ -3414,20 +3414,20 @@
       <c r="E6" s="13"/>
     </row>
     <row r="7" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B7" s="121" t="s">
+      <c r="B7" s="129" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="123"/>
+      <c r="C7" s="130"/>
+      <c r="D7" s="130"/>
+      <c r="E7" s="131"/>
     </row>
     <row r="8" spans="2:35" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B8" s="124" t="s">
+      <c r="B8" s="135" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="125"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="126"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="136"/>
+      <c r="E8" s="137"/>
     </row>
     <row r="9" spans="2:35" ht="22.5" customHeight="1" thickBot="1">
       <c r="B9" s="14" t="s">
@@ -3444,46 +3444,46 @@
       </c>
     </row>
     <row r="10" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B10" s="127" t="s">
+      <c r="B10" s="122" t="s">
         <v>52</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="127"/>
+      <c r="E10" s="122"/>
     </row>
     <row r="11" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B11" s="128"/>
+      <c r="B11" s="123"/>
       <c r="C11" s="5" t="s">
         <v>54</v>
       </c>
       <c r="D11" s="5"/>
-      <c r="E11" s="128"/>
+      <c r="E11" s="123"/>
     </row>
     <row r="12" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B12" s="128"/>
+      <c r="B12" s="123"/>
       <c r="C12" s="5" t="s">
         <v>55</v>
       </c>
       <c r="D12" s="5"/>
-      <c r="E12" s="128"/>
+      <c r="E12" s="123"/>
     </row>
     <row r="13" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B13" s="128"/>
+      <c r="B13" s="123"/>
       <c r="C13" s="7" t="s">
         <v>56</v>
       </c>
       <c r="D13" s="7"/>
-      <c r="E13" s="128"/>
+      <c r="E13" s="123"/>
     </row>
     <row r="14" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B14" s="129" t="s">
+      <c r="B14" s="119" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="130"/>
-      <c r="D14" s="130"/>
-      <c r="E14" s="131"/>
+      <c r="C14" s="120"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="121"/>
     </row>
     <row r="15" spans="2:35" ht="22.5" customHeight="1">
       <c r="B15" s="14" t="s">
@@ -3500,33 +3500,33 @@
       </c>
     </row>
     <row r="16" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B16" s="127" t="s">
+      <c r="B16" s="122" t="s">
         <v>59</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>60</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="133"/>
+      <c r="E16" s="125"/>
     </row>
     <row r="17" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B17" s="128"/>
+      <c r="B17" s="123"/>
       <c r="C17" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="5"/>
-      <c r="E17" s="134"/>
+      <c r="E17" s="126"/>
     </row>
     <row r="18" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B18" s="132"/>
+      <c r="B18" s="124"/>
       <c r="C18" s="5" t="s">
         <v>62</v>
       </c>
       <c r="D18" s="5"/>
-      <c r="E18" s="135"/>
+      <c r="E18" s="127"/>
     </row>
     <row r="19" spans="2:5" ht="54" customHeight="1">
-      <c r="B19" s="136" t="s">
+      <c r="B19" s="128" t="s">
         <v>63</v>
       </c>
       <c r="C19" s="18" t="s">
@@ -3538,7 +3538,7 @@
       </c>
     </row>
     <row r="20" spans="2:5" ht="20.25" customHeight="1">
-      <c r="B20" s="128"/>
+      <c r="B20" s="123"/>
       <c r="C20" s="19" t="s">
         <v>65</v>
       </c>
@@ -3546,7 +3546,7 @@
       <c r="E20" s="4"/>
     </row>
     <row r="21" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B21" s="132"/>
+      <c r="B21" s="124"/>
       <c r="C21" s="5" t="s">
         <v>66</v>
       </c>
@@ -3622,11 +3622,11 @@
       <c r="E28" s="13"/>
     </row>
     <row r="29" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B29" s="121" t="s">
+      <c r="B29" s="129" t="s">
         <v>77</v>
       </c>
-      <c r="C29" s="122"/>
-      <c r="D29" s="123"/>
+      <c r="C29" s="130"/>
+      <c r="D29" s="131"/>
       <c r="E29" s="13"/>
     </row>
     <row r="30" spans="2:5" ht="22.5" customHeight="1">
@@ -5426,11 +5426,11 @@
         <v>0</v>
       </c>
       <c r="D68" s="99">
-        <f>D44</f>
+        <f>D45</f>
         <v>0</v>
       </c>
       <c r="E68" s="99">
-        <f t="shared" ref="E68:W68" si="11">E44</f>
+        <f t="shared" ref="E68:W68" si="11">E45</f>
         <v>0</v>
       </c>
       <c r="F68" s="99">
@@ -6909,84 +6909,84 @@
       </c>
       <c r="C95" s="87"/>
       <c r="D95" s="87"/>
-      <c r="E95" s="137" t="e">
+      <c r="E95" s="118" t="e">
         <f>-D85*$D$33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F95" s="137" t="e">
+      <c r="F95" s="118" t="e">
         <f t="shared" ref="F95:W95" si="26">-E85*$D$33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G95" s="137" t="e">
+      <c r="G95" s="118" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H95" s="137" t="e">
+      <c r="H95" s="118" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I95" s="137" t="e">
+      <c r="I95" s="118" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J95" s="137" t="e">
+      <c r="J95" s="118" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K95" s="137" t="e">
+      <c r="K95" s="118" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L95" s="137" t="e">
+      <c r="L95" s="118" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M95" s="137" t="e">
+      <c r="M95" s="118" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N95" s="137" t="e">
+      <c r="N95" s="118" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O95" s="137" t="e">
+      <c r="O95" s="118" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P95" s="137" t="e">
+      <c r="P95" s="118" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q95" s="137" t="e">
+      <c r="Q95" s="118" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R95" s="137" t="e">
+      <c r="R95" s="118" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S95" s="137" t="e">
+      <c r="S95" s="118" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T95" s="137" t="e">
+      <c r="T95" s="118" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U95" s="137" t="e">
+      <c r="U95" s="118" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V95" s="137" t="e">
+      <c r="V95" s="118" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W95" s="137" t="e">
+      <c r="W95" s="118" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X95" s="137" t="e">
-        <f t="shared" ref="F95:X95" si="27">-W85*$D$33</f>
+      <c r="X95" s="118" t="e">
+        <f t="shared" ref="X95" si="27">-W85*$D$33</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -7746,16 +7746,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="E10:E13"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B16:B18"/>
     <mergeCell ref="E16:E18"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="E10:E13"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel Generic Template/excel公版.xlsx
+++ b/Excel Generic Template/excel公版.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\信邦\ai_agent2\Excel Generic Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B50EFA-B92A-4C88-AC1C-0BCC71111C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A4D263-1CCD-4D20-AE64-03959D5B5606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="滾算紀錄單(總紀錄)" sheetId="7" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="ss" localSheetId="2">#REF!</definedName>
     <definedName name="ss">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="98">
   <si>
     <t>-</t>
   </si>
@@ -1072,6 +1072,29 @@
         <family val="2"/>
       </rPr>
       <t>折舊</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>成本法</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>IRR</t>
     </r>
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
@@ -1091,7 +1114,7 @@
     <numFmt numFmtId="182" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="183" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1306,6 +1329,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -2212,6 +2242,39 @@
     <xf numFmtId="182" fontId="9" fillId="11" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="19" fillId="12" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="12" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="12" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="12" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="12" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="12" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="20" fillId="13" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2221,12 +2284,6 @@
     <xf numFmtId="176" fontId="20" fillId="13" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="176" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2241,33 +2298,6 @@
     </xf>
     <xf numFmtId="176" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="12" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="12" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="12" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="12" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="12" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="12" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2915,19 +2945,21 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1">
+    <row r="1" spans="1:9" ht="18.75" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>85</v>
       </c>
@@ -2935,25 +2967,28 @@
         <v>86</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1">
+    <row r="2" spans="1:9" ht="18.75" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2962,8 +2997,9 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" ht="18.75" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -2972,8 +3008,9 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" ht="18.75" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -2982,8 +3019,9 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" ht="18.75" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -2992,8 +3030,9 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" ht="18.75" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -3002,8 +3041,9 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" ht="18.75" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -3012,8 +3052,9 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" ht="18.75" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -3022,8 +3063,9 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" ht="18.75" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -3032,8 +3074,9 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" ht="18.75" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -3042,8 +3085,9 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" ht="18.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -3052,8 +3096,9 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" ht="18.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -3062,8 +3107,9 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" ht="18.75" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -3072,8 +3118,9 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" ht="18.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -3082,8 +3129,9 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
-    </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" ht="18.75" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -3092,8 +3140,9 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" ht="18.75" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -3102,8 +3151,9 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" ht="18.75" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -3112,8 +3162,9 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9" ht="18.75" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -3122,8 +3173,9 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9" ht="18.75" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -3132,8 +3184,9 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9" ht="18.75" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -3142,8 +3195,9 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9" ht="18.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -3152,8 +3206,9 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
-    </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:9" ht="18.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -3162,8 +3217,9 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" ht="18.75" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -3172,8 +3228,9 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-    </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" ht="18.75" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -3182,8 +3239,9 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
-    </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="1:9" ht="18.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -3192,8 +3250,9 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
-    </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="1:9" ht="18.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -3202,8 +3261,9 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
-    </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="1:9" ht="18.75" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -3212,8 +3272,9 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="1:9" ht="18.75" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -3222,8 +3283,9 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
-    </row>
-    <row r="29" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9" ht="18.75" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -3232,8 +3294,9 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
-    </row>
-    <row r="30" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="1:9" ht="18.75" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -3242,6 +3305,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>
@@ -3274,12 +3338,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:35" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B1" s="132" t="s">
+      <c r="B1" s="119" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="134"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="121"/>
       <c r="P1" s="117">
         <f>1-D11</f>
         <v>1</v>
@@ -3414,20 +3478,20 @@
       <c r="E6" s="13"/>
     </row>
     <row r="7" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B7" s="129" t="s">
+      <c r="B7" s="122" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="131"/>
+      <c r="C7" s="123"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="124"/>
     </row>
     <row r="8" spans="2:35" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B8" s="135" t="s">
+      <c r="B8" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="136"/>
-      <c r="D8" s="136"/>
-      <c r="E8" s="137"/>
+      <c r="C8" s="126"/>
+      <c r="D8" s="126"/>
+      <c r="E8" s="127"/>
     </row>
     <row r="9" spans="2:35" ht="22.5" customHeight="1" thickBot="1">
       <c r="B9" s="14" t="s">
@@ -3444,46 +3508,46 @@
       </c>
     </row>
     <row r="10" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B10" s="122" t="s">
+      <c r="B10" s="128" t="s">
         <v>52</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="122"/>
+      <c r="E10" s="128"/>
     </row>
     <row r="11" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B11" s="123"/>
+      <c r="B11" s="129"/>
       <c r="C11" s="5" t="s">
         <v>54</v>
       </c>
       <c r="D11" s="5"/>
-      <c r="E11" s="123"/>
+      <c r="E11" s="129"/>
     </row>
     <row r="12" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B12" s="123"/>
+      <c r="B12" s="129"/>
       <c r="C12" s="5" t="s">
         <v>55</v>
       </c>
       <c r="D12" s="5"/>
-      <c r="E12" s="123"/>
+      <c r="E12" s="129"/>
     </row>
     <row r="13" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B13" s="123"/>
+      <c r="B13" s="129"/>
       <c r="C13" s="7" t="s">
         <v>56</v>
       </c>
       <c r="D13" s="7"/>
-      <c r="E13" s="123"/>
+      <c r="E13" s="129"/>
     </row>
     <row r="14" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B14" s="119" t="s">
+      <c r="B14" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="120"/>
-      <c r="D14" s="120"/>
-      <c r="E14" s="121"/>
+      <c r="C14" s="131"/>
+      <c r="D14" s="131"/>
+      <c r="E14" s="132"/>
     </row>
     <row r="15" spans="2:35" ht="22.5" customHeight="1">
       <c r="B15" s="14" t="s">
@@ -3500,33 +3564,33 @@
       </c>
     </row>
     <row r="16" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B16" s="122" t="s">
+      <c r="B16" s="128" t="s">
         <v>59</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>60</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="125"/>
+      <c r="E16" s="134"/>
     </row>
     <row r="17" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B17" s="123"/>
+      <c r="B17" s="129"/>
       <c r="C17" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="5"/>
-      <c r="E17" s="126"/>
+      <c r="E17" s="135"/>
     </row>
     <row r="18" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B18" s="124"/>
+      <c r="B18" s="133"/>
       <c r="C18" s="5" t="s">
         <v>62</v>
       </c>
       <c r="D18" s="5"/>
-      <c r="E18" s="127"/>
+      <c r="E18" s="136"/>
     </row>
     <row r="19" spans="2:5" ht="54" customHeight="1">
-      <c r="B19" s="128" t="s">
+      <c r="B19" s="137" t="s">
         <v>63</v>
       </c>
       <c r="C19" s="18" t="s">
@@ -3538,7 +3602,7 @@
       </c>
     </row>
     <row r="20" spans="2:5" ht="20.25" customHeight="1">
-      <c r="B20" s="123"/>
+      <c r="B20" s="129"/>
       <c r="C20" s="19" t="s">
         <v>65</v>
       </c>
@@ -3546,7 +3610,7 @@
       <c r="E20" s="4"/>
     </row>
     <row r="21" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B21" s="124"/>
+      <c r="B21" s="133"/>
       <c r="C21" s="5" t="s">
         <v>66</v>
       </c>
@@ -3622,11 +3686,11 @@
       <c r="E28" s="13"/>
     </row>
     <row r="29" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B29" s="129" t="s">
+      <c r="B29" s="122" t="s">
         <v>77</v>
       </c>
-      <c r="C29" s="130"/>
-      <c r="D29" s="131"/>
+      <c r="C29" s="123"/>
+      <c r="D29" s="124"/>
       <c r="E29" s="13"/>
     </row>
     <row r="30" spans="2:5" ht="22.5" customHeight="1">
@@ -7746,16 +7810,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="E10:E13"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B29:D29"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel Generic Template/excel公版.xlsx
+++ b/Excel Generic Template/excel公版.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\信邦\ai_agent2\Excel Generic Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A4D263-1CCD-4D20-AE64-03959D5B5606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F64371-9F45-466C-B117-FB750542B53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="滾算紀錄單(總紀錄)" sheetId="7" r:id="rId1"/>
@@ -1103,13 +1103,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="9">
+  <numFmts count="6">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="177" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="178" formatCode="0.000%"/>
-    <numFmt numFmtId="179" formatCode="0.0000%"/>
-    <numFmt numFmtId="180" formatCode="0.00000%"/>
     <numFmt numFmtId="181" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="182" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="183" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
@@ -1892,7 +1889,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2172,15 +2169,6 @@
     <xf numFmtId="177" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2242,6 +2230,45 @@
     <xf numFmtId="182" fontId="9" fillId="11" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="20" fillId="13" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="13" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="13" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="12" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="12" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="12" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="176" fontId="19" fillId="12" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2251,15 +2278,6 @@
     <xf numFmtId="176" fontId="19" fillId="12" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="12" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="12" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="12" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="176" fontId="20" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2269,35 +2287,11 @@
     <xf numFmtId="176" fontId="20" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="13" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="13" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="13" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3338,89 +3332,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:35" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B1" s="119" t="s">
+      <c r="B1" s="129" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="121"/>
-      <c r="P1" s="117">
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="131"/>
+      <c r="P1" s="114">
         <f>1-D11</f>
         <v>1</v>
       </c>
-      <c r="Q1" s="117">
+      <c r="Q1" s="114">
         <f t="shared" ref="Q1:AI1" si="0">P1-$D12</f>
         <v>1</v>
       </c>
-      <c r="R1" s="117">
+      <c r="R1" s="114">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="S1" s="117">
+      <c r="S1" s="114">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="T1" s="117">
+      <c r="T1" s="114">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="U1" s="117">
+      <c r="U1" s="114">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="V1" s="117">
+      <c r="V1" s="114">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="W1" s="117">
+      <c r="W1" s="114">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="X1" s="117">
+      <c r="X1" s="114">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Y1" s="117">
+      <c r="Y1" s="114">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Z1" s="117">
+      <c r="Z1" s="114">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AA1" s="117">
+      <c r="AA1" s="114">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AB1" s="117">
+      <c r="AB1" s="114">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AC1" s="117">
+      <c r="AC1" s="114">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AD1" s="117">
+      <c r="AD1" s="114">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AE1" s="117">
+      <c r="AE1" s="114">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AF1" s="117">
+      <c r="AF1" s="114">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AG1" s="117">
+      <c r="AG1" s="114">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AH1" s="117">
+      <c r="AH1" s="114">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AI1" s="117">
+      <c r="AI1" s="114">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -3478,20 +3472,20 @@
       <c r="E6" s="13"/>
     </row>
     <row r="7" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B7" s="122" t="s">
+      <c r="B7" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="124"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="128"/>
     </row>
     <row r="8" spans="2:35" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B8" s="125" t="s">
+      <c r="B8" s="132" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="126"/>
-      <c r="D8" s="126"/>
-      <c r="E8" s="127"/>
+      <c r="C8" s="133"/>
+      <c r="D8" s="133"/>
+      <c r="E8" s="134"/>
     </row>
     <row r="9" spans="2:35" ht="22.5" customHeight="1" thickBot="1">
       <c r="B9" s="14" t="s">
@@ -3508,46 +3502,46 @@
       </c>
     </row>
     <row r="10" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B10" s="128" t="s">
+      <c r="B10" s="119" t="s">
         <v>52</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="128"/>
+      <c r="E10" s="119"/>
     </row>
     <row r="11" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B11" s="129"/>
+      <c r="B11" s="120"/>
       <c r="C11" s="5" t="s">
         <v>54</v>
       </c>
       <c r="D11" s="5"/>
-      <c r="E11" s="129"/>
+      <c r="E11" s="120"/>
     </row>
     <row r="12" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B12" s="129"/>
+      <c r="B12" s="120"/>
       <c r="C12" s="5" t="s">
         <v>55</v>
       </c>
       <c r="D12" s="5"/>
-      <c r="E12" s="129"/>
+      <c r="E12" s="120"/>
     </row>
     <row r="13" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B13" s="129"/>
+      <c r="B13" s="120"/>
       <c r="C13" s="7" t="s">
         <v>56</v>
       </c>
       <c r="D13" s="7"/>
-      <c r="E13" s="129"/>
+      <c r="E13" s="120"/>
     </row>
     <row r="14" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B14" s="130" t="s">
+      <c r="B14" s="116" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="131"/>
-      <c r="D14" s="131"/>
-      <c r="E14" s="132"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="117"/>
+      <c r="E14" s="118"/>
     </row>
     <row r="15" spans="2:35" ht="22.5" customHeight="1">
       <c r="B15" s="14" t="s">
@@ -3564,33 +3558,33 @@
       </c>
     </row>
     <row r="16" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B16" s="128" t="s">
+      <c r="B16" s="119" t="s">
         <v>59</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>60</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="134"/>
+      <c r="E16" s="122"/>
     </row>
     <row r="17" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B17" s="129"/>
+      <c r="B17" s="120"/>
       <c r="C17" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="5"/>
-      <c r="E17" s="135"/>
+      <c r="E17" s="123"/>
     </row>
     <row r="18" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B18" s="133"/>
+      <c r="B18" s="121"/>
       <c r="C18" s="5" t="s">
         <v>62</v>
       </c>
       <c r="D18" s="5"/>
-      <c r="E18" s="136"/>
+      <c r="E18" s="124"/>
     </row>
     <row r="19" spans="2:5" ht="54" customHeight="1">
-      <c r="B19" s="137" t="s">
+      <c r="B19" s="125" t="s">
         <v>63</v>
       </c>
       <c r="C19" s="18" t="s">
@@ -3602,7 +3596,7 @@
       </c>
     </row>
     <row r="20" spans="2:5" ht="20.25" customHeight="1">
-      <c r="B20" s="129"/>
+      <c r="B20" s="120"/>
       <c r="C20" s="19" t="s">
         <v>65</v>
       </c>
@@ -3610,7 +3604,7 @@
       <c r="E20" s="4"/>
     </row>
     <row r="21" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B21" s="133"/>
+      <c r="B21" s="121"/>
       <c r="C21" s="5" t="s">
         <v>66</v>
       </c>
@@ -3686,11 +3680,11 @@
       <c r="E28" s="13"/>
     </row>
     <row r="29" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B29" s="122" t="s">
+      <c r="B29" s="126" t="s">
         <v>77</v>
       </c>
-      <c r="C29" s="123"/>
-      <c r="D29" s="124"/>
+      <c r="C29" s="127"/>
+      <c r="D29" s="128"/>
       <c r="E29" s="13"/>
     </row>
     <row r="30" spans="2:5" ht="22.5" customHeight="1">
@@ -3917,83 +3911,83 @@
       <c r="C40" s="9">
         <v>0</v>
       </c>
-      <c r="D40" s="105">
+      <c r="D40" s="102">
         <f>$D$10*P1</f>
         <v>0</v>
       </c>
-      <c r="E40" s="105">
+      <c r="E40" s="102">
         <f t="shared" ref="E40:W40" si="1">$D$10*Q1</f>
         <v>0</v>
       </c>
-      <c r="F40" s="105">
+      <c r="F40" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G40" s="105">
+      <c r="G40" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H40" s="105">
+      <c r="H40" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I40" s="105">
+      <c r="I40" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J40" s="105">
+      <c r="J40" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K40" s="105">
+      <c r="K40" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L40" s="105">
+      <c r="L40" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M40" s="105">
+      <c r="M40" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N40" s="105">
+      <c r="N40" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O40" s="105">
+      <c r="O40" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P40" s="105">
+      <c r="P40" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q40" s="105">
+      <c r="Q40" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R40" s="105">
+      <c r="R40" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S40" s="105">
+      <c r="S40" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T40" s="105">
+      <c r="T40" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U40" s="105">
+      <c r="U40" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="V40" s="105">
+      <c r="V40" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W40" s="105">
+      <c r="W40" s="102">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -4006,83 +4000,83 @@
       <c r="C41" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="D41" s="104">
+      <c r="D41" s="101">
         <f>D40*$D$13</f>
         <v>0</v>
       </c>
-      <c r="E41" s="104">
+      <c r="E41" s="101">
         <f t="shared" ref="E41:W41" si="2">E40*$D$13</f>
         <v>0</v>
       </c>
-      <c r="F41" s="104">
+      <c r="F41" s="101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G41" s="104">
+      <c r="G41" s="101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H41" s="104">
+      <c r="H41" s="101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I41" s="104">
+      <c r="I41" s="101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J41" s="104">
+      <c r="J41" s="101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K41" s="104">
+      <c r="K41" s="101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L41" s="104">
+      <c r="L41" s="101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M41" s="104">
+      <c r="M41" s="101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N41" s="104">
+      <c r="N41" s="101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O41" s="104">
+      <c r="O41" s="101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P41" s="104">
+      <c r="P41" s="101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q41" s="104">
+      <c r="Q41" s="101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R41" s="104">
+      <c r="R41" s="101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S41" s="104">
+      <c r="S41" s="101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T41" s="104">
+      <c r="T41" s="101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U41" s="104">
+      <c r="U41" s="101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V41" s="104">
+      <c r="V41" s="101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W41" s="104">
+      <c r="W41" s="101">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4182,31 +4176,31 @@
       <c r="B44" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="C44" s="98">
+      <c r="C44" s="95">
         <f>-(D16/(1-D17)+D18)*C4</f>
         <v>0</v>
       </c>
-      <c r="D44" s="99"/>
-      <c r="E44" s="99"/>
-      <c r="F44" s="99"/>
-      <c r="G44" s="99"/>
-      <c r="H44" s="99"/>
-      <c r="I44" s="99"/>
-      <c r="J44" s="99"/>
-      <c r="K44" s="99"/>
-      <c r="L44" s="99"/>
-      <c r="M44" s="99"/>
-      <c r="N44" s="99"/>
-      <c r="O44" s="99"/>
-      <c r="P44" s="99"/>
-      <c r="Q44" s="99"/>
-      <c r="R44" s="99"/>
-      <c r="S44" s="99"/>
-      <c r="T44" s="99"/>
-      <c r="U44" s="99"/>
-      <c r="V44" s="99"/>
-      <c r="W44" s="99"/>
-      <c r="X44" s="99"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
+      <c r="F44" s="96"/>
+      <c r="G44" s="96"/>
+      <c r="H44" s="96"/>
+      <c r="I44" s="96"/>
+      <c r="J44" s="96"/>
+      <c r="K44" s="96"/>
+      <c r="L44" s="96"/>
+      <c r="M44" s="96"/>
+      <c r="N44" s="96"/>
+      <c r="O44" s="96"/>
+      <c r="P44" s="96"/>
+      <c r="Q44" s="96"/>
+      <c r="R44" s="96"/>
+      <c r="S44" s="96"/>
+      <c r="T44" s="96"/>
+      <c r="U44" s="96"/>
+      <c r="V44" s="96"/>
+      <c r="W44" s="96"/>
+      <c r="X44" s="96"/>
     </row>
     <row r="45" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
       <c r="B45" s="66" t="s">
@@ -4215,54 +4209,54 @@
       <c r="C45" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="D45" s="99"/>
-      <c r="E45" s="99"/>
-      <c r="F45" s="99"/>
-      <c r="G45" s="99"/>
-      <c r="H45" s="99"/>
-      <c r="I45" s="99"/>
-      <c r="J45" s="99"/>
-      <c r="K45" s="99"/>
-      <c r="L45" s="99"/>
-      <c r="M45" s="99"/>
-      <c r="N45" s="99"/>
-      <c r="O45" s="99"/>
-      <c r="P45" s="99"/>
-      <c r="Q45" s="99"/>
-      <c r="R45" s="99"/>
-      <c r="S45" s="99"/>
-      <c r="T45" s="99"/>
-      <c r="U45" s="99"/>
-      <c r="V45" s="99"/>
-      <c r="W45" s="99"/>
-      <c r="X45" s="99"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
+      <c r="F45" s="96"/>
+      <c r="G45" s="96"/>
+      <c r="H45" s="96"/>
+      <c r="I45" s="96"/>
+      <c r="J45" s="96"/>
+      <c r="K45" s="96"/>
+      <c r="L45" s="96"/>
+      <c r="M45" s="96"/>
+      <c r="N45" s="96"/>
+      <c r="O45" s="96"/>
+      <c r="P45" s="96"/>
+      <c r="Q45" s="96"/>
+      <c r="R45" s="96"/>
+      <c r="S45" s="96"/>
+      <c r="T45" s="96"/>
+      <c r="U45" s="96"/>
+      <c r="V45" s="96"/>
+      <c r="W45" s="96"/>
+      <c r="X45" s="96"/>
     </row>
     <row r="46" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
       <c r="B46" s="66" t="s">
         <v>10</v>
       </c>
       <c r="C46" s="59"/>
-      <c r="D46" s="99"/>
-      <c r="E46" s="99"/>
-      <c r="F46" s="99"/>
-      <c r="G46" s="99"/>
-      <c r="H46" s="99"/>
-      <c r="I46" s="99"/>
-      <c r="J46" s="99"/>
-      <c r="K46" s="99"/>
-      <c r="L46" s="99"/>
-      <c r="M46" s="99"/>
-      <c r="N46" s="99"/>
-      <c r="O46" s="99"/>
-      <c r="P46" s="99"/>
-      <c r="Q46" s="99"/>
-      <c r="R46" s="99"/>
-      <c r="S46" s="99"/>
-      <c r="T46" s="99"/>
-      <c r="U46" s="99"/>
-      <c r="V46" s="99"/>
-      <c r="W46" s="99"/>
-      <c r="X46" s="99"/>
+      <c r="D46" s="96"/>
+      <c r="E46" s="96"/>
+      <c r="F46" s="96"/>
+      <c r="G46" s="96"/>
+      <c r="H46" s="96"/>
+      <c r="I46" s="96"/>
+      <c r="J46" s="96"/>
+      <c r="K46" s="96"/>
+      <c r="L46" s="96"/>
+      <c r="M46" s="96"/>
+      <c r="N46" s="96"/>
+      <c r="O46" s="96"/>
+      <c r="P46" s="96"/>
+      <c r="Q46" s="96"/>
+      <c r="R46" s="96"/>
+      <c r="S46" s="96"/>
+      <c r="T46" s="96"/>
+      <c r="U46" s="96"/>
+      <c r="V46" s="96"/>
+      <c r="W46" s="96"/>
+      <c r="X46" s="96"/>
     </row>
     <row r="47" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
       <c r="B47" s="66" t="s">
@@ -4271,27 +4265,27 @@
       <c r="C47" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="D47" s="99"/>
-      <c r="E47" s="99"/>
-      <c r="F47" s="99"/>
-      <c r="G47" s="99"/>
-      <c r="H47" s="99"/>
-      <c r="I47" s="99"/>
-      <c r="J47" s="99"/>
-      <c r="K47" s="99"/>
-      <c r="L47" s="99"/>
-      <c r="M47" s="99"/>
-      <c r="N47" s="99"/>
-      <c r="O47" s="99"/>
-      <c r="P47" s="99"/>
-      <c r="Q47" s="99"/>
-      <c r="R47" s="99"/>
-      <c r="S47" s="99"/>
-      <c r="T47" s="99"/>
-      <c r="U47" s="99"/>
-      <c r="V47" s="99"/>
-      <c r="W47" s="99"/>
-      <c r="X47" s="99"/>
+      <c r="D47" s="96"/>
+      <c r="E47" s="96"/>
+      <c r="F47" s="96"/>
+      <c r="G47" s="96"/>
+      <c r="H47" s="96"/>
+      <c r="I47" s="96"/>
+      <c r="J47" s="96"/>
+      <c r="K47" s="96"/>
+      <c r="L47" s="96"/>
+      <c r="M47" s="96"/>
+      <c r="N47" s="96"/>
+      <c r="O47" s="96"/>
+      <c r="P47" s="96"/>
+      <c r="Q47" s="96"/>
+      <c r="R47" s="96"/>
+      <c r="S47" s="96"/>
+      <c r="T47" s="96"/>
+      <c r="U47" s="96"/>
+      <c r="V47" s="96"/>
+      <c r="W47" s="96"/>
+      <c r="X47" s="96"/>
     </row>
     <row r="48" spans="2:24" s="57" customFormat="1" ht="18.75" customHeight="1">
       <c r="B48" s="66" t="s">
@@ -4300,27 +4294,27 @@
       <c r="C48" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="D48" s="99"/>
-      <c r="E48" s="99"/>
-      <c r="F48" s="99"/>
-      <c r="G48" s="99"/>
-      <c r="H48" s="99"/>
-      <c r="I48" s="99"/>
-      <c r="J48" s="99"/>
-      <c r="K48" s="99"/>
-      <c r="L48" s="99"/>
-      <c r="M48" s="99"/>
-      <c r="N48" s="99"/>
-      <c r="O48" s="99"/>
-      <c r="P48" s="99"/>
-      <c r="Q48" s="99"/>
-      <c r="R48" s="99"/>
-      <c r="S48" s="99"/>
-      <c r="T48" s="99"/>
-      <c r="U48" s="99"/>
-      <c r="V48" s="99"/>
-      <c r="W48" s="99"/>
-      <c r="X48" s="99"/>
+      <c r="D48" s="96"/>
+      <c r="E48" s="96"/>
+      <c r="F48" s="96"/>
+      <c r="G48" s="96"/>
+      <c r="H48" s="96"/>
+      <c r="I48" s="96"/>
+      <c r="J48" s="96"/>
+      <c r="K48" s="96"/>
+      <c r="L48" s="96"/>
+      <c r="M48" s="96"/>
+      <c r="N48" s="96"/>
+      <c r="O48" s="96"/>
+      <c r="P48" s="96"/>
+      <c r="Q48" s="96"/>
+      <c r="R48" s="96"/>
+      <c r="S48" s="96"/>
+      <c r="T48" s="96"/>
+      <c r="U48" s="96"/>
+      <c r="V48" s="96"/>
+      <c r="W48" s="96"/>
+      <c r="X48" s="96"/>
     </row>
     <row r="49" spans="2:36" s="57" customFormat="1" ht="18.75" customHeight="1">
       <c r="B49" s="66" t="s">
@@ -4329,218 +4323,218 @@
       <c r="C49" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="D49" s="99"/>
-      <c r="E49" s="99"/>
-      <c r="F49" s="99"/>
-      <c r="G49" s="99"/>
-      <c r="H49" s="99"/>
-      <c r="I49" s="99"/>
-      <c r="J49" s="99"/>
-      <c r="K49" s="99"/>
-      <c r="L49" s="99"/>
-      <c r="M49" s="99"/>
-      <c r="N49" s="99"/>
-      <c r="O49" s="99"/>
-      <c r="P49" s="99"/>
-      <c r="Q49" s="99"/>
-      <c r="R49" s="99"/>
-      <c r="S49" s="99"/>
-      <c r="T49" s="99"/>
-      <c r="U49" s="99"/>
-      <c r="V49" s="99"/>
-      <c r="W49" s="99"/>
-      <c r="X49" s="99"/>
+      <c r="D49" s="96"/>
+      <c r="E49" s="96"/>
+      <c r="F49" s="96"/>
+      <c r="G49" s="96"/>
+      <c r="H49" s="96"/>
+      <c r="I49" s="96"/>
+      <c r="J49" s="96"/>
+      <c r="K49" s="96"/>
+      <c r="L49" s="96"/>
+      <c r="M49" s="96"/>
+      <c r="N49" s="96"/>
+      <c r="O49" s="96"/>
+      <c r="P49" s="96"/>
+      <c r="Q49" s="96"/>
+      <c r="R49" s="96"/>
+      <c r="S49" s="96"/>
+      <c r="T49" s="96"/>
+      <c r="U49" s="96"/>
+      <c r="V49" s="96"/>
+      <c r="W49" s="96"/>
+      <c r="X49" s="96"/>
     </row>
     <row r="50" spans="2:36" s="57" customFormat="1" ht="18.75" customHeight="1">
       <c r="B50" s="66" t="s">
         <v>14</v>
       </c>
       <c r="C50" s="59"/>
-      <c r="D50" s="99"/>
-      <c r="E50" s="99"/>
-      <c r="F50" s="99"/>
-      <c r="G50" s="99"/>
-      <c r="H50" s="99"/>
-      <c r="I50" s="99"/>
-      <c r="J50" s="99"/>
-      <c r="K50" s="99"/>
-      <c r="L50" s="99"/>
-      <c r="M50" s="99"/>
-      <c r="N50" s="99"/>
-      <c r="O50" s="99"/>
-      <c r="P50" s="99"/>
-      <c r="Q50" s="99"/>
-      <c r="R50" s="99"/>
-      <c r="S50" s="99"/>
-      <c r="T50" s="99"/>
-      <c r="U50" s="99"/>
-      <c r="V50" s="99"/>
-      <c r="W50" s="99"/>
-      <c r="X50" s="99"/>
+      <c r="D50" s="96"/>
+      <c r="E50" s="96"/>
+      <c r="F50" s="96"/>
+      <c r="G50" s="96"/>
+      <c r="H50" s="96"/>
+      <c r="I50" s="96"/>
+      <c r="J50" s="96"/>
+      <c r="K50" s="96"/>
+      <c r="L50" s="96"/>
+      <c r="M50" s="96"/>
+      <c r="N50" s="96"/>
+      <c r="O50" s="96"/>
+      <c r="P50" s="96"/>
+      <c r="Q50" s="96"/>
+      <c r="R50" s="96"/>
+      <c r="S50" s="96"/>
+      <c r="T50" s="96"/>
+      <c r="U50" s="96"/>
+      <c r="V50" s="96"/>
+      <c r="W50" s="96"/>
+      <c r="X50" s="96"/>
     </row>
     <row r="51" spans="2:36" s="57" customFormat="1" ht="18.75" customHeight="1">
       <c r="B51" s="66" t="s">
         <v>15</v>
       </c>
       <c r="C51" s="67"/>
-      <c r="D51" s="99"/>
-      <c r="E51" s="99"/>
-      <c r="F51" s="99"/>
-      <c r="G51" s="99"/>
-      <c r="H51" s="99"/>
-      <c r="I51" s="99"/>
-      <c r="J51" s="99"/>
-      <c r="K51" s="99"/>
-      <c r="L51" s="99"/>
-      <c r="M51" s="99"/>
-      <c r="N51" s="99"/>
-      <c r="O51" s="99"/>
-      <c r="P51" s="99"/>
-      <c r="Q51" s="99"/>
-      <c r="R51" s="99"/>
-      <c r="S51" s="99"/>
-      <c r="T51" s="99"/>
-      <c r="U51" s="99"/>
-      <c r="V51" s="99"/>
-      <c r="W51" s="99"/>
-      <c r="X51" s="99"/>
+      <c r="D51" s="96"/>
+      <c r="E51" s="96"/>
+      <c r="F51" s="96"/>
+      <c r="G51" s="96"/>
+      <c r="H51" s="96"/>
+      <c r="I51" s="96"/>
+      <c r="J51" s="96"/>
+      <c r="K51" s="96"/>
+      <c r="L51" s="96"/>
+      <c r="M51" s="96"/>
+      <c r="N51" s="96"/>
+      <c r="O51" s="96"/>
+      <c r="P51" s="96"/>
+      <c r="Q51" s="96"/>
+      <c r="R51" s="96"/>
+      <c r="S51" s="96"/>
+      <c r="T51" s="96"/>
+      <c r="U51" s="96"/>
+      <c r="V51" s="96"/>
+      <c r="W51" s="96"/>
+      <c r="X51" s="96"/>
     </row>
     <row r="52" spans="2:36" s="57" customFormat="1" ht="18.75" customHeight="1">
       <c r="B52" s="66" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="67"/>
-      <c r="D52" s="99"/>
-      <c r="E52" s="99"/>
-      <c r="F52" s="99"/>
-      <c r="G52" s="99"/>
-      <c r="H52" s="99"/>
-      <c r="I52" s="99"/>
-      <c r="J52" s="99"/>
-      <c r="K52" s="99"/>
-      <c r="L52" s="99"/>
-      <c r="M52" s="99"/>
-      <c r="N52" s="99"/>
-      <c r="O52" s="99"/>
-      <c r="P52" s="99"/>
-      <c r="Q52" s="99"/>
-      <c r="R52" s="99"/>
-      <c r="S52" s="99"/>
-      <c r="T52" s="99"/>
-      <c r="U52" s="99"/>
-      <c r="V52" s="99"/>
-      <c r="W52" s="99"/>
-      <c r="X52" s="99"/>
+      <c r="D52" s="96"/>
+      <c r="E52" s="96"/>
+      <c r="F52" s="96"/>
+      <c r="G52" s="96"/>
+      <c r="H52" s="96"/>
+      <c r="I52" s="96"/>
+      <c r="J52" s="96"/>
+      <c r="K52" s="96"/>
+      <c r="L52" s="96"/>
+      <c r="M52" s="96"/>
+      <c r="N52" s="96"/>
+      <c r="O52" s="96"/>
+      <c r="P52" s="96"/>
+      <c r="Q52" s="96"/>
+      <c r="R52" s="96"/>
+      <c r="S52" s="96"/>
+      <c r="T52" s="96"/>
+      <c r="U52" s="96"/>
+      <c r="V52" s="96"/>
+      <c r="W52" s="96"/>
+      <c r="X52" s="96"/>
     </row>
     <row r="53" spans="2:36" s="57" customFormat="1" ht="18.75" customHeight="1">
       <c r="B53" s="70" t="s">
         <v>17</v>
       </c>
       <c r="C53" s="67"/>
-      <c r="D53" s="99"/>
-      <c r="E53" s="99"/>
-      <c r="F53" s="99"/>
-      <c r="G53" s="99"/>
-      <c r="H53" s="99"/>
-      <c r="I53" s="99"/>
-      <c r="J53" s="99"/>
-      <c r="K53" s="99"/>
-      <c r="L53" s="99"/>
-      <c r="M53" s="99"/>
-      <c r="N53" s="99"/>
-      <c r="O53" s="99"/>
-      <c r="P53" s="99"/>
-      <c r="Q53" s="99"/>
-      <c r="R53" s="99"/>
-      <c r="S53" s="99"/>
-      <c r="T53" s="99"/>
-      <c r="U53" s="99"/>
-      <c r="V53" s="99"/>
-      <c r="W53" s="99"/>
-      <c r="X53" s="99"/>
+      <c r="D53" s="96"/>
+      <c r="E53" s="96"/>
+      <c r="F53" s="96"/>
+      <c r="G53" s="96"/>
+      <c r="H53" s="96"/>
+      <c r="I53" s="96"/>
+      <c r="J53" s="96"/>
+      <c r="K53" s="96"/>
+      <c r="L53" s="96"/>
+      <c r="M53" s="96"/>
+      <c r="N53" s="96"/>
+      <c r="O53" s="96"/>
+      <c r="P53" s="96"/>
+      <c r="Q53" s="96"/>
+      <c r="R53" s="96"/>
+      <c r="S53" s="96"/>
+      <c r="T53" s="96"/>
+      <c r="U53" s="96"/>
+      <c r="V53" s="96"/>
+      <c r="W53" s="96"/>
+      <c r="X53" s="96"/>
     </row>
     <row r="54" spans="2:36" s="57" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B54" s="70" t="s">
         <v>18</v>
       </c>
       <c r="C54" s="67"/>
-      <c r="D54" s="99" t="e">
+      <c r="D54" s="96" t="e">
         <f>-(D64+D67+D68+D71+D72+D73+D74)*0.2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E54" s="99" t="e">
+      <c r="E54" s="96" t="e">
         <f t="shared" ref="E54:W54" si="3">-(E64+E67+E68+E71+E72+E73+E74)*0.2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F54" s="99" t="e">
+      <c r="F54" s="96" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G54" s="99" t="e">
+      <c r="G54" s="96" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H54" s="99" t="e">
+      <c r="H54" s="96" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I54" s="99" t="e">
+      <c r="I54" s="96" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J54" s="99" t="e">
+      <c r="J54" s="96" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K54" s="99" t="e">
+      <c r="K54" s="96" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L54" s="99" t="e">
+      <c r="L54" s="96" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M54" s="99" t="e">
+      <c r="M54" s="96" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N54" s="99" t="e">
+      <c r="N54" s="96" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O54" s="99" t="e">
+      <c r="O54" s="96" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P54" s="99" t="e">
+      <c r="P54" s="96" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q54" s="99" t="e">
+      <c r="Q54" s="96" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R54" s="99" t="e">
+      <c r="R54" s="96" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S54" s="99" t="e">
+      <c r="S54" s="96" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T54" s="99" t="e">
+      <c r="T54" s="96" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U54" s="99" t="e">
+      <c r="U54" s="96" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V54" s="99" t="e">
+      <c r="V54" s="96" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W54" s="99" t="e">
+      <c r="W54" s="96" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
@@ -4550,87 +4544,87 @@
       <c r="B55" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="C55" s="103">
+      <c r="C55" s="100">
         <f>C44</f>
         <v>0</v>
       </c>
-      <c r="D55" s="100" t="e">
+      <c r="D55" s="97" t="e">
         <f>SUM(D41:D54)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E55" s="100" t="e">
+      <c r="E55" s="97" t="e">
         <f>SUM(E41:E54)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F55" s="100" t="e">
+      <c r="F55" s="97" t="e">
         <f t="shared" ref="F55:W55" si="4">SUM(F41:F54)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G55" s="100" t="e">
+      <c r="G55" s="97" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H55" s="100" t="e">
+      <c r="H55" s="97" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I55" s="100" t="e">
+      <c r="I55" s="97" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J55" s="100" t="e">
+      <c r="J55" s="97" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K55" s="100" t="e">
+      <c r="K55" s="97" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L55" s="100" t="e">
+      <c r="L55" s="97" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M55" s="100" t="e">
+      <c r="M55" s="97" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N55" s="100" t="e">
+      <c r="N55" s="97" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O55" s="100" t="e">
+      <c r="O55" s="97" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P55" s="100" t="e">
+      <c r="P55" s="97" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q55" s="100" t="e">
+      <c r="Q55" s="97" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R55" s="100" t="e">
+      <c r="R55" s="97" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S55" s="100" t="e">
+      <c r="S55" s="97" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T55" s="100" t="e">
+      <c r="T55" s="97" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U55" s="100" t="e">
+      <c r="U55" s="97" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V55" s="100" t="e">
+      <c r="V55" s="97" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W55" s="100" t="e">
+      <c r="W55" s="97" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
@@ -4652,87 +4646,87 @@
       <c r="B56" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="D56" s="101" t="e">
+      <c r="D56" s="98" t="e">
         <f>C55+D55</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E56" s="101" t="e">
+      <c r="E56" s="98" t="e">
         <f>D56+E55</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F56" s="101" t="e">
+      <c r="F56" s="98" t="e">
         <f t="shared" ref="F56:X56" si="5">E56+F55</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G56" s="101" t="e">
+      <c r="G56" s="98" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H56" s="101" t="e">
+      <c r="H56" s="98" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I56" s="101" t="e">
+      <c r="I56" s="98" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J56" s="101" t="e">
+      <c r="J56" s="98" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K56" s="101" t="e">
+      <c r="K56" s="98" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L56" s="101" t="e">
+      <c r="L56" s="98" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M56" s="101" t="e">
+      <c r="M56" s="98" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N56" s="101" t="e">
+      <c r="N56" s="98" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O56" s="101" t="e">
+      <c r="O56" s="98" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P56" s="101" t="e">
+      <c r="P56" s="98" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q56" s="101" t="e">
+      <c r="Q56" s="98" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R56" s="101" t="e">
+      <c r="R56" s="98" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S56" s="101" t="e">
+      <c r="S56" s="98" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T56" s="101" t="e">
+      <c r="T56" s="98" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U56" s="101" t="e">
+      <c r="U56" s="98" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V56" s="101" t="e">
+      <c r="V56" s="98" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W56" s="101" t="e">
+      <c r="W56" s="98" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X56" s="101" t="e">
+      <c r="X56" s="98" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
@@ -4754,7 +4748,7 @@
         <v>21</v>
       </c>
       <c r="C57" s="80"/>
-      <c r="D57" s="102" t="e">
+      <c r="D57" s="99" t="e">
         <f t="shared" ref="D57:X57" si="6">IF((D56)&gt;0,"回收","未回收")</f>
         <v>#DIV/0!</v>
       </c>
@@ -4855,7 +4849,7 @@
       <c r="B58" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="C58" s="97" t="e">
+      <c r="C58" s="135" t="e">
         <f>IRR(C55:W55)</f>
         <v>#VALUE!</v>
       </c>
@@ -5134,83 +5128,83 @@
       <c r="C63" s="9">
         <v>0</v>
       </c>
-      <c r="D63" s="105">
+      <c r="D63" s="102">
         <f t="shared" ref="D63:W63" si="8">D40</f>
         <v>0</v>
       </c>
-      <c r="E63" s="105">
+      <c r="E63" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F63" s="105">
+      <c r="F63" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G63" s="105">
+      <c r="G63" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="H63" s="105">
+      <c r="H63" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I63" s="105">
+      <c r="I63" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="J63" s="105">
+      <c r="J63" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="K63" s="105">
+      <c r="K63" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L63" s="105">
+      <c r="L63" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="M63" s="105">
+      <c r="M63" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N63" s="105">
+      <c r="N63" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O63" s="105">
+      <c r="O63" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="P63" s="105">
+      <c r="P63" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q63" s="105">
+      <c r="Q63" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R63" s="105">
+      <c r="R63" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S63" s="105">
+      <c r="S63" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T63" s="105">
+      <c r="T63" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="U63" s="105">
+      <c r="U63" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V63" s="105">
+      <c r="V63" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W63" s="105">
+      <c r="W63" s="102">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -5223,83 +5217,83 @@
       <c r="C64" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="D64" s="104">
+      <c r="D64" s="101">
         <f t="shared" ref="D64:W64" si="9">D41</f>
         <v>0</v>
       </c>
-      <c r="E64" s="104">
+      <c r="E64" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="F64" s="104">
+      <c r="F64" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="G64" s="104">
+      <c r="G64" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H64" s="104">
+      <c r="H64" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="I64" s="104">
+      <c r="I64" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J64" s="104">
+      <c r="J64" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="K64" s="104">
+      <c r="K64" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="L64" s="104">
+      <c r="L64" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="M64" s="104">
+      <c r="M64" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="N64" s="104">
+      <c r="N64" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="O64" s="104">
+      <c r="O64" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="P64" s="104">
+      <c r="P64" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q64" s="104">
+      <c r="Q64" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="R64" s="104">
+      <c r="R64" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="S64" s="104">
+      <c r="S64" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T64" s="104">
+      <c r="T64" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U64" s="104">
+      <c r="U64" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="V64" s="104">
+      <c r="V64" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="W64" s="104">
+      <c r="W64" s="101">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -5400,83 +5394,83 @@
         <v>96</v>
       </c>
       <c r="C67" s="59"/>
-      <c r="D67" s="106" t="e">
+      <c r="D67" s="103" t="e">
         <f>$C$44/$E$16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E67" s="106" t="e">
+      <c r="E67" s="103" t="e">
         <f t="shared" ref="E67:W67" si="10">$C$44/$E$16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F67" s="106" t="e">
+      <c r="F67" s="103" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G67" s="106" t="e">
+      <c r="G67" s="103" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H67" s="106" t="e">
+      <c r="H67" s="103" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I67" s="106" t="e">
+      <c r="I67" s="103" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J67" s="106" t="e">
+      <c r="J67" s="103" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K67" s="106" t="e">
+      <c r="K67" s="103" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L67" s="106" t="e">
+      <c r="L67" s="103" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M67" s="106" t="e">
+      <c r="M67" s="103" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N67" s="106" t="e">
+      <c r="N67" s="103" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O67" s="106" t="e">
+      <c r="O67" s="103" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P67" s="106" t="e">
+      <c r="P67" s="103" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q67" s="106" t="e">
+      <c r="Q67" s="103" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R67" s="106" t="e">
+      <c r="R67" s="103" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S67" s="106" t="e">
+      <c r="S67" s="103" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T67" s="106" t="e">
+      <c r="T67" s="103" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U67" s="106" t="e">
+      <c r="U67" s="103" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V67" s="106" t="e">
+      <c r="V67" s="103" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W67" s="106" t="e">
+      <c r="W67" s="103" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
@@ -5489,83 +5483,83 @@
       <c r="C68" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="D68" s="99">
+      <c r="D68" s="96">
         <f>D45</f>
         <v>0</v>
       </c>
-      <c r="E68" s="99">
+      <c r="E68" s="96">
         <f t="shared" ref="E68:W68" si="11">E45</f>
         <v>0</v>
       </c>
-      <c r="F68" s="99">
+      <c r="F68" s="96">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="G68" s="99">
+      <c r="G68" s="96">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="H68" s="99">
+      <c r="H68" s="96">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="I68" s="99">
+      <c r="I68" s="96">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="J68" s="99">
+      <c r="J68" s="96">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="K68" s="99">
+      <c r="K68" s="96">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="L68" s="99">
+      <c r="L68" s="96">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="M68" s="99">
+      <c r="M68" s="96">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="N68" s="99">
+      <c r="N68" s="96">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="O68" s="99">
+      <c r="O68" s="96">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="P68" s="99">
+      <c r="P68" s="96">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q68" s="99">
+      <c r="Q68" s="96">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="R68" s="99">
+      <c r="R68" s="96">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S68" s="99">
+      <c r="S68" s="96">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="T68" s="99">
+      <c r="T68" s="96">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="U68" s="99">
+      <c r="U68" s="96">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="V68" s="99">
+      <c r="V68" s="96">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="W68" s="99">
+      <c r="W68" s="96">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -5605,83 +5599,83 @@
       <c r="C70" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="D70" s="99">
+      <c r="D70" s="96">
         <f>-D109*$D25</f>
         <v>0</v>
       </c>
-      <c r="E70" s="99">
+      <c r="E70" s="96">
         <f t="shared" ref="E70:W70" si="12">-E109*$D25</f>
         <v>0</v>
       </c>
-      <c r="F70" s="99">
+      <c r="F70" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="G70" s="99">
+      <c r="G70" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H70" s="99">
+      <c r="H70" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I70" s="99">
+      <c r="I70" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="J70" s="99">
+      <c r="J70" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K70" s="99">
+      <c r="K70" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L70" s="99">
+      <c r="L70" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="M70" s="99">
+      <c r="M70" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="N70" s="99">
+      <c r="N70" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="O70" s="99">
+      <c r="O70" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="P70" s="99">
+      <c r="P70" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Q70" s="99">
+      <c r="Q70" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="R70" s="99">
+      <c r="R70" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="S70" s="99">
+      <c r="S70" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="T70" s="99">
+      <c r="T70" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="U70" s="99">
+      <c r="U70" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="V70" s="99">
+      <c r="V70" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="W70" s="99">
+      <c r="W70" s="96">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
@@ -5694,83 +5688,83 @@
       <c r="C71" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="D71" s="99">
+      <c r="D71" s="96">
         <f t="shared" ref="D71:W71" si="13">D48</f>
         <v>0</v>
       </c>
-      <c r="E71" s="99">
+      <c r="E71" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F71" s="99">
+      <c r="F71" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="G71" s="99">
+      <c r="G71" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="H71" s="99">
+      <c r="H71" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="I71" s="99">
+      <c r="I71" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="J71" s="99">
+      <c r="J71" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="K71" s="99">
+      <c r="K71" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="L71" s="99">
+      <c r="L71" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M71" s="99">
+      <c r="M71" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="N71" s="99">
+      <c r="N71" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="O71" s="99">
+      <c r="O71" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="P71" s="99">
+      <c r="P71" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Q71" s="99">
+      <c r="Q71" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="R71" s="99">
+      <c r="R71" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S71" s="99">
+      <c r="S71" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="T71" s="99">
+      <c r="T71" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U71" s="99">
+      <c r="U71" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="V71" s="99">
+      <c r="V71" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="W71" s="99">
+      <c r="W71" s="96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
@@ -5783,83 +5777,83 @@
       <c r="C72" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="D72" s="99">
+      <c r="D72" s="96">
         <f t="shared" ref="D72:W72" si="14">D49</f>
         <v>0</v>
       </c>
-      <c r="E72" s="99">
+      <c r="E72" s="96">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="F72" s="99">
+      <c r="F72" s="96">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G72" s="99">
+      <c r="G72" s="96">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H72" s="99">
+      <c r="H72" s="96">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="I72" s="99">
+      <c r="I72" s="96">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="J72" s="99">
+      <c r="J72" s="96">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="K72" s="99">
+      <c r="K72" s="96">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="L72" s="99">
+      <c r="L72" s="96">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="M72" s="99">
+      <c r="M72" s="96">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="N72" s="99">
+      <c r="N72" s="96">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="O72" s="99">
+      <c r="O72" s="96">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="P72" s="99">
+      <c r="P72" s="96">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="Q72" s="99">
+      <c r="Q72" s="96">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="R72" s="99">
+      <c r="R72" s="96">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="S72" s="99">
+      <c r="S72" s="96">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="T72" s="99">
+      <c r="T72" s="96">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="U72" s="99">
+      <c r="U72" s="96">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="V72" s="99">
+      <c r="V72" s="96">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="W72" s="99">
+      <c r="W72" s="96">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
@@ -5870,83 +5864,83 @@
         <v>14</v>
       </c>
       <c r="C73" s="59"/>
-      <c r="D73" s="99">
+      <c r="D73" s="96">
         <f t="shared" ref="D73:W73" si="15">D50</f>
         <v>0</v>
       </c>
-      <c r="E73" s="99">
+      <c r="E73" s="96">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="F73" s="99">
+      <c r="F73" s="96">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="G73" s="99">
+      <c r="G73" s="96">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H73" s="99">
+      <c r="H73" s="96">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I73" s="99">
+      <c r="I73" s="96">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="J73" s="99">
+      <c r="J73" s="96">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="K73" s="99">
+      <c r="K73" s="96">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="L73" s="99">
+      <c r="L73" s="96">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="M73" s="99">
+      <c r="M73" s="96">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="N73" s="99">
+      <c r="N73" s="96">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="O73" s="99">
+      <c r="O73" s="96">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="P73" s="99">
+      <c r="P73" s="96">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Q73" s="99">
+      <c r="Q73" s="96">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="R73" s="99">
+      <c r="R73" s="96">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="S73" s="99">
+      <c r="S73" s="96">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="T73" s="99">
+      <c r="T73" s="96">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="U73" s="99">
+      <c r="U73" s="96">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="V73" s="99">
+      <c r="V73" s="96">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="W73" s="99">
+      <c r="W73" s="96">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
@@ -6011,87 +6005,87 @@
         <v>94</v>
       </c>
       <c r="C76" s="82"/>
-      <c r="D76" s="100" t="e">
+      <c r="D76" s="97" t="e">
         <f>SUM(D64:D75)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E76" s="100" t="e">
+      <c r="E76" s="97" t="e">
         <f t="shared" ref="E76:W76" si="16">SUM(E64:E75)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F76" s="100" t="e">
+      <c r="F76" s="97" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G76" s="100" t="e">
+      <c r="G76" s="97" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H76" s="100" t="e">
+      <c r="H76" s="97" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I76" s="100" t="e">
+      <c r="I76" s="97" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J76" s="100" t="e">
+      <c r="J76" s="97" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K76" s="100" t="e">
+      <c r="K76" s="97" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L76" s="100" t="e">
+      <c r="L76" s="97" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M76" s="100" t="e">
+      <c r="M76" s="97" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N76" s="100" t="e">
+      <c r="N76" s="97" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O76" s="100" t="e">
+      <c r="O76" s="97" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P76" s="100" t="e">
+      <c r="P76" s="97" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q76" s="100" t="e">
+      <c r="Q76" s="97" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R76" s="100" t="e">
+      <c r="R76" s="97" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S76" s="100" t="e">
+      <c r="S76" s="97" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T76" s="100" t="e">
+      <c r="T76" s="97" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U76" s="100" t="e">
+      <c r="U76" s="97" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V76" s="100" t="e">
+      <c r="V76" s="97" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W76" s="100" t="e">
+      <c r="W76" s="97" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X76" s="100">
+      <c r="X76" s="97">
         <f t="shared" ref="X76" si="17">SUM(X64:X75)</f>
         <v>0</v>
       </c>
@@ -6101,87 +6095,87 @@
         <v>18</v>
       </c>
       <c r="C77" s="67"/>
-      <c r="D77" s="99" t="e">
+      <c r="D77" s="96" t="e">
         <f>-D76*0.2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E77" s="99" t="e">
+      <c r="E77" s="96" t="e">
         <f t="shared" ref="E77:W77" si="18">-E76*0.2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F77" s="99" t="e">
+      <c r="F77" s="96" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G77" s="99" t="e">
+      <c r="G77" s="96" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H77" s="99" t="e">
+      <c r="H77" s="96" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I77" s="99" t="e">
+      <c r="I77" s="96" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J77" s="99" t="e">
+      <c r="J77" s="96" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K77" s="99" t="e">
+      <c r="K77" s="96" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L77" s="99" t="e">
+      <c r="L77" s="96" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M77" s="99" t="e">
+      <c r="M77" s="96" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N77" s="99" t="e">
+      <c r="N77" s="96" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O77" s="99" t="e">
+      <c r="O77" s="96" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P77" s="99" t="e">
+      <c r="P77" s="96" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q77" s="99" t="e">
+      <c r="Q77" s="96" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R77" s="99" t="e">
+      <c r="R77" s="96" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S77" s="99" t="e">
+      <c r="S77" s="96" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T77" s="99" t="e">
+      <c r="T77" s="96" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U77" s="99" t="e">
+      <c r="U77" s="96" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V77" s="99" t="e">
+      <c r="V77" s="96" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W77" s="99" t="e">
+      <c r="W77" s="96" t="e">
         <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X77" s="99">
+      <c r="X77" s="96">
         <f t="shared" ref="X77" si="19">-X76*0.2</f>
         <v>0</v>
       </c>
@@ -6190,87 +6184,87 @@
       <c r="B78" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="D78" s="107" t="e">
+      <c r="D78" s="104" t="e">
         <f>SUM(D76:D77)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E78" s="107" t="e">
+      <c r="E78" s="104" t="e">
         <f t="shared" ref="E78:W78" si="20">SUM(E76:E77)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F78" s="107" t="e">
+      <c r="F78" s="104" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G78" s="107" t="e">
+      <c r="G78" s="104" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H78" s="107" t="e">
+      <c r="H78" s="104" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I78" s="107" t="e">
+      <c r="I78" s="104" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J78" s="107" t="e">
+      <c r="J78" s="104" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K78" s="107" t="e">
+      <c r="K78" s="104" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L78" s="107" t="e">
+      <c r="L78" s="104" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M78" s="107" t="e">
+      <c r="M78" s="104" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N78" s="107" t="e">
+      <c r="N78" s="104" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O78" s="107" t="e">
+      <c r="O78" s="104" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P78" s="107" t="e">
+      <c r="P78" s="104" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q78" s="107" t="e">
+      <c r="Q78" s="104" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R78" s="107" t="e">
+      <c r="R78" s="104" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S78" s="107" t="e">
+      <c r="S78" s="104" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T78" s="107" t="e">
+      <c r="T78" s="104" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U78" s="107" t="e">
+      <c r="U78" s="104" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V78" s="107" t="e">
+      <c r="V78" s="104" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W78" s="107" t="e">
+      <c r="W78" s="104" t="e">
         <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X78" s="107">
+      <c r="X78" s="104">
         <f t="shared" ref="X78" si="21">SUM(X76:X77)</f>
         <v>0</v>
       </c>
@@ -6517,83 +6511,83 @@
         <v>23</v>
       </c>
       <c r="C85" s="85"/>
-      <c r="D85" s="108" t="e">
+      <c r="D85" s="105" t="e">
         <f>D78</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E85" s="108" t="e">
+      <c r="E85" s="105" t="e">
         <f t="shared" ref="E85:W85" si="23">E78</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F85" s="108" t="e">
+      <c r="F85" s="105" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G85" s="108" t="e">
+      <c r="G85" s="105" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H85" s="108" t="e">
+      <c r="H85" s="105" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I85" s="108" t="e">
+      <c r="I85" s="105" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J85" s="108" t="e">
+      <c r="J85" s="105" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K85" s="108" t="e">
+      <c r="K85" s="105" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L85" s="108" t="e">
+      <c r="L85" s="105" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M85" s="108" t="e">
+      <c r="M85" s="105" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N85" s="108" t="e">
+      <c r="N85" s="105" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O85" s="108" t="e">
+      <c r="O85" s="105" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P85" s="108" t="e">
+      <c r="P85" s="105" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q85" s="108" t="e">
+      <c r="Q85" s="105" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R85" s="108" t="e">
+      <c r="R85" s="105" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S85" s="108" t="e">
+      <c r="S85" s="105" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T85" s="108" t="e">
+      <c r="T85" s="105" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U85" s="108" t="e">
+      <c r="U85" s="105" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V85" s="108" t="e">
+      <c r="V85" s="105" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W85" s="108" t="e">
+      <c r="W85" s="105" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
@@ -6605,171 +6599,171 @@
         <v>24</v>
       </c>
       <c r="C86" s="85"/>
-      <c r="D86" s="109" t="e">
+      <c r="D86" s="106" t="e">
         <f>-D67</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E86" s="109" t="e">
+      <c r="E86" s="106" t="e">
         <f t="shared" ref="E86:W86" si="24">-E67</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F86" s="109" t="e">
+      <c r="F86" s="106" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G86" s="109" t="e">
+      <c r="G86" s="106" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H86" s="109" t="e">
+      <c r="H86" s="106" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I86" s="109" t="e">
+      <c r="I86" s="106" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J86" s="109" t="e">
+      <c r="J86" s="106" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K86" s="109" t="e">
+      <c r="K86" s="106" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L86" s="109" t="e">
+      <c r="L86" s="106" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M86" s="109" t="e">
+      <c r="M86" s="106" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N86" s="109" t="e">
+      <c r="N86" s="106" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O86" s="109" t="e">
+      <c r="O86" s="106" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P86" s="109" t="e">
+      <c r="P86" s="106" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q86" s="109" t="e">
+      <c r="Q86" s="106" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R86" s="109" t="e">
+      <c r="R86" s="106" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S86" s="109" t="e">
+      <c r="S86" s="106" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T86" s="109" t="e">
+      <c r="T86" s="106" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U86" s="109" t="e">
+      <c r="U86" s="106" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V86" s="109" t="e">
+      <c r="V86" s="106" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W86" s="109" t="e">
+      <c r="W86" s="106" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X86" s="110"/>
-      <c r="Y86" s="110"/>
+      <c r="X86" s="107"/>
+      <c r="Y86" s="107"/>
     </row>
     <row r="87" spans="2:25" s="57" customFormat="1">
       <c r="B87" s="85" t="s">
         <v>25</v>
       </c>
       <c r="C87" s="85"/>
-      <c r="D87" s="111" t="e">
+      <c r="D87" s="108" t="e">
         <f>SUM(D85:D86)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E87" s="111" t="e">
+      <c r="E87" s="108" t="e">
         <f t="shared" ref="E87:W87" si="25">SUM(E85:E86)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F87" s="111" t="e">
+      <c r="F87" s="108" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G87" s="111" t="e">
+      <c r="G87" s="108" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H87" s="111" t="e">
+      <c r="H87" s="108" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I87" s="111" t="e">
+      <c r="I87" s="108" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J87" s="111" t="e">
+      <c r="J87" s="108" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K87" s="111" t="e">
+      <c r="K87" s="108" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L87" s="111" t="e">
+      <c r="L87" s="108" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M87" s="111" t="e">
+      <c r="M87" s="108" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N87" s="111" t="e">
+      <c r="N87" s="108" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O87" s="111" t="e">
+      <c r="O87" s="108" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P87" s="111" t="e">
+      <c r="P87" s="108" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q87" s="111" t="e">
+      <c r="Q87" s="108" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R87" s="111" t="e">
+      <c r="R87" s="108" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S87" s="111" t="e">
+      <c r="S87" s="108" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T87" s="111" t="e">
+      <c r="T87" s="108" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U87" s="111" t="e">
+      <c r="U87" s="108" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V87" s="111" t="e">
+      <c r="V87" s="108" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W87" s="111" t="e">
+      <c r="W87" s="108" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
@@ -6805,7 +6799,7 @@
         <v>26</v>
       </c>
       <c r="C89" s="90"/>
-      <c r="D89" s="112">
+      <c r="D89" s="109">
         <f>C44</f>
         <v>0</v>
       </c>
@@ -6885,7 +6879,7 @@
         <v>27</v>
       </c>
       <c r="C92" s="90"/>
-      <c r="D92" s="112">
+      <c r="D92" s="109">
         <f>-D89*D31</f>
         <v>0</v>
       </c>
@@ -6915,26 +6909,26 @@
         <v>28</v>
       </c>
       <c r="C93" s="85"/>
-      <c r="D93" s="116"/>
-      <c r="E93" s="116"/>
-      <c r="F93" s="116"/>
-      <c r="G93" s="116"/>
-      <c r="H93" s="116"/>
-      <c r="I93" s="116"/>
-      <c r="J93" s="116"/>
-      <c r="K93" s="116"/>
-      <c r="L93" s="116"/>
-      <c r="M93" s="116"/>
-      <c r="N93" s="116"/>
-      <c r="O93" s="116"/>
-      <c r="P93" s="116"/>
-      <c r="Q93" s="116"/>
-      <c r="R93" s="116"/>
-      <c r="S93" s="116"/>
-      <c r="T93" s="116"/>
-      <c r="U93" s="116"/>
-      <c r="V93" s="116"/>
-      <c r="W93" s="116"/>
+      <c r="D93" s="113"/>
+      <c r="E93" s="113"/>
+      <c r="F93" s="113"/>
+      <c r="G93" s="113"/>
+      <c r="H93" s="113"/>
+      <c r="I93" s="113"/>
+      <c r="J93" s="113"/>
+      <c r="K93" s="113"/>
+      <c r="L93" s="113"/>
+      <c r="M93" s="113"/>
+      <c r="N93" s="113"/>
+      <c r="O93" s="113"/>
+      <c r="P93" s="113"/>
+      <c r="Q93" s="113"/>
+      <c r="R93" s="113"/>
+      <c r="S93" s="113"/>
+      <c r="T93" s="113"/>
+      <c r="U93" s="113"/>
+      <c r="V93" s="113"/>
+      <c r="W93" s="113"/>
       <c r="X93" s="78"/>
     </row>
     <row r="94" spans="2:25" s="57" customFormat="1">
@@ -6942,7 +6936,7 @@
         <v>29</v>
       </c>
       <c r="C94" s="87"/>
-      <c r="D94" s="108">
+      <c r="D94" s="105">
         <f>-D89*(1-D31)</f>
         <v>0</v>
       </c>
@@ -6973,83 +6967,83 @@
       </c>
       <c r="C95" s="87"/>
       <c r="D95" s="87"/>
-      <c r="E95" s="118" t="e">
+      <c r="E95" s="115" t="e">
         <f>-D85*$D$33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F95" s="118" t="e">
+      <c r="F95" s="115" t="e">
         <f t="shared" ref="F95:W95" si="26">-E85*$D$33</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G95" s="118" t="e">
+      <c r="G95" s="115" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H95" s="118" t="e">
+      <c r="H95" s="115" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I95" s="118" t="e">
+      <c r="I95" s="115" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J95" s="118" t="e">
+      <c r="J95" s="115" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K95" s="118" t="e">
+      <c r="K95" s="115" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L95" s="118" t="e">
+      <c r="L95" s="115" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M95" s="118" t="e">
+      <c r="M95" s="115" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N95" s="118" t="e">
+      <c r="N95" s="115" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O95" s="118" t="e">
+      <c r="O95" s="115" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P95" s="118" t="e">
+      <c r="P95" s="115" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q95" s="118" t="e">
+      <c r="Q95" s="115" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R95" s="118" t="e">
+      <c r="R95" s="115" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S95" s="118" t="e">
+      <c r="S95" s="115" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T95" s="118" t="e">
+      <c r="T95" s="115" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U95" s="118" t="e">
+      <c r="U95" s="115" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V95" s="118" t="e">
+      <c r="V95" s="115" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W95" s="118" t="e">
+      <c r="W95" s="115" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X95" s="118" t="e">
+      <c r="X95" s="115" t="e">
         <f t="shared" ref="X95" si="27">-W85*$D$33</f>
         <v>#DIV/0!</v>
       </c>
@@ -7060,26 +7054,26 @@
       </c>
       <c r="C96" s="92"/>
       <c r="D96" s="92"/>
-      <c r="E96" s="114"/>
-      <c r="F96" s="114"/>
-      <c r="G96" s="114"/>
-      <c r="H96" s="114"/>
-      <c r="I96" s="114"/>
-      <c r="J96" s="114"/>
-      <c r="K96" s="114"/>
-      <c r="L96" s="114"/>
-      <c r="M96" s="114"/>
-      <c r="N96" s="114"/>
-      <c r="O96" s="114"/>
-      <c r="P96" s="114"/>
-      <c r="Q96" s="114"/>
-      <c r="R96" s="114"/>
-      <c r="S96" s="114"/>
-      <c r="T96" s="114"/>
-      <c r="U96" s="114"/>
-      <c r="V96" s="114"/>
-      <c r="W96" s="114"/>
-      <c r="X96" s="113" t="e">
+      <c r="E96" s="111"/>
+      <c r="F96" s="111"/>
+      <c r="G96" s="111"/>
+      <c r="H96" s="111"/>
+      <c r="I96" s="111"/>
+      <c r="J96" s="111"/>
+      <c r="K96" s="111"/>
+      <c r="L96" s="111"/>
+      <c r="M96" s="111"/>
+      <c r="N96" s="111"/>
+      <c r="O96" s="111"/>
+      <c r="P96" s="111"/>
+      <c r="Q96" s="111"/>
+      <c r="R96" s="111"/>
+      <c r="S96" s="111"/>
+      <c r="T96" s="111"/>
+      <c r="U96" s="111"/>
+      <c r="V96" s="111"/>
+      <c r="W96" s="111"/>
+      <c r="X96" s="110" t="e">
         <f>-W101-X95</f>
         <v>#DIV/0!</v>
       </c>
@@ -7138,86 +7132,86 @@
       <c r="B99" s="85" t="s">
         <v>32</v>
       </c>
-      <c r="C99" s="108">
-        <v>0</v>
-      </c>
-      <c r="D99" s="108" t="e">
+      <c r="C99" s="105">
+        <v>0</v>
+      </c>
+      <c r="D99" s="105" t="e">
         <f>SUM(D87:D96)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E99" s="108" t="e">
+      <c r="E99" s="105" t="e">
         <f t="shared" ref="E99:W99" si="28">SUM(E87:E96)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F99" s="108" t="e">
+      <c r="F99" s="105" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G99" s="108" t="e">
+      <c r="G99" s="105" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H99" s="108" t="e">
+      <c r="H99" s="105" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I99" s="108" t="e">
+      <c r="I99" s="105" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J99" s="108" t="e">
+      <c r="J99" s="105" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K99" s="108" t="e">
+      <c r="K99" s="105" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L99" s="108" t="e">
+      <c r="L99" s="105" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M99" s="108" t="e">
+      <c r="M99" s="105" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N99" s="108" t="e">
+      <c r="N99" s="105" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O99" s="108" t="e">
+      <c r="O99" s="105" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P99" s="108" t="e">
+      <c r="P99" s="105" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q99" s="108" t="e">
+      <c r="Q99" s="105" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R99" s="108" t="e">
+      <c r="R99" s="105" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S99" s="108" t="e">
+      <c r="S99" s="105" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T99" s="108" t="e">
+      <c r="T99" s="105" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U99" s="108" t="e">
+      <c r="U99" s="105" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V99" s="108" t="e">
+      <c r="V99" s="105" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W99" s="108" t="e">
+      <c r="W99" s="105" t="e">
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
@@ -7227,86 +7221,86 @@
       <c r="B100" s="85" t="s">
         <v>33</v>
       </c>
-      <c r="C100" s="108">
-        <v>0</v>
-      </c>
-      <c r="D100" s="108">
+      <c r="C100" s="105">
+        <v>0</v>
+      </c>
+      <c r="D100" s="105">
         <f>C101</f>
         <v>0</v>
       </c>
-      <c r="E100" s="108" t="e">
+      <c r="E100" s="105" t="e">
         <f>D101</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F100" s="108" t="e">
+      <c r="F100" s="105" t="e">
         <f>E101</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G100" s="108" t="e">
+      <c r="G100" s="105" t="e">
         <f t="shared" ref="G100:W100" si="29">F101</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H100" s="108" t="e">
+      <c r="H100" s="105" t="e">
         <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I100" s="108" t="e">
+      <c r="I100" s="105" t="e">
         <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J100" s="108" t="e">
+      <c r="J100" s="105" t="e">
         <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K100" s="108" t="e">
+      <c r="K100" s="105" t="e">
         <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L100" s="108" t="e">
+      <c r="L100" s="105" t="e">
         <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M100" s="108" t="e">
+      <c r="M100" s="105" t="e">
         <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N100" s="108" t="e">
+      <c r="N100" s="105" t="e">
         <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O100" s="108" t="e">
+      <c r="O100" s="105" t="e">
         <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P100" s="108" t="e">
+      <c r="P100" s="105" t="e">
         <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q100" s="108" t="e">
+      <c r="Q100" s="105" t="e">
         <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R100" s="108" t="e">
+      <c r="R100" s="105" t="e">
         <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S100" s="108" t="e">
+      <c r="S100" s="105" t="e">
         <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T100" s="108" t="e">
+      <c r="T100" s="105" t="e">
         <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U100" s="108" t="e">
+      <c r="U100" s="105" t="e">
         <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V100" s="108" t="e">
+      <c r="V100" s="105" t="e">
         <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W100" s="108" t="e">
+      <c r="W100" s="105" t="e">
         <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
@@ -7316,86 +7310,86 @@
       <c r="B101" s="85" t="s">
         <v>34</v>
       </c>
-      <c r="C101" s="108">
-        <v>0</v>
-      </c>
-      <c r="D101" s="108" t="e">
+      <c r="C101" s="105">
+        <v>0</v>
+      </c>
+      <c r="D101" s="105" t="e">
         <f>D99+D100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E101" s="108" t="e">
+      <c r="E101" s="105" t="e">
         <f>E99+E100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F101" s="108" t="e">
+      <c r="F101" s="105" t="e">
         <f t="shared" ref="F101:W101" si="30">F99+F100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G101" s="108" t="e">
+      <c r="G101" s="105" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H101" s="108" t="e">
+      <c r="H101" s="105" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I101" s="108" t="e">
+      <c r="I101" s="105" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J101" s="108" t="e">
+      <c r="J101" s="105" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K101" s="108" t="e">
+      <c r="K101" s="105" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L101" s="108" t="e">
+      <c r="L101" s="105" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M101" s="108" t="e">
+      <c r="M101" s="105" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N101" s="108" t="e">
+      <c r="N101" s="105" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O101" s="108" t="e">
+      <c r="O101" s="105" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P101" s="108" t="e">
+      <c r="P101" s="105" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q101" s="108" t="e">
+      <c r="Q101" s="105" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R101" s="108" t="e">
+      <c r="R101" s="105" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S101" s="108" t="e">
+      <c r="S101" s="105" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T101" s="108" t="e">
+      <c r="T101" s="105" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U101" s="108" t="e">
+      <c r="U101" s="105" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V101" s="108" t="e">
+      <c r="V101" s="105" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W101" s="108" t="e">
+      <c r="W101" s="105" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
@@ -7456,87 +7450,87 @@
         <v>35</v>
       </c>
       <c r="C104" s="94"/>
-      <c r="D104" s="115">
+      <c r="D104" s="112">
         <f>-D94</f>
         <v>0</v>
       </c>
-      <c r="E104" s="111" t="e">
+      <c r="E104" s="108" t="e">
         <f>-E95-E96</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F104" s="111" t="e">
+      <c r="F104" s="108" t="e">
         <f t="shared" ref="F104:X104" si="31">-F95-F96</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G104" s="111" t="e">
+      <c r="G104" s="108" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H104" s="111" t="e">
+      <c r="H104" s="108" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I104" s="111" t="e">
+      <c r="I104" s="108" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J104" s="111" t="e">
+      <c r="J104" s="108" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K104" s="111" t="e">
+      <c r="K104" s="108" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L104" s="111" t="e">
+      <c r="L104" s="108" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M104" s="111" t="e">
+      <c r="M104" s="108" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N104" s="111" t="e">
+      <c r="N104" s="108" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O104" s="111" t="e">
+      <c r="O104" s="108" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P104" s="111" t="e">
+      <c r="P104" s="108" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q104" s="111" t="e">
+      <c r="Q104" s="108" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R104" s="111" t="e">
+      <c r="R104" s="108" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S104" s="111" t="e">
+      <c r="S104" s="108" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T104" s="111" t="e">
+      <c r="T104" s="108" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U104" s="111" t="e">
+      <c r="U104" s="108" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V104" s="111" t="e">
+      <c r="V104" s="108" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W104" s="111" t="e">
+      <c r="W104" s="108" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X104" s="111" t="e">
+      <c r="X104" s="108" t="e">
         <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
@@ -7545,7 +7539,7 @@
       <c r="B105" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="C105" s="96" t="e">
+      <c r="C105" s="136" t="e">
         <f>IRR(D104:X104)</f>
         <v>#VALUE!</v>
       </c>
@@ -7576,83 +7570,83 @@
         <v>37</v>
       </c>
       <c r="C106" s="94"/>
-      <c r="D106" s="115" t="e">
+      <c r="D106" s="112" t="e">
         <f>D85-D94</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E106" s="111" t="e">
+      <c r="E106" s="108" t="e">
         <f>E85</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F106" s="111" t="e">
+      <c r="F106" s="108" t="e">
         <f>F85-F96</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G106" s="111" t="e">
+      <c r="G106" s="108" t="e">
         <f t="shared" ref="G106:W106" si="32">G85-G96</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H106" s="111" t="e">
+      <c r="H106" s="108" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I106" s="111" t="e">
+      <c r="I106" s="108" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J106" s="111" t="e">
+      <c r="J106" s="108" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K106" s="111" t="e">
+      <c r="K106" s="108" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L106" s="111" t="e">
+      <c r="L106" s="108" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M106" s="111" t="e">
+      <c r="M106" s="108" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N106" s="111" t="e">
+      <c r="N106" s="108" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O106" s="111" t="e">
+      <c r="O106" s="108" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P106" s="111" t="e">
+      <c r="P106" s="108" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q106" s="111" t="e">
+      <c r="Q106" s="108" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R106" s="111" t="e">
+      <c r="R106" s="108" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S106" s="111" t="e">
+      <c r="S106" s="108" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T106" s="111" t="e">
+      <c r="T106" s="108" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U106" s="111" t="e">
+      <c r="U106" s="108" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V106" s="111" t="e">
+      <c r="V106" s="108" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W106" s="111" t="e">
+      <c r="W106" s="108" t="e">
         <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
@@ -7662,7 +7656,7 @@
       <c r="B107" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="C107" s="95" t="e">
+      <c r="C107" s="136" t="e">
         <f>IRR(D106:W106)</f>
         <v>#VALUE!</v>
       </c>
@@ -7717,86 +7711,86 @@
       <c r="B109" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="C109" s="108">
-        <v>0</v>
-      </c>
-      <c r="D109" s="108">
+      <c r="C109" s="105">
+        <v>0</v>
+      </c>
+      <c r="D109" s="105">
         <f>D92</f>
         <v>0</v>
       </c>
-      <c r="E109" s="108">
+      <c r="E109" s="105">
         <f>D109+E93</f>
         <v>0</v>
       </c>
-      <c r="F109" s="108">
+      <c r="F109" s="105">
         <f t="shared" ref="F109:W109" si="33">E109+F93</f>
         <v>0</v>
       </c>
-      <c r="G109" s="108">
+      <c r="G109" s="105">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="H109" s="108">
+      <c r="H109" s="105">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="I109" s="108">
+      <c r="I109" s="105">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="J109" s="108">
+      <c r="J109" s="105">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="K109" s="108">
+      <c r="K109" s="105">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="L109" s="108">
+      <c r="L109" s="105">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="M109" s="108">
+      <c r="M109" s="105">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="N109" s="108">
+      <c r="N109" s="105">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="O109" s="108">
+      <c r="O109" s="105">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="P109" s="108">
+      <c r="P109" s="105">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="Q109" s="108">
+      <c r="Q109" s="105">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="R109" s="108">
+      <c r="R109" s="105">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="S109" s="108">
+      <c r="S109" s="105">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="T109" s="108">
+      <c r="T109" s="105">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="U109" s="108">
+      <c r="U109" s="105">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="V109" s="108">
+      <c r="V109" s="105">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="W109" s="108">
+      <c r="W109" s="105">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
@@ -7810,16 +7804,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="E10:E13"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B16:B18"/>
     <mergeCell ref="E16:E18"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="E10:E13"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel Generic Template/excel公版.xlsx
+++ b/Excel Generic Template/excel公版.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\信邦\ai_agent2\Excel Generic Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD8D2530-407E-4EA4-B3B8-8CB9A603D989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A462C1-5C1B-4BAE-8FF6-2B23BBBFC25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14303" yWindow="-660" windowWidth="21795" windowHeight="13695" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="空白範例" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -3350,6 +3350,18 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="179" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3364,18 +3376,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3665,12 +3665,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B1" s="137" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="138"/>
+      <c r="B1" s="141" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="142"/>
       <c r="F1" s="33" t="s">
         <v>49</v>
       </c>
@@ -3825,20 +3825,20 @@
       <c r="E6" s="11"/>
     </row>
     <row r="7" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B7" s="137" t="s">
+      <c r="B7" s="141" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="137"/>
-      <c r="D7" s="137"/>
-      <c r="E7" s="137"/>
+      <c r="C7" s="141"/>
+      <c r="D7" s="141"/>
+      <c r="E7" s="141"/>
     </row>
     <row r="8" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B8" s="139" t="s">
+      <c r="B8" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="139"/>
-      <c r="D8" s="139"/>
-      <c r="E8" s="139"/>
+      <c r="C8" s="143"/>
+      <c r="D8" s="143"/>
+      <c r="E8" s="143"/>
     </row>
     <row r="9" spans="2:35" ht="22.5" customHeight="1">
       <c r="B9" s="12" t="s">
@@ -3858,14 +3858,14 @@
       </c>
     </row>
     <row r="10" spans="2:35" ht="30" customHeight="1">
-      <c r="B10" s="140" t="s">
+      <c r="B10" s="144" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="15"/>
-      <c r="E10" s="141">
+      <c r="E10" s="145">
         <f>C3</f>
         <v>20</v>
       </c>
@@ -3874,45 +3874,45 @@
       </c>
     </row>
     <row r="11" spans="2:35" ht="30" customHeight="1">
-      <c r="B11" s="140"/>
+      <c r="B11" s="144"/>
       <c r="C11" s="10" t="s">
         <v>15</v>
       </c>
       <c r="D11" s="16"/>
-      <c r="E11" s="141"/>
+      <c r="E11" s="145"/>
       <c r="F11" s="36" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="12" spans="2:35" ht="30" customHeight="1">
-      <c r="B12" s="140"/>
+      <c r="B12" s="144"/>
       <c r="C12" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="17"/>
-      <c r="E12" s="141"/>
+      <c r="E12" s="145"/>
       <c r="F12" s="36" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="13" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B13" s="140"/>
+      <c r="B13" s="144"/>
       <c r="C13" s="18" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="19"/>
-      <c r="E13" s="141"/>
+      <c r="E13" s="145"/>
       <c r="F13" s="34" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="14" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B14" s="142" t="s">
+      <c r="B14" s="137" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="142"/>
-      <c r="D14" s="142"/>
-      <c r="E14" s="142"/>
+      <c r="C14" s="137"/>
+      <c r="D14" s="137"/>
+      <c r="E14" s="137"/>
     </row>
     <row r="15" spans="2:35" ht="22.5" customHeight="1">
       <c r="B15" s="12" t="s">
@@ -3932,14 +3932,14 @@
       </c>
     </row>
     <row r="16" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B16" s="143" t="s">
+      <c r="B16" s="138" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="20"/>
-      <c r="E16" s="144">
+      <c r="E16" s="139">
         <f>C3</f>
         <v>20</v>
       </c>
@@ -3948,29 +3948,29 @@
       </c>
     </row>
     <row r="17" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B17" s="143"/>
+      <c r="B17" s="138"/>
       <c r="C17" s="10" t="s">
         <v>22</v>
       </c>
       <c r="D17" s="21"/>
-      <c r="E17" s="144"/>
+      <c r="E17" s="139"/>
       <c r="F17" s="34" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B18" s="143"/>
+      <c r="B18" s="138"/>
       <c r="C18" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D18" s="22"/>
-      <c r="E18" s="144"/>
+      <c r="E18" s="139"/>
       <c r="F18" s="34" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="54" customHeight="1">
-      <c r="B19" s="145" t="s">
+      <c r="B19" s="140" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="23" t="s">
@@ -3985,7 +3985,7 @@
       </c>
     </row>
     <row r="20" spans="2:6" ht="20.25" customHeight="1">
-      <c r="B20" s="145"/>
+      <c r="B20" s="140"/>
       <c r="C20" s="24" t="s">
         <v>26</v>
       </c>
@@ -3999,7 +3999,7 @@
       </c>
     </row>
     <row r="21" spans="2:6" ht="30" customHeight="1">
-      <c r="B21" s="145"/>
+      <c r="B21" s="140"/>
       <c r="C21" s="10" t="s">
         <v>27</v>
       </c>
@@ -4105,11 +4105,11 @@
       <c r="E28" s="11"/>
     </row>
     <row r="29" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B29" s="137" t="s">
+      <c r="B29" s="141" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="137"/>
-      <c r="D29" s="137"/>
+      <c r="C29" s="141"/>
+      <c r="D29" s="141"/>
       <c r="E29" s="11"/>
     </row>
     <row r="30" spans="2:6" ht="22.5" customHeight="1">
@@ -4657,6 +4657,7 @@
       <c r="C45" s="64" t="s">
         <v>2</v>
       </c>
+      <c r="D45" s="73"/>
       <c r="E45" s="73"/>
       <c r="F45" s="73"/>
       <c r="G45" s="73"/>
@@ -8245,16 +8246,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="E10:E13"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B16:B18"/>
     <mergeCell ref="E16:E18"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="E10:E13"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Excel Generic Template/excel公版.xlsx
+++ b/Excel Generic Template/excel公版.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\信邦\ai_agent2\Excel Generic Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A462C1-5C1B-4BAE-8FF6-2B23BBBFC25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242924B1-D410-4688-9FDF-02B040AA3415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14303" yWindow="-660" windowWidth="21795" windowHeight="13695" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="空白範例" sheetId="2" r:id="rId1"/>
@@ -3350,6 +3350,21 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="179" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3361,21 +3376,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3665,12 +3665,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B1" s="141" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="142"/>
+      <c r="B1" s="137" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="138"/>
       <c r="F1" s="33" t="s">
         <v>49</v>
       </c>
@@ -3825,20 +3825,20 @@
       <c r="E6" s="11"/>
     </row>
     <row r="7" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B7" s="141" t="s">
+      <c r="B7" s="137" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="141"/>
-      <c r="D7" s="141"/>
-      <c r="E7" s="141"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="137"/>
+      <c r="E7" s="137"/>
     </row>
     <row r="8" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B8" s="143" t="s">
+      <c r="B8" s="139" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="143"/>
-      <c r="D8" s="143"/>
-      <c r="E8" s="143"/>
+      <c r="C8" s="139"/>
+      <c r="D8" s="139"/>
+      <c r="E8" s="139"/>
     </row>
     <row r="9" spans="2:35" ht="22.5" customHeight="1">
       <c r="B9" s="12" t="s">
@@ -3858,14 +3858,14 @@
       </c>
     </row>
     <row r="10" spans="2:35" ht="30" customHeight="1">
-      <c r="B10" s="144" t="s">
+      <c r="B10" s="140" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="15"/>
-      <c r="E10" s="145">
+      <c r="E10" s="141">
         <f>C3</f>
         <v>20</v>
       </c>
@@ -3874,45 +3874,45 @@
       </c>
     </row>
     <row r="11" spans="2:35" ht="30" customHeight="1">
-      <c r="B11" s="144"/>
+      <c r="B11" s="140"/>
       <c r="C11" s="10" t="s">
         <v>15</v>
       </c>
       <c r="D11" s="16"/>
-      <c r="E11" s="145"/>
+      <c r="E11" s="141"/>
       <c r="F11" s="36" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="12" spans="2:35" ht="30" customHeight="1">
-      <c r="B12" s="144"/>
+      <c r="B12" s="140"/>
       <c r="C12" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="17"/>
-      <c r="E12" s="145"/>
+      <c r="E12" s="141"/>
       <c r="F12" s="36" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="13" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B13" s="144"/>
+      <c r="B13" s="140"/>
       <c r="C13" s="18" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="19"/>
-      <c r="E13" s="145"/>
+      <c r="E13" s="141"/>
       <c r="F13" s="34" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="14" spans="2:35" ht="22.5" customHeight="1">
-      <c r="B14" s="137" t="s">
+      <c r="B14" s="142" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="137"/>
-      <c r="D14" s="137"/>
-      <c r="E14" s="137"/>
+      <c r="C14" s="142"/>
+      <c r="D14" s="142"/>
+      <c r="E14" s="142"/>
     </row>
     <row r="15" spans="2:35" ht="22.5" customHeight="1">
       <c r="B15" s="12" t="s">
@@ -3932,14 +3932,14 @@
       </c>
     </row>
     <row r="16" spans="2:35" ht="21.75" customHeight="1">
-      <c r="B16" s="138" t="s">
+      <c r="B16" s="143" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="20"/>
-      <c r="E16" s="139">
+      <c r="E16" s="144">
         <f>C3</f>
         <v>20</v>
       </c>
@@ -3948,29 +3948,29 @@
       </c>
     </row>
     <row r="17" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B17" s="138"/>
+      <c r="B17" s="143"/>
       <c r="C17" s="10" t="s">
         <v>22</v>
       </c>
       <c r="D17" s="21"/>
-      <c r="E17" s="139"/>
+      <c r="E17" s="144"/>
       <c r="F17" s="34" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B18" s="138"/>
+      <c r="B18" s="143"/>
       <c r="C18" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D18" s="22"/>
-      <c r="E18" s="139"/>
+      <c r="E18" s="144"/>
       <c r="F18" s="34" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="54" customHeight="1">
-      <c r="B19" s="140" t="s">
+      <c r="B19" s="145" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="23" t="s">
@@ -3985,7 +3985,7 @@
       </c>
     </row>
     <row r="20" spans="2:6" ht="20.25" customHeight="1">
-      <c r="B20" s="140"/>
+      <c r="B20" s="145"/>
       <c r="C20" s="24" t="s">
         <v>26</v>
       </c>
@@ -3999,7 +3999,7 @@
       </c>
     </row>
     <row r="21" spans="2:6" ht="30" customHeight="1">
-      <c r="B21" s="140"/>
+      <c r="B21" s="145"/>
       <c r="C21" s="10" t="s">
         <v>27</v>
       </c>
@@ -4105,11 +4105,11 @@
       <c r="E28" s="11"/>
     </row>
     <row r="29" spans="2:6" ht="22.5" customHeight="1">
-      <c r="B29" s="141" t="s">
+      <c r="B29" s="137" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="141"/>
-      <c r="D29" s="141"/>
+      <c r="C29" s="137"/>
+      <c r="D29" s="137"/>
       <c r="E29" s="11"/>
     </row>
     <row r="30" spans="2:6" ht="22.5" customHeight="1">
@@ -5932,7 +5932,7 @@
         <v>2</v>
       </c>
       <c r="D68" s="73">
-        <f>D44</f>
+        <f>D45</f>
         <v>0</v>
       </c>
       <c r="E68" s="73">
@@ -8246,16 +8246,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="E10:E13"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B29:D29"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
